--- a/new_model/model_Fe_Si_B_260311/fine_tuning/matpes_nofe8b4_0.0001_40_10_rnd_e/test_res/model_rnd_e_matpes_nofe8b4_lr0.0001_40_10_test.xlsx
+++ b/new_model/model_Fe_Si_B_260311/fine_tuning/matpes_nofe8b4_0.0001_40_10_rnd_e/test_res/model_rnd_e_matpes_nofe8b4_lr0.0001_40_10_test.xlsx
@@ -479,7 +479,7 @@
         <v>-352.89092233</v>
       </c>
       <c r="E2" t="n">
-        <v>-353.1501167440813</v>
+        <v>-353.1501167440814</v>
       </c>
       <c r="F2" t="n">
         <v>-6535.017080185185</v>
@@ -504,13 +504,13 @@
         <v>-354.71875992</v>
       </c>
       <c r="E3" t="n">
-        <v>-355.25912250836</v>
+        <v>-355.2591225083599</v>
       </c>
       <c r="F3" t="n">
         <v>-6568.865924444445</v>
       </c>
       <c r="G3" t="n">
-        <v>-6578.872639043703</v>
+        <v>-6578.872639043701</v>
       </c>
     </row>
     <row r="4">
@@ -554,13 +554,13 @@
         <v>-356.0869274</v>
       </c>
       <c r="E5" t="n">
-        <v>-356.9276013540673</v>
+        <v>-356.9276013540674</v>
       </c>
       <c r="F5" t="n">
         <v>-6594.202359259259</v>
       </c>
       <c r="G5" t="n">
-        <v>-6609.77039544569</v>
+        <v>-6609.770395445692</v>
       </c>
     </row>
     <row r="6">
@@ -579,13 +579,13 @@
         <v>-359.84864784</v>
       </c>
       <c r="E6" t="n">
-        <v>-360.3461800199902</v>
+        <v>-360.3461800199903</v>
       </c>
       <c r="F6" t="n">
         <v>-6663.863848888889</v>
       </c>
       <c r="G6" t="n">
-        <v>-6673.077407777597</v>
+        <v>-6673.077407777599</v>
       </c>
     </row>
     <row r="7">
@@ -604,13 +604,13 @@
         <v>-358.03511683</v>
       </c>
       <c r="E7" t="n">
-        <v>-358.7227010745767</v>
+        <v>-358.7227010745768</v>
       </c>
       <c r="F7" t="n">
         <v>-6630.279941296297</v>
       </c>
       <c r="G7" t="n">
-        <v>-6643.012982862531</v>
+        <v>-6643.012982862532</v>
       </c>
     </row>
     <row r="8">
@@ -654,13 +654,13 @@
         <v>-360.19257752</v>
       </c>
       <c r="E9" t="n">
-        <v>-361.0519572348706</v>
+        <v>-361.0519572348705</v>
       </c>
       <c r="F9" t="n">
         <v>-6670.232917037037</v>
       </c>
       <c r="G9" t="n">
-        <v>-6686.147356201307</v>
+        <v>-6686.147356201306</v>
       </c>
     </row>
     <row r="10">
@@ -735,7 +735,7 @@
         <v>-6560.624371481482</v>
       </c>
       <c r="G12" t="n">
-        <v>-6581.311696268956</v>
+        <v>-6581.311696268957</v>
       </c>
     </row>
     <row r="13">
@@ -804,7 +804,7 @@
         <v>-355.98978912</v>
       </c>
       <c r="E15" t="n">
-        <v>-357.0619284816954</v>
+        <v>-357.0619284816953</v>
       </c>
       <c r="F15" t="n">
         <v>-6592.403502222222</v>
@@ -929,13 +929,13 @@
         <v>-357.38458237</v>
       </c>
       <c r="E20" t="n">
-        <v>-358.2926415108785</v>
+        <v>-358.2926415108786</v>
       </c>
       <c r="F20" t="n">
         <v>-6618.233006851851</v>
       </c>
       <c r="G20" t="n">
-        <v>-6635.048916868121</v>
+        <v>-6635.048916868122</v>
       </c>
     </row>
     <row r="21">
@@ -960,7 +960,7 @@
         <v>-6678.663742777778</v>
       </c>
       <c r="G21" t="n">
-        <v>-6594.388368262091</v>
+        <v>-6594.38836826209</v>
       </c>
     </row>
     <row r="22">
@@ -1054,13 +1054,13 @@
         <v>-357.66477533</v>
       </c>
       <c r="E25" t="n">
-        <v>-358.3794679939109</v>
+        <v>-358.3794679939108</v>
       </c>
       <c r="F25" t="n">
         <v>-6623.42176537037</v>
       </c>
       <c r="G25" t="n">
-        <v>-6636.656814702053</v>
+        <v>-6636.656814702052</v>
       </c>
     </row>
     <row r="26">
@@ -1085,7 +1085,7 @@
         <v>-6678.452526481481</v>
       </c>
       <c r="G26" t="n">
-        <v>-6699.704192236271</v>
+        <v>-6699.704192236273</v>
       </c>
     </row>
     <row r="27">
@@ -1154,13 +1154,13 @@
         <v>-362.16073209</v>
       </c>
       <c r="E29" t="n">
-        <v>-362.5710886919695</v>
+        <v>-362.5710886919696</v>
       </c>
       <c r="F29" t="n">
         <v>-6706.680223888889</v>
       </c>
       <c r="G29" t="n">
-        <v>-6714.279420221657</v>
+        <v>-6714.27942022166</v>
       </c>
     </row>
     <row r="30">
@@ -1204,13 +1204,13 @@
         <v>-356.29007932</v>
       </c>
       <c r="E31" t="n">
-        <v>-356.8578809425286</v>
+        <v>-356.8578809425287</v>
       </c>
       <c r="F31" t="n">
         <v>-6597.964431851852</v>
       </c>
       <c r="G31" t="n">
-        <v>-6608.479276713492</v>
+        <v>-6608.479276713494</v>
       </c>
     </row>
     <row r="32">
@@ -1304,13 +1304,13 @@
         <v>-360.03553538</v>
       </c>
       <c r="E35" t="n">
-        <v>-360.8893702146419</v>
+        <v>-360.889370214642</v>
       </c>
       <c r="F35" t="n">
         <v>-6667.32472925926</v>
       </c>
       <c r="G35" t="n">
-        <v>-6683.136485456332</v>
+        <v>-6683.136485456333</v>
       </c>
     </row>
     <row r="36">
@@ -1379,13 +1379,13 @@
         <v>-355.68126147</v>
       </c>
       <c r="E38" t="n">
-        <v>-356.263097639294</v>
+        <v>-356.2630976392939</v>
       </c>
       <c r="F38" t="n">
         <v>-6586.690027222222</v>
       </c>
       <c r="G38" t="n">
-        <v>-6597.464771098036</v>
+        <v>-6597.464771098034</v>
       </c>
     </row>
     <row r="39">
@@ -1410,7 +1410,7 @@
         <v>-6409.853097962964</v>
       </c>
       <c r="G39" t="n">
-        <v>-6423.078974080888</v>
+        <v>-6423.078974080887</v>
       </c>
     </row>
     <row r="40">
@@ -1454,13 +1454,13 @@
         <v>-361.12052669</v>
       </c>
       <c r="E41" t="n">
-        <v>-361.9341177822771</v>
+        <v>-361.9341177822772</v>
       </c>
       <c r="F41" t="n">
         <v>-6687.417160925927</v>
       </c>
       <c r="G41" t="n">
-        <v>-6702.483662634761</v>
+        <v>-6702.483662634762</v>
       </c>
     </row>
     <row r="42">
@@ -1479,13 +1479,13 @@
         <v>-356.97023688</v>
       </c>
       <c r="E42" t="n">
-        <v>-358.0660511734706</v>
+        <v>-358.0660511734705</v>
       </c>
       <c r="F42" t="n">
         <v>-6610.559942222223</v>
       </c>
       <c r="G42" t="n">
-        <v>-6630.852799508714</v>
+        <v>-6630.852799508713</v>
       </c>
     </row>
     <row r="43">
@@ -1535,7 +1535,7 @@
         <v>-6701.84344037037</v>
       </c>
       <c r="G44" t="n">
-        <v>-6710.779345949036</v>
+        <v>-6710.779345949035</v>
       </c>
     </row>
     <row r="45">
@@ -1604,13 +1604,13 @@
         <v>-359.80143962</v>
       </c>
       <c r="E47" t="n">
-        <v>-360.7321296680469</v>
+        <v>-360.7321296680468</v>
       </c>
       <c r="F47" t="n">
         <v>-6662.989622592593</v>
       </c>
       <c r="G47" t="n">
-        <v>-6680.22462348235</v>
+        <v>-6680.224623482348</v>
       </c>
     </row>
     <row r="48">
@@ -1704,13 +1704,13 @@
         <v>-361.85477759</v>
       </c>
       <c r="E51" t="n">
-        <v>-362.762617954071</v>
+        <v>-362.7626179540711</v>
       </c>
       <c r="F51" t="n">
         <v>-6701.014399814815</v>
       </c>
       <c r="G51" t="n">
-        <v>-6717.826258408722</v>
+        <v>-6717.826258408724</v>
       </c>
     </row>
     <row r="52">
@@ -1879,13 +1879,13 @@
         <v>-357.05933372</v>
       </c>
       <c r="E58" t="n">
-        <v>-357.5613612656088</v>
+        <v>-357.5613612656089</v>
       </c>
       <c r="F58" t="n">
         <v>-6612.209883703704</v>
       </c>
       <c r="G58" t="n">
-        <v>-6621.506690103867</v>
+        <v>-6621.506690103868</v>
       </c>
     </row>
     <row r="59">
@@ -1929,13 +1929,13 @@
         <v>-348.73229168</v>
       </c>
       <c r="E60" t="n">
-        <v>-349.4156733629105</v>
+        <v>-349.4156733629104</v>
       </c>
       <c r="F60" t="n">
         <v>-6458.005401481482</v>
       </c>
       <c r="G60" t="n">
-        <v>-6470.660617831675</v>
+        <v>-6470.660617831674</v>
       </c>
     </row>
     <row r="61">
@@ -1960,7 +1960,7 @@
         <v>-6678.079822777778</v>
       </c>
       <c r="G61" t="n">
-        <v>-6689.864657820905</v>
+        <v>-6689.864657820906</v>
       </c>
     </row>
     <row r="62">
@@ -2004,13 +2004,13 @@
         <v>-362.42007398</v>
       </c>
       <c r="E63" t="n">
-        <v>-363.3547316047169</v>
+        <v>-363.3547316047168</v>
       </c>
       <c r="F63" t="n">
         <v>-6711.482851481481</v>
       </c>
       <c r="G63" t="n">
-        <v>-6728.791326013276</v>
+        <v>-6728.791326013274</v>
       </c>
     </row>
     <row r="64">
@@ -2029,13 +2029,13 @@
         <v>-359.57758351</v>
       </c>
       <c r="E64" t="n">
-        <v>-360.145700564123</v>
+        <v>-360.1457005641231</v>
       </c>
       <c r="F64" t="n">
         <v>-6658.844139074075</v>
       </c>
       <c r="G64" t="n">
-        <v>-6669.364825261538</v>
+        <v>-6669.364825261539</v>
       </c>
     </row>
     <row r="65">
@@ -2054,13 +2054,13 @@
         <v>-120.42308565</v>
       </c>
       <c r="E65" t="n">
-        <v>-118.8811145692296</v>
+        <v>-118.8811145692297</v>
       </c>
       <c r="F65" t="n">
         <v>-6690.171425</v>
       </c>
       <c r="G65" t="n">
-        <v>-6604.506364957201</v>
+        <v>-6604.506364957203</v>
       </c>
     </row>
     <row r="66">
@@ -2160,7 +2160,7 @@
         <v>-6588.597629444444</v>
       </c>
       <c r="G69" t="n">
-        <v>-6598.219715484264</v>
+        <v>-6598.219715484265</v>
       </c>
     </row>
     <row r="70">
@@ -2179,13 +2179,13 @@
         <v>-361.82007421</v>
       </c>
       <c r="E70" t="n">
-        <v>-362.6513408472435</v>
+        <v>-362.6513408472436</v>
       </c>
       <c r="F70" t="n">
         <v>-6700.37174462963</v>
       </c>
       <c r="G70" t="n">
-        <v>-6715.765571245251</v>
+        <v>-6715.765571245252</v>
       </c>
     </row>
     <row r="71">
@@ -2204,13 +2204,13 @@
         <v>-351.34183157</v>
       </c>
       <c r="E71" t="n">
-        <v>-352.1448617265715</v>
+        <v>-352.1448617265716</v>
       </c>
       <c r="F71" t="n">
         <v>-6506.33021425926</v>
       </c>
       <c r="G71" t="n">
-        <v>-6521.201143084659</v>
+        <v>-6521.20114308466</v>
       </c>
     </row>
     <row r="72">
@@ -2229,13 +2229,13 @@
         <v>-359.50610907</v>
       </c>
       <c r="E72" t="n">
-        <v>-360.0824948917174</v>
+        <v>-360.0824948917175</v>
       </c>
       <c r="F72" t="n">
         <v>-6657.520538333333</v>
       </c>
       <c r="G72" t="n">
-        <v>-6668.19434984662</v>
+        <v>-6668.194349846622</v>
       </c>
     </row>
     <row r="73">
@@ -2285,7 +2285,7 @@
         <v>-6620.841493518518</v>
       </c>
       <c r="G74" t="n">
-        <v>-6634.944542986999</v>
+        <v>-6634.944542987</v>
       </c>
     </row>
     <row r="75">
@@ -2335,7 +2335,7 @@
         <v>-6621.838402037037</v>
       </c>
       <c r="G76" t="n">
-        <v>-6629.092924144159</v>
+        <v>-6629.09292414416</v>
       </c>
     </row>
     <row r="77">
@@ -2354,13 +2354,13 @@
         <v>-360.60359796</v>
       </c>
       <c r="E77" t="n">
-        <v>-360.8640547744736</v>
+        <v>-360.8640547744737</v>
       </c>
       <c r="F77" t="n">
         <v>-6677.844406666666</v>
       </c>
       <c r="G77" t="n">
-        <v>-6682.66768100877</v>
+        <v>-6682.667681008773</v>
       </c>
     </row>
     <row r="78">
@@ -2479,13 +2479,13 @@
         <v>-359.02627606</v>
       </c>
       <c r="E82" t="n">
-        <v>-359.7419932949487</v>
+        <v>-359.7419932949488</v>
       </c>
       <c r="F82" t="n">
         <v>-6648.634741851852</v>
       </c>
       <c r="G82" t="n">
-        <v>-6661.888764721272</v>
+        <v>-6661.888764721273</v>
       </c>
     </row>
     <row r="83">
@@ -2504,13 +2504,13 @@
         <v>-357.07680184</v>
       </c>
       <c r="E83" t="n">
-        <v>-357.7451810073044</v>
+        <v>-357.7451810073043</v>
       </c>
       <c r="F83" t="n">
         <v>-6612.533367407407</v>
       </c>
       <c r="G83" t="n">
-        <v>-6624.910759394526</v>
+        <v>-6624.910759394525</v>
       </c>
     </row>
     <row r="84">
@@ -2560,7 +2560,7 @@
         <v>-6669.518325925926</v>
       </c>
       <c r="G85" t="n">
-        <v>-6677.968788788157</v>
+        <v>-6677.968788788158</v>
       </c>
     </row>
     <row r="86">
@@ -2760,7 +2760,7 @@
         <v>-6612.370690555555</v>
       </c>
       <c r="G93" t="n">
-        <v>-6525.175547562476</v>
+        <v>-6525.175547562478</v>
       </c>
     </row>
     <row r="94">
@@ -2785,7 +2785,7 @@
         <v>-6695.12405537037</v>
       </c>
       <c r="G94" t="n">
-        <v>-6711.755719445697</v>
+        <v>-6711.755719445696</v>
       </c>
     </row>
     <row r="95">
@@ -2854,13 +2854,13 @@
         <v>-361.53601897</v>
       </c>
       <c r="E97" t="n">
-        <v>-362.0314612329049</v>
+        <v>-362.0314612329048</v>
       </c>
       <c r="F97" t="n">
         <v>-6695.111462407407</v>
       </c>
       <c r="G97" t="n">
-        <v>-6704.286319127869</v>
+        <v>-6704.286319127867</v>
       </c>
     </row>
     <row r="98">
@@ -2904,13 +2904,13 @@
         <v>-346.29628625</v>
       </c>
       <c r="E99" t="n">
-        <v>-346.7019606716755</v>
+        <v>-346.7019606716754</v>
       </c>
       <c r="F99" t="n">
         <v>-6412.894189814815</v>
       </c>
       <c r="G99" t="n">
-        <v>-6420.406679105101</v>
+        <v>-6420.4066791051</v>
       </c>
     </row>
     <row r="100">
@@ -2929,13 +2929,13 @@
         <v>-361.0405644</v>
       </c>
       <c r="E100" t="n">
-        <v>-361.913084942896</v>
+        <v>-361.9130849428959</v>
       </c>
       <c r="F100" t="n">
         <v>-6685.936377777777</v>
       </c>
       <c r="G100" t="n">
-        <v>-6702.094165609185</v>
+        <v>-6702.094165609184</v>
       </c>
     </row>
     <row r="101">
@@ -3079,13 +3079,13 @@
         <v>-360.11768403</v>
       </c>
       <c r="E106" t="n">
-        <v>-360.7159644841181</v>
+        <v>-360.715964484118</v>
       </c>
       <c r="F106" t="n">
         <v>-6668.846000555555</v>
       </c>
       <c r="G106" t="n">
-        <v>-6679.92526822441</v>
+        <v>-6679.925268224408</v>
       </c>
     </row>
     <row r="107">
@@ -3104,13 +3104,13 @@
         <v>-360.89120086</v>
       </c>
       <c r="E107" t="n">
-        <v>-361.5524745875355</v>
+        <v>-361.5524745875354</v>
       </c>
       <c r="F107" t="n">
         <v>-6683.170386296297</v>
       </c>
       <c r="G107" t="n">
-        <v>-6695.416196065472</v>
+        <v>-6695.416196065471</v>
       </c>
     </row>
     <row r="108">
@@ -3160,7 +3160,7 @@
         <v>-6617.695571851852</v>
       </c>
       <c r="G109" t="n">
-        <v>-6631.345413063034</v>
+        <v>-6631.345413063033</v>
       </c>
     </row>
     <row r="110">
@@ -3185,7 +3185,7 @@
         <v>-6709.862471111111</v>
       </c>
       <c r="G110" t="n">
-        <v>-6718.117781339516</v>
+        <v>-6718.117781339517</v>
       </c>
     </row>
     <row r="111">
@@ -3235,7 +3235,7 @@
         <v>-6618.13776037037</v>
       </c>
       <c r="G112" t="n">
-        <v>-6631.58610077663</v>
+        <v>-6631.586100776632</v>
       </c>
     </row>
     <row r="113">
@@ -3304,13 +3304,13 @@
         <v>-357.29227817</v>
       </c>
       <c r="E115" t="n">
-        <v>-357.8766787732224</v>
+        <v>-357.8766787732225</v>
       </c>
       <c r="F115" t="n">
         <v>-6616.523669814814</v>
       </c>
       <c r="G115" t="n">
-        <v>-6627.345903207823</v>
+        <v>-6627.345903207824</v>
       </c>
     </row>
     <row r="116">
@@ -3404,13 +3404,13 @@
         <v>-352.75395071</v>
       </c>
       <c r="E119" t="n">
-        <v>-353.5856663204293</v>
+        <v>-353.5856663204294</v>
       </c>
       <c r="F119" t="n">
         <v>-6532.480568703704</v>
       </c>
       <c r="G119" t="n">
-        <v>-6547.88270963758</v>
+        <v>-6547.882709637581</v>
       </c>
     </row>
     <row r="120">
@@ -3429,13 +3429,13 @@
         <v>-362.17572767</v>
       </c>
       <c r="E120" t="n">
-        <v>-362.9727668076359</v>
+        <v>-362.972766807636</v>
       </c>
       <c r="F120" t="n">
         <v>-6706.957919814815</v>
       </c>
       <c r="G120" t="n">
-        <v>-6721.71790384511</v>
+        <v>-6721.717903845111</v>
       </c>
     </row>
     <row r="121">
@@ -3454,13 +3454,13 @@
         <v>-357.45867594</v>
       </c>
       <c r="E121" t="n">
-        <v>-358.09240172559</v>
+        <v>-358.0924017255901</v>
       </c>
       <c r="F121" t="n">
         <v>-6619.60511</v>
       </c>
       <c r="G121" t="n">
-        <v>-6631.340772696112</v>
+        <v>-6631.340772696113</v>
       </c>
     </row>
     <row r="122">
@@ -3510,7 +3510,7 @@
         <v>-6811.255107777778</v>
       </c>
       <c r="G123" t="n">
-        <v>-6725.100935508706</v>
+        <v>-6725.100935508704</v>
       </c>
     </row>
     <row r="124">
@@ -3610,7 +3610,7 @@
         <v>-6881.245245</v>
       </c>
       <c r="G127" t="n">
-        <v>-6796.142129785785</v>
+        <v>-6796.142129785783</v>
       </c>
     </row>
     <row r="128">
@@ -3760,7 +3760,7 @@
         <v>-6733.266356851852</v>
       </c>
       <c r="G133" t="n">
-        <v>-6744.644428879747</v>
+        <v>-6744.644428879746</v>
       </c>
     </row>
     <row r="134">
@@ -3879,13 +3879,13 @@
         <v>-364.81041283</v>
       </c>
       <c r="E138" t="n">
-        <v>-365.2990696446201</v>
+        <v>-365.29906964462</v>
       </c>
       <c r="F138" t="n">
         <v>-6755.748385740741</v>
       </c>
       <c r="G138" t="n">
-        <v>-6764.797586011484</v>
+        <v>-6764.797586011483</v>
       </c>
     </row>
     <row r="139">
@@ -4035,7 +4035,7 @@
         <v>-6843.828052777778</v>
       </c>
       <c r="G144" t="n">
-        <v>-6773.336161526767</v>
+        <v>-6773.336161526765</v>
       </c>
     </row>
     <row r="145">
@@ -4110,7 +4110,7 @@
         <v>-6781.524434444445</v>
       </c>
       <c r="G147" t="n">
-        <v>-6699.154617698066</v>
+        <v>-6699.154617698065</v>
       </c>
     </row>
     <row r="148">
@@ -4135,7 +4135,7 @@
         <v>-6729.986600925926</v>
       </c>
       <c r="G148" t="n">
-        <v>-6744.620720257924</v>
+        <v>-6744.620720257923</v>
       </c>
     </row>
     <row r="149">
@@ -4185,7 +4185,7 @@
         <v>-6726.533117407408</v>
       </c>
       <c r="G150" t="n">
-        <v>-6738.869329691123</v>
+        <v>-6738.869329691124</v>
       </c>
     </row>
     <row r="151">
@@ -4229,13 +4229,13 @@
         <v>-367.22130349</v>
       </c>
       <c r="E152" t="n">
-        <v>-367.9962202184728</v>
+        <v>-367.9962202184729</v>
       </c>
       <c r="F152" t="n">
         <v>-6800.394509074074</v>
       </c>
       <c r="G152" t="n">
-        <v>-6814.744818860608</v>
+        <v>-6814.744818860609</v>
       </c>
     </row>
     <row r="153">
@@ -4304,13 +4304,13 @@
         <v>-363.42060594</v>
       </c>
       <c r="E155" t="n">
-        <v>-363.8503177716675</v>
+        <v>-363.8503177716676</v>
       </c>
       <c r="F155" t="n">
         <v>-6730.011221111111</v>
       </c>
       <c r="G155" t="n">
-        <v>-6737.968847623472</v>
+        <v>-6737.968847623473</v>
       </c>
     </row>
     <row r="156">
@@ -4354,13 +4354,13 @@
         <v>-362.56642406</v>
       </c>
       <c r="E157" t="n">
-        <v>-363.3016557216393</v>
+        <v>-363.3016557216392</v>
       </c>
       <c r="F157" t="n">
         <v>-6714.193038148148</v>
       </c>
       <c r="G157" t="n">
-        <v>-6727.808439289616</v>
+        <v>-6727.808439289615</v>
       </c>
     </row>
     <row r="158">
@@ -4410,7 +4410,7 @@
         <v>-6870.915102592593</v>
       </c>
       <c r="G159" t="n">
-        <v>-6886.364868490309</v>
+        <v>-6886.36486849031</v>
       </c>
     </row>
     <row r="160">
@@ -4429,13 +4429,13 @@
         <v>-363.42181068</v>
       </c>
       <c r="E160" t="n">
-        <v>-363.7280706536444</v>
+        <v>-363.7280706536445</v>
       </c>
       <c r="F160" t="n">
         <v>-6730.033531111111</v>
       </c>
       <c r="G160" t="n">
-        <v>-6735.705012104526</v>
+        <v>-6735.705012104528</v>
       </c>
     </row>
     <row r="161">
@@ -4460,7 +4460,7 @@
         <v>-6753.823457592592</v>
       </c>
       <c r="G161" t="n">
-        <v>-6765.872973401758</v>
+        <v>-6765.872973401757</v>
       </c>
     </row>
     <row r="162">
@@ -4529,13 +4529,13 @@
         <v>-364.035281</v>
       </c>
       <c r="E164" t="n">
-        <v>-364.9406146994787</v>
+        <v>-364.9406146994786</v>
       </c>
       <c r="F164" t="n">
         <v>-6741.394092592593</v>
       </c>
       <c r="G164" t="n">
-        <v>-6758.159531471827</v>
+        <v>-6758.159531471826</v>
       </c>
     </row>
     <row r="165">
@@ -4560,7 +4560,7 @@
         <v>-6758.422900925926</v>
       </c>
       <c r="G165" t="n">
-        <v>-6773.620906621604</v>
+        <v>-6773.620906621606</v>
       </c>
     </row>
     <row r="166">
@@ -4579,13 +4579,13 @@
         <v>-123.43375618</v>
       </c>
       <c r="E166" t="n">
-        <v>-122.0254538004711</v>
+        <v>-122.025453800471</v>
       </c>
       <c r="F166" t="n">
         <v>-6857.430898888889</v>
       </c>
       <c r="G166" t="n">
-        <v>-6779.191877803948</v>
+        <v>-6779.191877803946</v>
       </c>
     </row>
     <row r="167">
@@ -4835,7 +4835,7 @@
         <v>-6834.667679444445</v>
       </c>
       <c r="G176" t="n">
-        <v>-6750.454404835119</v>
+        <v>-6750.454404835117</v>
       </c>
     </row>
     <row r="177">
@@ -4885,7 +4885,7 @@
         <v>-6718.793581666667</v>
       </c>
       <c r="G178" t="n">
-        <v>-6646.30225867883</v>
+        <v>-6646.302258678828</v>
       </c>
     </row>
     <row r="179">
@@ -4929,13 +4929,13 @@
         <v>-121.0848282</v>
       </c>
       <c r="E180" t="n">
-        <v>-119.6568038074891</v>
+        <v>-119.656803807489</v>
       </c>
       <c r="F180" t="n">
         <v>-6726.9349</v>
       </c>
       <c r="G180" t="n">
-        <v>-6647.60021152717</v>
+        <v>-6647.600211527169</v>
       </c>
     </row>
     <row r="181">
@@ -5085,7 +5085,7 @@
         <v>-7296.46497375</v>
       </c>
       <c r="G186" t="n">
-        <v>-7284.917014546395</v>
+        <v>-7284.917014546396</v>
       </c>
     </row>
     <row r="187">
@@ -5135,7 +5135,7 @@
         <v>-7398.061030625</v>
       </c>
       <c r="G188" t="n">
-        <v>-7389.418038070851</v>
+        <v>-7389.41803807085</v>
       </c>
     </row>
     <row r="189">
@@ -5179,13 +5179,13 @@
         <v>-127.76199014</v>
       </c>
       <c r="E190" t="n">
-        <v>-128.2368811596604</v>
+        <v>-128.2368811596605</v>
       </c>
       <c r="F190" t="n">
         <v>-7985.12438375</v>
       </c>
       <c r="G190" t="n">
-        <v>-8014.805072478775</v>
+        <v>-8014.805072478779</v>
       </c>
     </row>
     <row r="191">
@@ -5210,7 +5210,7 @@
         <v>-8051.6912825</v>
       </c>
       <c r="G191" t="n">
-        <v>-8076.257697811185</v>
+        <v>-8076.257697811187</v>
       </c>
     </row>
     <row r="192">
@@ -5304,13 +5304,13 @@
         <v>-127.99189292</v>
       </c>
       <c r="E195" t="n">
-        <v>-128.3271139511405</v>
+        <v>-128.3271139511406</v>
       </c>
       <c r="F195" t="n">
         <v>-7999.4933075</v>
       </c>
       <c r="G195" t="n">
-        <v>-8020.444621946284</v>
+        <v>-8020.444621946286</v>
       </c>
     </row>
     <row r="196">
@@ -5410,7 +5410,7 @@
         <v>-8166.113448124999</v>
       </c>
       <c r="G199" t="n">
-        <v>-8186.999530698742</v>
+        <v>-8186.999530698744</v>
       </c>
     </row>
     <row r="200">
@@ -5510,7 +5510,7 @@
         <v>-7687.946486875</v>
       </c>
       <c r="G203" t="n">
-        <v>-7676.597854044149</v>
+        <v>-7676.597854044147</v>
       </c>
     </row>
     <row r="204">
@@ -5529,13 +5529,13 @@
         <v>-122.06782885</v>
       </c>
       <c r="E204" t="n">
-        <v>-121.8656776189736</v>
+        <v>-121.8656776189735</v>
       </c>
       <c r="F204" t="n">
         <v>-7629.239303124999</v>
       </c>
       <c r="G204" t="n">
-        <v>-7616.604851185849</v>
+        <v>-7616.604851185847</v>
       </c>
     </row>
     <row r="205">
@@ -5625,13 +5625,13 @@
         <v>-355.76357702</v>
       </c>
       <c r="E2" t="n">
-        <v>-356.3634409284848</v>
+        <v>-356.3634409284847</v>
       </c>
       <c r="F2" t="n">
         <v>-6588.214389259259</v>
       </c>
       <c r="G2" t="n">
-        <v>-6599.322980157125</v>
+        <v>-6599.322980157124</v>
       </c>
     </row>
     <row r="3">
@@ -5681,7 +5681,7 @@
         <v>-6593.849936666667</v>
       </c>
       <c r="G4" t="n">
-        <v>-6610.240633093134</v>
+        <v>-6610.240633093135</v>
       </c>
     </row>
     <row r="5">
@@ -5750,13 +5750,13 @@
         <v>-361.3557364</v>
       </c>
       <c r="E7" t="n">
-        <v>-362.1703829278853</v>
+        <v>-362.1703829278854</v>
       </c>
       <c r="F7" t="n">
         <v>-6691.772896296296</v>
       </c>
       <c r="G7" t="n">
-        <v>-6706.858943108988</v>
+        <v>-6706.858943108989</v>
       </c>
     </row>
     <row r="8">
@@ -5850,13 +5850,13 @@
         <v>-361.31518065</v>
       </c>
       <c r="E11" t="n">
-        <v>-362.1276048556213</v>
+        <v>-362.1276048556214</v>
       </c>
       <c r="F11" t="n">
         <v>-6691.021863888889</v>
       </c>
       <c r="G11" t="n">
-        <v>-6706.066756585579</v>
+        <v>-6706.06675658558</v>
       </c>
     </row>
     <row r="12">
@@ -5975,13 +5975,13 @@
         <v>-360.51117952</v>
       </c>
       <c r="E16" t="n">
-        <v>-361.4319757465554</v>
+        <v>-361.4319757465555</v>
       </c>
       <c r="F16" t="n">
         <v>-6676.132954074074</v>
       </c>
       <c r="G16" t="n">
-        <v>-6693.184736047322</v>
+        <v>-6693.184736047324</v>
       </c>
     </row>
     <row r="17">
@@ -6000,13 +6000,13 @@
         <v>-344.96437191</v>
       </c>
       <c r="E17" t="n">
-        <v>-345.4389293726981</v>
+        <v>-345.4389293726982</v>
       </c>
       <c r="F17" t="n">
         <v>-6388.229109444444</v>
       </c>
       <c r="G17" t="n">
-        <v>-6397.017210605521</v>
+        <v>-6397.017210605523</v>
       </c>
     </row>
     <row r="18">
@@ -6175,13 +6175,13 @@
         <v>-355.21734672</v>
       </c>
       <c r="E24" t="n">
-        <v>-355.8161057487613</v>
+        <v>-355.8161057487614</v>
       </c>
       <c r="F24" t="n">
         <v>-6578.099013333333</v>
       </c>
       <c r="G24" t="n">
-        <v>-6589.18714349558</v>
+        <v>-6589.187143495581</v>
       </c>
     </row>
     <row r="25">
@@ -6206,7 +6206,7 @@
         <v>-6413.788642777778</v>
       </c>
       <c r="G25" t="n">
-        <v>-6431.922172799083</v>
+        <v>-6431.922172799082</v>
       </c>
     </row>
     <row r="26">
@@ -6231,7 +6231,7 @@
         <v>-6711.944562777778</v>
       </c>
       <c r="G26" t="n">
-        <v>-6630.069406629405</v>
+        <v>-6630.069406629403</v>
       </c>
     </row>
     <row r="27">
@@ -6275,13 +6275,13 @@
         <v>-355.95275363</v>
       </c>
       <c r="E28" t="n">
-        <v>-356.7857620951828</v>
+        <v>-356.7857620951827</v>
       </c>
       <c r="F28" t="n">
         <v>-6591.717659814814</v>
       </c>
       <c r="G28" t="n">
-        <v>-6607.143742503385</v>
+        <v>-6607.143742503384</v>
       </c>
     </row>
     <row r="29">
@@ -6300,13 +6300,13 @@
         <v>-342.29795303</v>
       </c>
       <c r="E29" t="n">
-        <v>-343.065574607364</v>
+        <v>-343.0655746073641</v>
       </c>
       <c r="F29" t="n">
         <v>-6338.850982037036</v>
       </c>
       <c r="G29" t="n">
-        <v>-6353.066196432667</v>
+        <v>-6353.066196432668</v>
       </c>
     </row>
     <row r="30">
@@ -6325,13 +6325,13 @@
         <v>-354.85796789</v>
       </c>
       <c r="E30" t="n">
-        <v>-355.2722341093745</v>
+        <v>-355.2722341093746</v>
       </c>
       <c r="F30" t="n">
         <v>-6571.443849814815</v>
       </c>
       <c r="G30" t="n">
-        <v>-6579.115446469898</v>
+        <v>-6579.115446469899</v>
       </c>
     </row>
     <row r="31">
@@ -6400,13 +6400,13 @@
         <v>-353.17400791</v>
       </c>
       <c r="E33" t="n">
-        <v>-353.9420470799131</v>
+        <v>-353.9420470799132</v>
       </c>
       <c r="F33" t="n">
         <v>-6540.25940574074</v>
       </c>
       <c r="G33" t="n">
-        <v>-6554.482353331724</v>
+        <v>-6554.482353331725</v>
       </c>
     </row>
     <row r="34">
@@ -6450,13 +6450,13 @@
         <v>-357.30992288</v>
       </c>
       <c r="E35" t="n">
-        <v>-358.0357307145594</v>
+        <v>-358.0357307145593</v>
       </c>
       <c r="F35" t="n">
         <v>-6616.850423703703</v>
       </c>
       <c r="G35" t="n">
-        <v>-6630.291309528878</v>
+        <v>-6630.291309528876</v>
       </c>
     </row>
     <row r="36">
@@ -6525,13 +6525,13 @@
         <v>-358.56298625</v>
       </c>
       <c r="E38" t="n">
-        <v>-359.3451592903987</v>
+        <v>-359.3451592903988</v>
       </c>
       <c r="F38" t="n">
         <v>-6640.055300925927</v>
       </c>
       <c r="G38" t="n">
-        <v>-6654.539986859235</v>
+        <v>-6654.539986859237</v>
       </c>
     </row>
     <row r="39">
@@ -6700,13 +6700,13 @@
         <v>-351.65762208</v>
       </c>
       <c r="E45" t="n">
-        <v>-352.4077012999643</v>
+        <v>-352.4077012999642</v>
       </c>
       <c r="F45" t="n">
         <v>-6512.178186666667</v>
       </c>
       <c r="G45" t="n">
-        <v>-6526.068542591932</v>
+        <v>-6526.06854259193</v>
       </c>
     </row>
     <row r="46">
@@ -6825,13 +6825,13 @@
         <v>-355.29472392</v>
       </c>
       <c r="E50" t="n">
-        <v>-355.8178420116939</v>
+        <v>-355.817842011694</v>
       </c>
       <c r="F50" t="n">
         <v>-6579.531924444444</v>
       </c>
       <c r="G50" t="n">
-        <v>-6589.219296512851</v>
+        <v>-6589.219296512852</v>
       </c>
     </row>
     <row r="51">
@@ -6881,7 +6881,7 @@
         <v>-6565.090397037037</v>
       </c>
       <c r="G52" t="n">
-        <v>-6583.655472411115</v>
+        <v>-6583.655472411116</v>
       </c>
     </row>
     <row r="53">
@@ -6950,13 +6950,13 @@
         <v>-358.5348658</v>
       </c>
       <c r="E55" t="n">
-        <v>-359.5403114186555</v>
+        <v>-359.5403114186554</v>
       </c>
       <c r="F55" t="n">
         <v>-6639.534551851852</v>
       </c>
       <c r="G55" t="n">
-        <v>-6658.153915160287</v>
+        <v>-6658.153915160286</v>
       </c>
     </row>
     <row r="56">
@@ -7006,7 +7006,7 @@
         <v>-6710.561754259259</v>
       </c>
       <c r="G57" t="n">
-        <v>-6722.671072094468</v>
+        <v>-6722.671072094467</v>
       </c>
     </row>
     <row r="58">
@@ -7025,13 +7025,13 @@
         <v>-362.17224142</v>
       </c>
       <c r="E58" t="n">
-        <v>-362.8801987941521</v>
+        <v>-362.880198794152</v>
       </c>
       <c r="F58" t="n">
         <v>-6706.893359629629</v>
       </c>
       <c r="G58" t="n">
-        <v>-6720.003681373187</v>
+        <v>-6720.003681373185</v>
       </c>
     </row>
     <row r="59">
@@ -7106,7 +7106,7 @@
         <v>-6692.750853703705</v>
       </c>
       <c r="G61" t="n">
-        <v>-6700.054905023997</v>
+        <v>-6700.054905023996</v>
       </c>
     </row>
     <row r="62">
@@ -7150,13 +7150,13 @@
         <v>-360.27798756</v>
       </c>
       <c r="E63" t="n">
-        <v>-361.2988485054429</v>
+        <v>-361.298848505443</v>
       </c>
       <c r="F63" t="n">
         <v>-6671.814584444444</v>
       </c>
       <c r="G63" t="n">
-        <v>-6690.719416767462</v>
+        <v>-6690.719416767463</v>
       </c>
     </row>
     <row r="64">
@@ -7175,13 +7175,13 @@
         <v>-356.92988655</v>
       </c>
       <c r="E64" t="n">
-        <v>-357.7924833130027</v>
+        <v>-357.7924833130026</v>
       </c>
       <c r="F64" t="n">
         <v>-6609.812713888889</v>
       </c>
       <c r="G64" t="n">
-        <v>-6625.786728018568</v>
+        <v>-6625.786728018567</v>
       </c>
     </row>
     <row r="65">
@@ -7206,7 +7206,7 @@
         <v>-6673.96832962963</v>
       </c>
       <c r="G65" t="n">
-        <v>-6684.404071198321</v>
+        <v>-6684.404071198319</v>
       </c>
     </row>
     <row r="66">
@@ -7231,7 +7231,7 @@
         <v>-6616.321117407408</v>
       </c>
       <c r="G66" t="n">
-        <v>-6634.617461697914</v>
+        <v>-6634.617461697915</v>
       </c>
     </row>
     <row r="67">
@@ -7250,13 +7250,13 @@
         <v>-360.60102876</v>
       </c>
       <c r="E67" t="n">
-        <v>-361.1956441695065</v>
+        <v>-361.1956441695064</v>
       </c>
       <c r="F67" t="n">
         <v>-6677.796828888889</v>
       </c>
       <c r="G67" t="n">
-        <v>-6688.80822536123</v>
+        <v>-6688.808225361229</v>
       </c>
     </row>
     <row r="68">
@@ -7306,7 +7306,7 @@
         <v>-6560.272802592593</v>
       </c>
       <c r="G69" t="n">
-        <v>-6578.17141232289</v>
+        <v>-6578.171412322891</v>
       </c>
     </row>
     <row r="70">
@@ -7331,7 +7331,7 @@
         <v>-6707.832794999999</v>
       </c>
       <c r="G70" t="n">
-        <v>-6612.219512127176</v>
+        <v>-6612.219512127175</v>
       </c>
     </row>
     <row r="71">
@@ -7350,13 +7350,13 @@
         <v>-120.17862857</v>
       </c>
       <c r="E71" t="n">
-        <v>-118.7765419063565</v>
+        <v>-118.7765419063564</v>
       </c>
       <c r="F71" t="n">
         <v>-6676.590476111111</v>
       </c>
       <c r="G71" t="n">
-        <v>-6598.69677257536</v>
+        <v>-6598.696772575358</v>
       </c>
     </row>
     <row r="72">
@@ -7475,13 +7475,13 @@
         <v>-116.22590605</v>
       </c>
       <c r="E76" t="n">
-        <v>-114.6355788694451</v>
+        <v>-114.635578869445</v>
       </c>
       <c r="F76" t="n">
         <v>-6456.994780555556</v>
       </c>
       <c r="G76" t="n">
-        <v>-6368.643270524725</v>
+        <v>-6368.643270524724</v>
       </c>
     </row>
     <row r="77">
@@ -7575,13 +7575,13 @@
         <v>-361.44721308</v>
       </c>
       <c r="E80" t="n">
-        <v>-362.4425063569063</v>
+        <v>-362.4425063569064</v>
       </c>
       <c r="F80" t="n">
         <v>-6693.466908888888</v>
       </c>
       <c r="G80" t="n">
-        <v>-6711.898265868635</v>
+        <v>-6711.898265868636</v>
       </c>
     </row>
     <row r="81">
@@ -7600,13 +7600,13 @@
         <v>-354.84919307</v>
       </c>
       <c r="E81" t="n">
-        <v>-355.5500734205528</v>
+        <v>-355.5500734205529</v>
       </c>
       <c r="F81" t="n">
         <v>-6571.281353148149</v>
       </c>
       <c r="G81" t="n">
-        <v>-6584.260618899127</v>
+        <v>-6584.260618899128</v>
       </c>
     </row>
     <row r="82">
@@ -7631,7 +7631,7 @@
         <v>-6488.593758333333</v>
       </c>
       <c r="G82" t="n">
-        <v>-6396.603154013088</v>
+        <v>-6396.603154013086</v>
       </c>
     </row>
     <row r="83">
@@ -7650,13 +7650,13 @@
         <v>-357.00584759</v>
       </c>
       <c r="E83" t="n">
-        <v>-357.2613232444746</v>
+        <v>-357.2613232444747</v>
       </c>
       <c r="F83" t="n">
         <v>-6611.219399814814</v>
       </c>
       <c r="G83" t="n">
-        <v>-6615.950430453233</v>
+        <v>-6615.950430453235</v>
       </c>
     </row>
     <row r="84">
@@ -7881,7 +7881,7 @@
         <v>-6566.855721296296</v>
       </c>
       <c r="G92" t="n">
-        <v>-6577.778125919575</v>
+        <v>-6577.778125919576</v>
       </c>
     </row>
     <row r="93">
@@ -7900,13 +7900,13 @@
         <v>-360.18841782</v>
       </c>
       <c r="E93" t="n">
-        <v>-361.0491658450662</v>
+        <v>-361.0491658450663</v>
       </c>
       <c r="F93" t="n">
         <v>-6670.155885555555</v>
       </c>
       <c r="G93" t="n">
-        <v>-6686.095663797523</v>
+        <v>-6686.095663797524</v>
       </c>
     </row>
     <row r="94">
@@ -8025,13 +8025,13 @@
         <v>-341.07639222</v>
       </c>
       <c r="E98" t="n">
-        <v>-342.1598472246728</v>
+        <v>-342.1598472246727</v>
       </c>
       <c r="F98" t="n">
         <v>-6316.229485555556</v>
       </c>
       <c r="G98" t="n">
-        <v>-6336.29346712357</v>
+        <v>-6336.293467123569</v>
       </c>
     </row>
     <row r="99">
@@ -8050,13 +8050,13 @@
         <v>-355.02670946</v>
       </c>
       <c r="E99" t="n">
-        <v>-355.3027472221835</v>
+        <v>-355.3027472221836</v>
       </c>
       <c r="F99" t="n">
         <v>-6574.568693703704</v>
       </c>
       <c r="G99" t="n">
-        <v>-6579.680504114511</v>
+        <v>-6579.680504114512</v>
       </c>
     </row>
     <row r="100">
@@ -8125,13 +8125,13 @@
         <v>-360.11042278</v>
       </c>
       <c r="E102" t="n">
-        <v>-360.5622151338653</v>
+        <v>-360.5622151338652</v>
       </c>
       <c r="F102" t="n">
         <v>-6668.711532962963</v>
       </c>
       <c r="G102" t="n">
-        <v>-6677.078058034542</v>
+        <v>-6677.078058034541</v>
       </c>
     </row>
     <row r="103">
@@ -8181,7 +8181,7 @@
         <v>-6605.939077407408</v>
       </c>
       <c r="G104" t="n">
-        <v>-6625.976366158628</v>
+        <v>-6625.976366158629</v>
       </c>
     </row>
     <row r="105">
@@ -8281,7 +8281,7 @@
         <v>-6537.778917037037</v>
       </c>
       <c r="G108" t="n">
-        <v>-6556.518335497506</v>
+        <v>-6556.518335497505</v>
       </c>
     </row>
     <row r="109">
@@ -8325,13 +8325,13 @@
         <v>-359.42987083</v>
       </c>
       <c r="E110" t="n">
-        <v>-359.966057808438</v>
+        <v>-359.9660578084381</v>
       </c>
       <c r="F110" t="n">
         <v>-6656.108719074075</v>
       </c>
       <c r="G110" t="n">
-        <v>-6666.038107563666</v>
+        <v>-6666.038107563667</v>
       </c>
     </row>
     <row r="111">
@@ -8350,13 +8350,13 @@
         <v>-357.6263799</v>
       </c>
       <c r="E111" t="n">
-        <v>-358.2640736936894</v>
+        <v>-358.2640736936893</v>
       </c>
       <c r="F111" t="n">
         <v>-6622.710738888889</v>
       </c>
       <c r="G111" t="n">
-        <v>-6634.519883216471</v>
+        <v>-6634.519883216469</v>
       </c>
     </row>
     <row r="112">
@@ -8550,13 +8550,13 @@
         <v>-361.93009182</v>
       </c>
       <c r="E119" t="n">
-        <v>-362.5447081874327</v>
+        <v>-362.5447081874328</v>
       </c>
       <c r="F119" t="n">
         <v>-6702.409107777778</v>
       </c>
       <c r="G119" t="n">
-        <v>-6713.790892359864</v>
+        <v>-6713.790892359866</v>
       </c>
     </row>
     <row r="120">
@@ -8606,7 +8606,7 @@
         <v>-6684.163082222221</v>
       </c>
       <c r="G121" t="n">
-        <v>-6699.393120409601</v>
+        <v>-6699.3931204096</v>
       </c>
     </row>
     <row r="122">
@@ -8625,13 +8625,13 @@
         <v>-353.34259406</v>
       </c>
       <c r="E122" t="n">
-        <v>-354.4589834957868</v>
+        <v>-354.4589834957867</v>
       </c>
       <c r="F122" t="n">
         <v>-6543.381371481482</v>
       </c>
       <c r="G122" t="n">
-        <v>-6564.055249921977</v>
+        <v>-6564.055249921976</v>
       </c>
     </row>
     <row r="123">
@@ -8650,13 +8650,13 @@
         <v>-119.65101334</v>
       </c>
       <c r="E123" t="n">
-        <v>-118.2882935804135</v>
+        <v>-118.2882935804134</v>
       </c>
       <c r="F123" t="n">
         <v>-6647.278518888889</v>
       </c>
       <c r="G123" t="n">
-        <v>-6571.571865578526</v>
+        <v>-6571.571865578524</v>
       </c>
     </row>
     <row r="124">
@@ -8675,13 +8675,13 @@
         <v>-355.70500108</v>
       </c>
       <c r="E124" t="n">
-        <v>-356.6204846106086</v>
+        <v>-356.6204846106085</v>
       </c>
       <c r="F124" t="n">
         <v>-6587.12964962963</v>
       </c>
       <c r="G124" t="n">
-        <v>-6604.083048344603</v>
+        <v>-6604.083048344602</v>
       </c>
     </row>
     <row r="125">
@@ -8756,7 +8756,7 @@
         <v>-6583.545548148149</v>
       </c>
       <c r="G127" t="n">
-        <v>-6584.778144910231</v>
+        <v>-6584.778144910232</v>
       </c>
     </row>
     <row r="128">
@@ -8775,13 +8775,13 @@
         <v>-345.53105924</v>
       </c>
       <c r="E128" t="n">
-        <v>-346.1503939894888</v>
+        <v>-346.1503939894889</v>
       </c>
       <c r="F128" t="n">
         <v>-6398.723319259258</v>
       </c>
       <c r="G128" t="n">
-        <v>-6410.19248128683</v>
+        <v>-6410.192481286831</v>
       </c>
     </row>
     <row r="129">
@@ -8875,13 +8875,13 @@
         <v>-354.95116502</v>
       </c>
       <c r="E132" t="n">
-        <v>-355.3078314255224</v>
+        <v>-355.3078314255225</v>
       </c>
       <c r="F132" t="n">
         <v>-6573.169722592593</v>
       </c>
       <c r="G132" t="n">
-        <v>-6579.774656028192</v>
+        <v>-6579.774656028195</v>
       </c>
     </row>
     <row r="133">
@@ -9006,7 +9006,7 @@
         <v>-6681.986968888889</v>
       </c>
       <c r="G137" t="n">
-        <v>-6691.872579132667</v>
+        <v>-6691.872579132666</v>
       </c>
     </row>
     <row r="138">
@@ -9081,7 +9081,7 @@
         <v>-6645.762168148148</v>
       </c>
       <c r="G140" t="n">
-        <v>-6659.710370103829</v>
+        <v>-6659.71037010383</v>
       </c>
     </row>
     <row r="141">
@@ -9106,7 +9106,7 @@
         <v>-6638.060125555556</v>
       </c>
       <c r="G141" t="n">
-        <v>-6648.973960872424</v>
+        <v>-6648.973960872425</v>
       </c>
     </row>
     <row r="142">
@@ -9125,13 +9125,13 @@
         <v>-361.80382835</v>
       </c>
       <c r="E142" t="n">
-        <v>-362.4930096173427</v>
+        <v>-362.4930096173428</v>
       </c>
       <c r="F142" t="n">
         <v>-6700.070895370371</v>
       </c>
       <c r="G142" t="n">
-        <v>-6712.833511432272</v>
+        <v>-6712.833511432273</v>
       </c>
     </row>
     <row r="143">
@@ -9200,13 +9200,13 @@
         <v>-351.01881719</v>
       </c>
       <c r="E145" t="n">
-        <v>-351.4198490472596</v>
+        <v>-351.4198490472595</v>
       </c>
       <c r="F145" t="n">
         <v>-6500.348466481481</v>
       </c>
       <c r="G145" t="n">
-        <v>-6507.774982356658</v>
+        <v>-6507.774982356657</v>
       </c>
     </row>
     <row r="146">
@@ -9225,7 +9225,7 @@
         <v>-358.16349788</v>
       </c>
       <c r="E146" t="n">
-        <v>-358.6665613937566</v>
+        <v>-358.6665613937567</v>
       </c>
       <c r="F146" t="n">
         <v>-6632.657368148149</v>
@@ -9256,7 +9256,7 @@
         <v>-6654.228626851852</v>
       </c>
       <c r="G147" t="n">
-        <v>-6667.378054038255</v>
+        <v>-6667.378054038256</v>
       </c>
     </row>
     <row r="148">
@@ -9375,13 +9375,13 @@
         <v>-355.84612331</v>
       </c>
       <c r="E152" t="n">
-        <v>-356.3204630376618</v>
+        <v>-356.3204630376619</v>
       </c>
       <c r="F152" t="n">
         <v>-6589.743024259259</v>
       </c>
       <c r="G152" t="n">
-        <v>-6598.527093290033</v>
+        <v>-6598.527093290035</v>
       </c>
     </row>
     <row r="153">
@@ -9500,13 +9500,13 @@
         <v>-355.02933702</v>
       </c>
       <c r="E157" t="n">
-        <v>-355.7403366456918</v>
+        <v>-355.7403366456919</v>
       </c>
       <c r="F157" t="n">
         <v>-6574.617352222223</v>
       </c>
       <c r="G157" t="n">
-        <v>-6587.784011957255</v>
+        <v>-6587.784011957257</v>
       </c>
     </row>
     <row r="158">
@@ -9625,13 +9625,13 @@
         <v>-120.81618523</v>
       </c>
       <c r="E162" t="n">
-        <v>-119.3922289764824</v>
+        <v>-119.3922289764823</v>
       </c>
       <c r="F162" t="n">
         <v>-6712.010290555556</v>
       </c>
       <c r="G162" t="n">
-        <v>-6632.901609804575</v>
+        <v>-6632.901609804573</v>
       </c>
     </row>
     <row r="163">
@@ -9700,13 +9700,13 @@
         <v>-361.14314984</v>
       </c>
       <c r="E165" t="n">
-        <v>-361.4715726320568</v>
+        <v>-361.4715726320567</v>
       </c>
       <c r="F165" t="n">
         <v>-6687.836108148148</v>
       </c>
       <c r="G165" t="n">
-        <v>-6693.918011704755</v>
+        <v>-6693.918011704754</v>
       </c>
     </row>
     <row r="166">
@@ -9950,13 +9950,13 @@
         <v>-353.85161311</v>
       </c>
       <c r="E175" t="n">
-        <v>-354.8096749801531</v>
+        <v>-354.8096749801532</v>
       </c>
       <c r="F175" t="n">
         <v>-6552.807650185186</v>
       </c>
       <c r="G175" t="n">
-        <v>-6570.549536669503</v>
+        <v>-6570.549536669504</v>
       </c>
     </row>
     <row r="176">
@@ -9975,13 +9975,13 @@
         <v>-355.95729424</v>
       </c>
       <c r="E176" t="n">
-        <v>-356.3990742549052</v>
+        <v>-356.3990742549051</v>
       </c>
       <c r="F176" t="n">
         <v>-6591.801745185186</v>
       </c>
       <c r="G176" t="n">
-        <v>-6599.982856572319</v>
+        <v>-6599.982856572318</v>
       </c>
     </row>
     <row r="177">
@@ -10031,7 +10031,7 @@
         <v>-6652.010147222223</v>
       </c>
       <c r="G178" t="n">
-        <v>-6662.959003875354</v>
+        <v>-6662.959003875353</v>
       </c>
     </row>
     <row r="179">
@@ -10075,13 +10075,13 @@
         <v>-361.75752284</v>
       </c>
       <c r="E180" t="n">
-        <v>-362.8406348238956</v>
+        <v>-362.8406348238958</v>
       </c>
       <c r="F180" t="n">
         <v>-6699.213385925926</v>
       </c>
       <c r="G180" t="n">
-        <v>-6719.271015257326</v>
+        <v>-6719.271015257329</v>
       </c>
     </row>
     <row r="181">
@@ -10125,13 +10125,13 @@
         <v>-360.4803276</v>
       </c>
       <c r="E182" t="n">
-        <v>-361.0385676603123</v>
+        <v>-361.0385676603124</v>
       </c>
       <c r="F182" t="n">
         <v>-6675.561622222222</v>
       </c>
       <c r="G182" t="n">
-        <v>-6685.899401116893</v>
+        <v>-6685.899401116895</v>
       </c>
     </row>
     <row r="183">
@@ -10200,13 +10200,13 @@
         <v>-361.8094646</v>
       </c>
       <c r="E185" t="n">
-        <v>-362.6093123624145</v>
+        <v>-362.6093123624146</v>
       </c>
       <c r="F185" t="n">
         <v>-6700.175270370371</v>
       </c>
       <c r="G185" t="n">
-        <v>-6714.98726597064</v>
+        <v>-6714.987265970641</v>
       </c>
     </row>
     <row r="186">
@@ -10275,13 +10275,13 @@
         <v>-355.42074312</v>
       </c>
       <c r="E188" t="n">
-        <v>-355.6160452080033</v>
+        <v>-355.6160452080032</v>
       </c>
       <c r="F188" t="n">
         <v>-6581.865613333333</v>
       </c>
       <c r="G188" t="n">
-        <v>-6585.482318666728</v>
+        <v>-6585.482318666727</v>
       </c>
     </row>
     <row r="189">
@@ -10300,13 +10300,13 @@
         <v>-360.84509004</v>
       </c>
       <c r="E189" t="n">
-        <v>-362.0313305669708</v>
+        <v>-362.0313305669709</v>
       </c>
       <c r="F189" t="n">
         <v>-6682.316482222222</v>
       </c>
       <c r="G189" t="n">
-        <v>-6704.28389938835</v>
+        <v>-6704.283899388351</v>
       </c>
     </row>
     <row r="190">
@@ -10381,7 +10381,7 @@
         <v>-6644.781291296296</v>
       </c>
       <c r="G192" t="n">
-        <v>-6656.364943263693</v>
+        <v>-6656.364943263692</v>
       </c>
     </row>
     <row r="193">
@@ -10431,7 +10431,7 @@
         <v>-6634.44507574074</v>
       </c>
       <c r="G194" t="n">
-        <v>-6641.781069583099</v>
+        <v>-6641.781069583098</v>
       </c>
     </row>
     <row r="195">
@@ -10606,7 +10606,7 @@
         <v>-6569.80165462963</v>
       </c>
       <c r="G201" t="n">
-        <v>-6585.144140085265</v>
+        <v>-6585.144140085267</v>
       </c>
     </row>
     <row r="202">
@@ -10625,13 +10625,13 @@
         <v>-361.95135052</v>
       </c>
       <c r="E202" t="n">
-        <v>-362.7045954409255</v>
+        <v>-362.7045954409256</v>
       </c>
       <c r="F202" t="n">
         <v>-6702.802787407407</v>
       </c>
       <c r="G202" t="n">
-        <v>-6716.751767424546</v>
+        <v>-6716.751767424547</v>
       </c>
     </row>
     <row r="203">
@@ -10650,13 +10650,13 @@
         <v>-361.42887628</v>
       </c>
       <c r="E203" t="n">
-        <v>-362.2394472033257</v>
+        <v>-362.2394472033258</v>
       </c>
       <c r="F203" t="n">
         <v>-6693.127338518519</v>
       </c>
       <c r="G203" t="n">
-        <v>-6708.137911172698</v>
+        <v>-6708.137911172699</v>
       </c>
     </row>
     <row r="204">
@@ -10681,7 +10681,7 @@
         <v>-6635.505766481481</v>
       </c>
       <c r="G204" t="n">
-        <v>-6657.809227660438</v>
+        <v>-6657.809227660437</v>
       </c>
     </row>
     <row r="205">
@@ -10725,13 +10725,13 @@
         <v>-351.84766282</v>
       </c>
       <c r="E206" t="n">
-        <v>-352.4168181358584</v>
+        <v>-352.4168181358583</v>
       </c>
       <c r="F206" t="n">
         <v>-6515.697459629629</v>
       </c>
       <c r="G206" t="n">
-        <v>-6526.237372886266</v>
+        <v>-6526.237372886265</v>
       </c>
     </row>
     <row r="207">
@@ -10806,7 +10806,7 @@
         <v>-6537.100979814814</v>
       </c>
       <c r="G209" t="n">
-        <v>-6553.870597659978</v>
+        <v>-6553.870597659979</v>
       </c>
     </row>
     <row r="210">
@@ -10825,13 +10825,13 @@
         <v>-361.28586924</v>
       </c>
       <c r="E210" t="n">
-        <v>-361.8738031566066</v>
+        <v>-361.8738031566067</v>
       </c>
       <c r="F210" t="n">
         <v>-6690.479060000001</v>
       </c>
       <c r="G210" t="n">
-        <v>-6701.366725122345</v>
+        <v>-6701.366725122346</v>
       </c>
     </row>
     <row r="211">
@@ -10881,7 +10881,7 @@
         <v>-6692.505493148148</v>
       </c>
       <c r="G212" t="n">
-        <v>-6701.429824634325</v>
+        <v>-6701.429824634323</v>
       </c>
     </row>
     <row r="213">
@@ -10906,7 +10906,7 @@
         <v>-6686.634161851852</v>
       </c>
       <c r="G213" t="n">
-        <v>-6706.756038839395</v>
+        <v>-6706.756038839397</v>
       </c>
     </row>
     <row r="214">
@@ -11150,13 +11150,13 @@
         <v>-358.74295443</v>
       </c>
       <c r="E223" t="n">
-        <v>-359.5558116960972</v>
+        <v>-359.5558116960973</v>
       </c>
       <c r="F223" t="n">
         <v>-6643.388045</v>
       </c>
       <c r="G223" t="n">
-        <v>-6658.440957335134</v>
+        <v>-6658.440957335136</v>
       </c>
     </row>
     <row r="224">
@@ -11175,13 +11175,13 @@
         <v>-347.57263539</v>
       </c>
       <c r="E224" t="n">
-        <v>-348.0161888911114</v>
+        <v>-348.0161888911115</v>
       </c>
       <c r="F224" t="n">
         <v>-6436.530285</v>
       </c>
       <c r="G224" t="n">
-        <v>-6444.744238724285</v>
+        <v>-6444.744238724286</v>
       </c>
     </row>
     <row r="225">
@@ -11275,7 +11275,7 @@
         <v>-359.17955389</v>
       </c>
       <c r="E228" t="n">
-        <v>-359.8328371650208</v>
+        <v>-359.8328371650207</v>
       </c>
       <c r="F228" t="n">
         <v>-6651.473220185186</v>
@@ -11300,13 +11300,13 @@
         <v>-350.81393328</v>
       </c>
       <c r="E229" t="n">
-        <v>-351.7649809193231</v>
+        <v>-351.764980919323</v>
       </c>
       <c r="F229" t="n">
         <v>-6496.55432</v>
       </c>
       <c r="G229" t="n">
-        <v>-6514.166313320799</v>
+        <v>-6514.166313320798</v>
       </c>
     </row>
     <row r="230">
@@ -11325,13 +11325,13 @@
         <v>-351.93007156</v>
       </c>
       <c r="E230" t="n">
-        <v>-352.7014553304242</v>
+        <v>-352.7014553304243</v>
       </c>
       <c r="F230" t="n">
         <v>-6517.223547407408</v>
       </c>
       <c r="G230" t="n">
-        <v>-6531.508432044892</v>
+        <v>-6531.508432044893</v>
       </c>
     </row>
     <row r="231">
@@ -11450,13 +11450,13 @@
         <v>-353.00711755</v>
       </c>
       <c r="E235" t="n">
-        <v>-353.7375582547653</v>
+        <v>-353.7375582547654</v>
       </c>
       <c r="F235" t="n">
         <v>-6537.168843518518</v>
       </c>
       <c r="G235" t="n">
-        <v>-6550.695523236394</v>
+        <v>-6550.695523236396</v>
       </c>
     </row>
     <row r="236">
@@ -11481,7 +11481,7 @@
         <v>-6674.416938888889</v>
       </c>
       <c r="G236" t="n">
-        <v>-6683.831487665862</v>
+        <v>-6683.831487665861</v>
       </c>
     </row>
     <row r="237">
@@ -11500,13 +11500,13 @@
         <v>-362.03007744</v>
       </c>
       <c r="E237" t="n">
-        <v>-362.5809621987613</v>
+        <v>-362.5809621987612</v>
       </c>
       <c r="F237" t="n">
         <v>-6704.260693333334</v>
       </c>
       <c r="G237" t="n">
-        <v>-6714.462262940023</v>
+        <v>-6714.462262940022</v>
       </c>
     </row>
     <row r="238">
@@ -11625,13 +11625,13 @@
         <v>-355.05937572</v>
       </c>
       <c r="E242" t="n">
-        <v>-355.6280143380877</v>
+        <v>-355.6280143380878</v>
       </c>
       <c r="F242" t="n">
         <v>-6575.173624444445</v>
       </c>
       <c r="G242" t="n">
-        <v>-6585.703969223846</v>
+        <v>-6585.703969223848</v>
       </c>
     </row>
     <row r="243">
@@ -11650,13 +11650,13 @@
         <v>-357.49335822</v>
       </c>
       <c r="E243" t="n">
-        <v>-357.8607714770735</v>
+        <v>-357.8607714770734</v>
       </c>
       <c r="F243" t="n">
         <v>-6620.247374444444</v>
       </c>
       <c r="G243" t="n">
-        <v>-6627.051323649508</v>
+        <v>-6627.051323649507</v>
       </c>
     </row>
     <row r="244">
@@ -11681,7 +11681,7 @@
         <v>-6613.334075185186</v>
       </c>
       <c r="G244" t="n">
-        <v>-6627.431540857128</v>
+        <v>-6627.431540857127</v>
       </c>
     </row>
     <row r="245">
@@ -11725,13 +11725,13 @@
         <v>-356.44114165</v>
       </c>
       <c r="E246" t="n">
-        <v>-356.9102922643098</v>
+        <v>-356.9102922643097</v>
       </c>
       <c r="F246" t="n">
         <v>-6600.761882407408</v>
       </c>
       <c r="G246" t="n">
-        <v>-6609.449856746477</v>
+        <v>-6609.449856746476</v>
       </c>
     </row>
     <row r="247">
@@ -11806,7 +11806,7 @@
         <v>-6620.793185555556</v>
       </c>
       <c r="G249" t="n">
-        <v>-6633.093107815553</v>
+        <v>-6633.093107815554</v>
       </c>
     </row>
     <row r="250">
@@ -11825,13 +11825,13 @@
         <v>-353.32451516</v>
       </c>
       <c r="E250" t="n">
-        <v>-353.9713952419951</v>
+        <v>-353.9713952419952</v>
       </c>
       <c r="F250" t="n">
         <v>-6543.046577037037</v>
       </c>
       <c r="G250" t="n">
-        <v>-6555.025837814725</v>
+        <v>-6555.025837814726</v>
       </c>
     </row>
     <row r="251">
@@ -11875,13 +11875,13 @@
         <v>-360.79604865</v>
       </c>
       <c r="E252" t="n">
-        <v>-361.7504855629126</v>
+        <v>-361.7504855629127</v>
       </c>
       <c r="F252" t="n">
         <v>-6681.408308333333</v>
       </c>
       <c r="G252" t="n">
-        <v>-6699.083065979863</v>
+        <v>-6699.083065979864</v>
       </c>
     </row>
     <row r="253">
@@ -11975,13 +11975,13 @@
         <v>-362.24209641</v>
       </c>
       <c r="E256" t="n">
-        <v>-362.9653104550669</v>
+        <v>-362.965310455067</v>
       </c>
       <c r="F256" t="n">
         <v>-6708.186970555555</v>
       </c>
       <c r="G256" t="n">
-        <v>-6721.57982324198</v>
+        <v>-6721.579823241981</v>
       </c>
     </row>
     <row r="257">
@@ -12000,13 +12000,13 @@
         <v>-362.12690136</v>
       </c>
       <c r="E257" t="n">
-        <v>-362.8589506181893</v>
+        <v>-362.8589506181894</v>
       </c>
       <c r="F257" t="n">
         <v>-6706.053728888888</v>
       </c>
       <c r="G257" t="n">
-        <v>-6719.610196633136</v>
+        <v>-6719.610196633137</v>
       </c>
     </row>
     <row r="258">
@@ -12075,7 +12075,7 @@
         <v>-356.09538079</v>
       </c>
       <c r="E260" t="n">
-        <v>-356.5208108874987</v>
+        <v>-356.5208108874986</v>
       </c>
       <c r="F260" t="n">
         <v>-6594.358903518518</v>
@@ -12106,7 +12106,7 @@
         <v>-6571.90323537037</v>
       </c>
       <c r="G261" t="n">
-        <v>-6591.497953176244</v>
+        <v>-6591.497953176245</v>
       </c>
     </row>
     <row r="262">
@@ -12200,13 +12200,13 @@
         <v>-352.84399011</v>
       </c>
       <c r="E265" t="n">
-        <v>-353.657758653731</v>
+        <v>-353.6577586537311</v>
       </c>
       <c r="F265" t="n">
         <v>-6534.147965</v>
       </c>
       <c r="G265" t="n">
-        <v>-6549.21775284687</v>
+        <v>-6549.217752846872</v>
       </c>
     </row>
     <row r="266">
@@ -12256,7 +12256,7 @@
         <v>-6596.994348148148</v>
       </c>
       <c r="G267" t="n">
-        <v>-6612.714772690205</v>
+        <v>-6612.714772690206</v>
       </c>
     </row>
     <row r="268">
@@ -12275,13 +12275,13 @@
         <v>-357.80176412</v>
       </c>
       <c r="E268" t="n">
-        <v>-358.5632971150147</v>
+        <v>-358.5632971150148</v>
       </c>
       <c r="F268" t="n">
         <v>-6625.958594814814</v>
       </c>
       <c r="G268" t="n">
-        <v>-6640.061057685459</v>
+        <v>-6640.06105768546</v>
       </c>
     </row>
     <row r="269">
@@ -12375,13 +12375,13 @@
         <v>-351.1397039</v>
       </c>
       <c r="E272" t="n">
-        <v>-351.5548949035723</v>
+        <v>-351.5548949035722</v>
       </c>
       <c r="F272" t="n">
         <v>-6502.587109259259</v>
       </c>
       <c r="G272" t="n">
-        <v>-6510.275831547635</v>
+        <v>-6510.275831547634</v>
       </c>
     </row>
     <row r="273">
@@ -12481,7 +12481,7 @@
         <v>-6670.921905</v>
       </c>
       <c r="G276" t="n">
-        <v>-6587.0340539469</v>
+        <v>-6587.034053946902</v>
       </c>
     </row>
     <row r="277">
@@ -12581,7 +12581,7 @@
         <v>-6609.807077777778</v>
       </c>
       <c r="G280" t="n">
-        <v>-6622.762013573566</v>
+        <v>-6622.762013573567</v>
       </c>
     </row>
     <row r="281">
@@ -12606,7 +12606,7 @@
         <v>-6704.784464444445</v>
       </c>
       <c r="G281" t="n">
-        <v>-6707.802096802973</v>
+        <v>-6707.802096802974</v>
       </c>
     </row>
     <row r="282">
@@ -12681,7 +12681,7 @@
         <v>-6534.955867407408</v>
       </c>
       <c r="G284" t="n">
-        <v>-6549.049555510317</v>
+        <v>-6549.049555510316</v>
       </c>
     </row>
     <row r="285">
@@ -12700,13 +12700,13 @@
         <v>-352.02803305</v>
       </c>
       <c r="E285" t="n">
-        <v>-353.1803663061474</v>
+        <v>-353.1803663061475</v>
       </c>
       <c r="F285" t="n">
         <v>-6519.037649074074</v>
       </c>
       <c r="G285" t="n">
-        <v>-6540.377153817545</v>
+        <v>-6540.377153817546</v>
       </c>
     </row>
     <row r="286">
@@ -12856,7 +12856,7 @@
         <v>-6632.22660962963</v>
       </c>
       <c r="G291" t="n">
-        <v>-6641.362158694111</v>
+        <v>-6641.362158694112</v>
       </c>
     </row>
     <row r="292">
@@ -12875,7 +12875,7 @@
         <v>-357.66600488</v>
       </c>
       <c r="E292" t="n">
-        <v>-358.6945820019931</v>
+        <v>-358.694582001993</v>
       </c>
       <c r="F292" t="n">
         <v>-6623.444534814816</v>
@@ -12900,13 +12900,13 @@
         <v>-354.63088603</v>
       </c>
       <c r="E293" t="n">
-        <v>-354.9583390800384</v>
+        <v>-354.9583390800385</v>
       </c>
       <c r="F293" t="n">
         <v>-6567.238630185185</v>
       </c>
       <c r="G293" t="n">
-        <v>-6573.302575556267</v>
+        <v>-6573.302575556268</v>
       </c>
     </row>
     <row r="294">
@@ -12931,7 +12931,7 @@
         <v>-6525.597906296295</v>
       </c>
       <c r="G294" t="n">
-        <v>-6550.400051800116</v>
+        <v>-6550.400051800115</v>
       </c>
     </row>
     <row r="295">
@@ -12950,13 +12950,13 @@
         <v>-359.75758305</v>
       </c>
       <c r="E295" t="n">
-        <v>-360.0984077714052</v>
+        <v>-360.0984077714051</v>
       </c>
       <c r="F295" t="n">
         <v>-6662.177463888889</v>
       </c>
       <c r="G295" t="n">
-        <v>-6668.4890328038</v>
+        <v>-6668.489032803798</v>
       </c>
     </row>
     <row r="296">
@@ -12975,13 +12975,13 @@
         <v>-350.22577124</v>
       </c>
       <c r="E296" t="n">
-        <v>-350.6741730827524</v>
+        <v>-350.6741730827525</v>
       </c>
       <c r="F296" t="n">
         <v>-6485.66243037037</v>
       </c>
       <c r="G296" t="n">
-        <v>-6493.966168199119</v>
+        <v>-6493.96616819912</v>
       </c>
     </row>
     <row r="297">
@@ -13050,13 +13050,13 @@
         <v>-350.51549445</v>
       </c>
       <c r="E299" t="n">
-        <v>-351.2534837542117</v>
+        <v>-351.2534837542118</v>
       </c>
       <c r="F299" t="n">
         <v>-6491.027675</v>
       </c>
       <c r="G299" t="n">
-        <v>-6504.694143596514</v>
+        <v>-6504.694143596515</v>
       </c>
     </row>
     <row r="300">
@@ -13100,13 +13100,13 @@
         <v>-353.97287117</v>
       </c>
       <c r="E301" t="n">
-        <v>-355.1097066973501</v>
+        <v>-355.10970669735</v>
       </c>
       <c r="F301" t="n">
         <v>-6555.053169814815</v>
       </c>
       <c r="G301" t="n">
-        <v>-6576.105679580557</v>
+        <v>-6576.105679580556</v>
       </c>
     </row>
     <row r="302">
@@ -13206,7 +13206,7 @@
         <v>-6541.424572962963</v>
       </c>
       <c r="G305" t="n">
-        <v>-6558.360387839792</v>
+        <v>-6558.360387839793</v>
       </c>
     </row>
     <row r="306">
@@ -13225,13 +13225,13 @@
         <v>-361.23156137</v>
       </c>
       <c r="E306" t="n">
-        <v>-361.6354721108956</v>
+        <v>-361.6354721108957</v>
       </c>
       <c r="F306" t="n">
         <v>-6689.473358703704</v>
       </c>
       <c r="G306" t="n">
-        <v>-6696.953187238809</v>
+        <v>-6696.95318723881</v>
       </c>
     </row>
     <row r="307">
@@ -13256,7 +13256,7 @@
         <v>-6659.484813703703</v>
       </c>
       <c r="G307" t="n">
-        <v>-6668.733992694743</v>
+        <v>-6668.733992694742</v>
       </c>
     </row>
     <row r="308">
@@ -13275,7 +13275,7 @@
         <v>-353.28122136</v>
       </c>
       <c r="E308" t="n">
-        <v>-354.0044013265373</v>
+        <v>-354.0044013265372</v>
       </c>
       <c r="F308" t="n">
         <v>-6542.24484</v>
@@ -13300,13 +13300,13 @@
         <v>-360.42480412</v>
       </c>
       <c r="E309" t="n">
-        <v>-360.9544412139296</v>
+        <v>-360.9544412139297</v>
       </c>
       <c r="F309" t="n">
         <v>-6674.533409629629</v>
       </c>
       <c r="G309" t="n">
-        <v>-6684.341503961659</v>
+        <v>-6684.34150396166</v>
       </c>
     </row>
     <row r="310">
@@ -13325,7 +13325,7 @@
         <v>-357.49886014</v>
       </c>
       <c r="E310" t="n">
-        <v>-358.0633984979787</v>
+        <v>-358.0633984979788</v>
       </c>
       <c r="F310" t="n">
         <v>-6620.349261851852</v>
@@ -13350,13 +13350,13 @@
         <v>-350.37864314</v>
       </c>
       <c r="E311" t="n">
-        <v>-350.7588349708128</v>
+        <v>-350.7588349708129</v>
       </c>
       <c r="F311" t="n">
         <v>-6488.493391481482</v>
       </c>
       <c r="G311" t="n">
-        <v>-6495.533980940979</v>
+        <v>-6495.53398094098</v>
       </c>
     </row>
     <row r="312">
@@ -13431,7 +13431,7 @@
         <v>-6551.348638148147</v>
       </c>
       <c r="G314" t="n">
-        <v>-6561.44718408936</v>
+        <v>-6561.447184089359</v>
       </c>
     </row>
     <row r="315">
@@ -13506,7 +13506,7 @@
         <v>-6559.433692962963</v>
       </c>
       <c r="G317" t="n">
-        <v>-6585.811806981247</v>
+        <v>-6585.811806981246</v>
       </c>
     </row>
     <row r="318">
@@ -13575,13 +13575,13 @@
         <v>-346.2264032</v>
       </c>
       <c r="E320" t="n">
-        <v>-347.052698979155</v>
+        <v>-347.0526989791551</v>
       </c>
       <c r="F320" t="n">
         <v>-6411.600059259259</v>
       </c>
       <c r="G320" t="n">
-        <v>-6426.901832947316</v>
+        <v>-6426.901832947317</v>
       </c>
     </row>
     <row r="321">
@@ -13631,7 +13631,7 @@
         <v>-6637.364975</v>
       </c>
       <c r="G322" t="n">
-        <v>-6647.00007986562</v>
+        <v>-6647.000079865621</v>
       </c>
     </row>
     <row r="323">
@@ -13650,13 +13650,13 @@
         <v>-354.89617512</v>
       </c>
       <c r="E323" t="n">
-        <v>-355.7349024639802</v>
+        <v>-355.7349024639801</v>
       </c>
       <c r="F323" t="n">
         <v>-6572.151391111111</v>
       </c>
       <c r="G323" t="n">
-        <v>-6587.683378962596</v>
+        <v>-6587.683378962594</v>
       </c>
     </row>
     <row r="324">
@@ -13800,13 +13800,13 @@
         <v>-357.72310762</v>
       </c>
       <c r="E329" t="n">
-        <v>-358.2968258042002</v>
+        <v>-358.2968258042003</v>
       </c>
       <c r="F329" t="n">
         <v>-6624.501992962963</v>
       </c>
       <c r="G329" t="n">
-        <v>-6635.126403781486</v>
+        <v>-6635.126403781487</v>
       </c>
     </row>
     <row r="330">
@@ -13831,7 +13831,7 @@
         <v>-6650.087916666667</v>
       </c>
       <c r="G330" t="n">
-        <v>-6575.918062691559</v>
+        <v>-6575.918062691557</v>
       </c>
     </row>
     <row r="331">
@@ -13875,7 +13875,7 @@
         <v>-354.90901634</v>
       </c>
       <c r="E332" t="n">
-        <v>-355.4657959148538</v>
+        <v>-355.4657959148539</v>
       </c>
       <c r="F332" t="n">
         <v>-6572.389191481481</v>
@@ -13925,7 +13925,7 @@
         <v>-361.15305938</v>
       </c>
       <c r="E334" t="n">
-        <v>-362.0993436920822</v>
+        <v>-362.0993436920823</v>
       </c>
       <c r="F334" t="n">
         <v>-6688.019618148148</v>
@@ -14031,7 +14031,7 @@
         <v>-6682.972284444444</v>
       </c>
       <c r="G338" t="n">
-        <v>-6588.91433729979</v>
+        <v>-6588.914337299789</v>
       </c>
     </row>
     <row r="339">
@@ -14100,13 +14100,13 @@
         <v>-360.55934518</v>
       </c>
       <c r="E341" t="n">
-        <v>-361.3511842749221</v>
+        <v>-361.351184274922</v>
       </c>
       <c r="F341" t="n">
         <v>-6677.024910740741</v>
       </c>
       <c r="G341" t="n">
-        <v>-6691.688597683743</v>
+        <v>-6691.688597683742</v>
       </c>
     </row>
     <row r="342">
@@ -14131,7 +14131,7 @@
         <v>-6570.319130000001</v>
       </c>
       <c r="G342" t="n">
-        <v>-6574.317679649605</v>
+        <v>-6574.317679649607</v>
       </c>
     </row>
     <row r="343">
@@ -14250,13 +14250,13 @@
         <v>-351.57729135</v>
       </c>
       <c r="E347" t="n">
-        <v>-352.0236947117094</v>
+        <v>-352.0236947117093</v>
       </c>
       <c r="F347" t="n">
         <v>-6510.690580555556</v>
       </c>
       <c r="G347" t="n">
-        <v>-6518.9573094761</v>
+        <v>-6518.957309476099</v>
       </c>
     </row>
     <row r="348">
@@ -14356,7 +14356,7 @@
         <v>-6620.886794814815</v>
       </c>
       <c r="G351" t="n">
-        <v>-6629.589648267512</v>
+        <v>-6629.589648267511</v>
       </c>
     </row>
     <row r="352">
@@ -14400,13 +14400,13 @@
         <v>-345.9256201</v>
       </c>
       <c r="E353" t="n">
-        <v>-348.2516228785119</v>
+        <v>-348.251622878512</v>
       </c>
       <c r="F353" t="n">
         <v>-6406.030001851852</v>
       </c>
       <c r="G353" t="n">
-        <v>-6449.10412737985</v>
+        <v>-6449.104127379851</v>
       </c>
     </row>
     <row r="354">
@@ -14531,7 +14531,7 @@
         <v>-6522.63607</v>
       </c>
       <c r="G358" t="n">
-        <v>-6538.186215130629</v>
+        <v>-6538.186215130628</v>
       </c>
     </row>
     <row r="359">
@@ -14625,13 +14625,13 @@
         <v>-351.70914765</v>
       </c>
       <c r="E362" t="n">
-        <v>-352.2166593879019</v>
+        <v>-352.2166593879018</v>
       </c>
       <c r="F362" t="n">
         <v>-6513.132363888889</v>
       </c>
       <c r="G362" t="n">
-        <v>-6522.53072940559</v>
+        <v>-6522.530729405589</v>
       </c>
     </row>
     <row r="363">
@@ -14700,7 +14700,7 @@
         <v>-351.71595871</v>
       </c>
       <c r="E365" t="n">
-        <v>-352.9310962696776</v>
+        <v>-352.9310962696775</v>
       </c>
       <c r="F365" t="n">
         <v>-6513.258494629629</v>
@@ -14756,7 +14756,7 @@
         <v>-6534.357268333333</v>
       </c>
       <c r="G367" t="n">
-        <v>-6449.274986802218</v>
+        <v>-6449.274986802217</v>
       </c>
     </row>
     <row r="368">
@@ -14825,13 +14825,13 @@
         <v>-358.48149619</v>
       </c>
       <c r="E370" t="n">
-        <v>-359.4384914075447</v>
+        <v>-359.4384914075446</v>
       </c>
       <c r="F370" t="n">
         <v>-6638.546225740741</v>
       </c>
       <c r="G370" t="n">
-        <v>-6656.268359398976</v>
+        <v>-6656.268359398975</v>
       </c>
     </row>
     <row r="371">
@@ -14856,7 +14856,7 @@
         <v>-6609.262531111111</v>
       </c>
       <c r="G371" t="n">
-        <v>-6621.080377312568</v>
+        <v>-6621.080377312569</v>
       </c>
     </row>
     <row r="372">
@@ -14875,13 +14875,13 @@
         <v>-361.46311527</v>
       </c>
       <c r="E372" t="n">
-        <v>-362.0407418699694</v>
+        <v>-362.0407418699695</v>
       </c>
       <c r="F372" t="n">
         <v>-6693.761393888889</v>
       </c>
       <c r="G372" t="n">
-        <v>-6704.458182777212</v>
+        <v>-6704.458182777213</v>
       </c>
     </row>
     <row r="373">
@@ -14900,13 +14900,13 @@
         <v>-357.56314494</v>
       </c>
       <c r="E373" t="n">
-        <v>-358.2453339305915</v>
+        <v>-358.2453339305914</v>
       </c>
       <c r="F373" t="n">
         <v>-6621.53972111111</v>
       </c>
       <c r="G373" t="n">
-        <v>-6634.172850566509</v>
+        <v>-6634.172850566508</v>
       </c>
     </row>
     <row r="374">
@@ -15000,13 +15000,13 @@
         <v>-356.03579902</v>
       </c>
       <c r="E377" t="n">
-        <v>-356.6442338597731</v>
+        <v>-356.6442338597732</v>
       </c>
       <c r="F377" t="n">
         <v>-6593.255537407408</v>
       </c>
       <c r="G377" t="n">
-        <v>-6604.522849255059</v>
+        <v>-6604.52284925506</v>
       </c>
     </row>
     <row r="378">
@@ -15025,13 +15025,13 @@
         <v>-355.58127238</v>
       </c>
       <c r="E378" t="n">
-        <v>-356.2226701892484</v>
+        <v>-356.2226701892483</v>
       </c>
       <c r="F378" t="n">
         <v>-6584.838377407407</v>
       </c>
       <c r="G378" t="n">
-        <v>-6596.716114615711</v>
+        <v>-6596.71611461571</v>
       </c>
     </row>
     <row r="379">
@@ -15050,13 +15050,13 @@
         <v>-356.89229544</v>
       </c>
       <c r="E379" t="n">
-        <v>-357.8643088736014</v>
+        <v>-357.8643088736015</v>
       </c>
       <c r="F379" t="n">
         <v>-6609.116582222223</v>
       </c>
       <c r="G379" t="n">
-        <v>-6627.116830992619</v>
+        <v>-6627.116830992621</v>
       </c>
     </row>
     <row r="380">
@@ -15100,13 +15100,13 @@
         <v>-352.54310634</v>
       </c>
       <c r="E381" t="n">
-        <v>-353.1875919253454</v>
+        <v>-353.1875919253455</v>
       </c>
       <c r="F381" t="n">
         <v>-6528.576043333333</v>
       </c>
       <c r="G381" t="n">
-        <v>-6540.51096158047</v>
+        <v>-6540.510961580472</v>
       </c>
     </row>
     <row r="382">
@@ -15125,13 +15125,13 @@
         <v>-355.15466457</v>
       </c>
       <c r="E382" t="n">
-        <v>-355.6967376232911</v>
+        <v>-355.6967376232912</v>
       </c>
       <c r="F382" t="n">
         <v>-6576.938232777778</v>
       </c>
       <c r="G382" t="n">
-        <v>-6586.976622653539</v>
+        <v>-6586.976622653541</v>
       </c>
     </row>
     <row r="383">
@@ -15156,7 +15156,7 @@
         <v>-6677.334064259259</v>
       </c>
       <c r="G383" t="n">
-        <v>-6690.6464724682</v>
+        <v>-6690.646472468199</v>
       </c>
     </row>
     <row r="384">
@@ -15175,13 +15175,13 @@
         <v>-360.53356462</v>
       </c>
       <c r="E384" t="n">
-        <v>-361.3516139175249</v>
+        <v>-361.351613917525</v>
       </c>
       <c r="F384" t="n">
         <v>-6676.547492962964</v>
       </c>
       <c r="G384" t="n">
-        <v>-6691.696554028239</v>
+        <v>-6691.696554028242</v>
       </c>
     </row>
     <row r="385">
@@ -15250,13 +15250,13 @@
         <v>-358.36094708</v>
       </c>
       <c r="E387" t="n">
-        <v>-358.9080266219611</v>
+        <v>-358.908026621961</v>
       </c>
       <c r="F387" t="n">
         <v>-6636.313834814815</v>
       </c>
       <c r="G387" t="n">
-        <v>-6646.444937443724</v>
+        <v>-6646.444937443723</v>
       </c>
     </row>
     <row r="388">
@@ -15400,13 +15400,13 @@
         <v>-356.78537083</v>
       </c>
       <c r="E393" t="n">
-        <v>-357.5303996465364</v>
+        <v>-357.5303996465365</v>
       </c>
       <c r="F393" t="n">
         <v>-6607.136496851851</v>
       </c>
       <c r="G393" t="n">
-        <v>-6620.93332678771</v>
+        <v>-6620.933326787712</v>
       </c>
     </row>
     <row r="394">
@@ -15425,13 +15425,13 @@
         <v>-352.6326487</v>
       </c>
       <c r="E394" t="n">
-        <v>-353.1643687411953</v>
+        <v>-353.1643687411954</v>
       </c>
       <c r="F394" t="n">
         <v>-6530.234235185186</v>
       </c>
       <c r="G394" t="n">
-        <v>-6540.080902614729</v>
+        <v>-6540.08090261473</v>
       </c>
     </row>
     <row r="395">
@@ -15450,13 +15450,13 @@
         <v>-354.78044547</v>
       </c>
       <c r="E395" t="n">
-        <v>-355.3656172479366</v>
+        <v>-355.3656172479367</v>
       </c>
       <c r="F395" t="n">
         <v>-6570.008249444445</v>
       </c>
       <c r="G395" t="n">
-        <v>-6580.844763850678</v>
+        <v>-6580.844763850679</v>
       </c>
     </row>
     <row r="396">
@@ -15475,13 +15475,13 @@
         <v>-120.39544137</v>
       </c>
       <c r="E396" t="n">
-        <v>-118.95358022771</v>
+        <v>-118.9535802277099</v>
       </c>
       <c r="F396" t="n">
         <v>-6688.635631666667</v>
       </c>
       <c r="G396" t="n">
-        <v>-6608.532234872776</v>
+        <v>-6608.532234872775</v>
       </c>
     </row>
     <row r="397">
@@ -15550,7 +15550,7 @@
         <v>-358.11918396</v>
       </c>
       <c r="E399" t="n">
-        <v>-359.1009223146429</v>
+        <v>-359.100922314643</v>
       </c>
       <c r="F399" t="n">
         <v>-6631.83674</v>
@@ -15581,7 +15581,7 @@
         <v>-6696.198331666667</v>
       </c>
       <c r="G400" t="n">
-        <v>-6618.871860849733</v>
+        <v>-6618.871860849732</v>
       </c>
     </row>
     <row r="401">
@@ -15625,13 +15625,13 @@
         <v>-361.5954513</v>
       </c>
       <c r="E402" t="n">
-        <v>-362.3034023498541</v>
+        <v>-362.303402349854</v>
       </c>
       <c r="F402" t="n">
         <v>-6696.21206111111</v>
       </c>
       <c r="G402" t="n">
-        <v>-6709.322265738038</v>
+        <v>-6709.322265738037</v>
       </c>
     </row>
     <row r="403">
@@ -15806,7 +15806,7 @@
         <v>-6628.159470000001</v>
       </c>
       <c r="G409" t="n">
-        <v>-6641.457829677268</v>
+        <v>-6641.457829677269</v>
       </c>
     </row>
     <row r="410">
@@ -15906,7 +15906,7 @@
         <v>-6681.38082537037</v>
       </c>
       <c r="G413" t="n">
-        <v>-6691.01369088667</v>
+        <v>-6691.013690886671</v>
       </c>
     </row>
     <row r="414">
@@ -16006,7 +16006,7 @@
         <v>-6611.819898148148</v>
       </c>
       <c r="G417" t="n">
-        <v>-6621.639139103058</v>
+        <v>-6621.639139103059</v>
       </c>
     </row>
     <row r="418">
@@ -16231,7 +16231,7 @@
         <v>-6670.28853462963</v>
       </c>
       <c r="G426" t="n">
-        <v>-6684.890313132214</v>
+        <v>-6684.890313132216</v>
       </c>
     </row>
     <row r="427">
@@ -16350,13 +16350,13 @@
         <v>-358.93973384</v>
       </c>
       <c r="E431" t="n">
-        <v>-359.4798432619027</v>
+        <v>-359.4798432619026</v>
       </c>
       <c r="F431" t="n">
         <v>-6647.032108148148</v>
       </c>
       <c r="G431" t="n">
-        <v>-6657.03413447968</v>
+        <v>-6657.034134479678</v>
       </c>
     </row>
     <row r="432">
@@ -16475,13 +16475,13 @@
         <v>-357.69558866</v>
       </c>
       <c r="E436" t="n">
-        <v>-358.0538041875595</v>
+        <v>-358.0538041875594</v>
       </c>
       <c r="F436" t="n">
         <v>-6623.992382592593</v>
       </c>
       <c r="G436" t="n">
-        <v>-6630.626003473324</v>
+        <v>-6630.626003473321</v>
       </c>
     </row>
     <row r="437">
@@ -16506,7 +16506,7 @@
         <v>-6643.085549814815</v>
       </c>
       <c r="G437" t="n">
-        <v>-6652.354452480963</v>
+        <v>-6652.354452480962</v>
       </c>
     </row>
     <row r="438">
@@ -16525,7 +16525,7 @@
         <v>-359.04426592</v>
       </c>
       <c r="E438" t="n">
-        <v>-359.8001724172462</v>
+        <v>-359.8001724172461</v>
       </c>
       <c r="F438" t="n">
         <v>-6648.967887407407</v>
@@ -16600,13 +16600,13 @@
         <v>-359.78366956</v>
       </c>
       <c r="E441" t="n">
-        <v>-360.3945006059554</v>
+        <v>-360.3945006059553</v>
       </c>
       <c r="F441" t="n">
         <v>-6662.660547407408</v>
       </c>
       <c r="G441" t="n">
-        <v>-6673.972233443618</v>
+        <v>-6673.972233443616</v>
       </c>
     </row>
     <row r="442">
@@ -16631,7 +16631,7 @@
         <v>-6684.637775185185</v>
       </c>
       <c r="G442" t="n">
-        <v>-6698.137836580998</v>
+        <v>-6698.137836580997</v>
       </c>
     </row>
     <row r="443">
@@ -16650,13 +16650,13 @@
         <v>-361.88771205</v>
       </c>
       <c r="E443" t="n">
-        <v>-362.8785965142578</v>
+        <v>-362.8785965142577</v>
       </c>
       <c r="F443" t="n">
         <v>-6701.624297222223</v>
       </c>
       <c r="G443" t="n">
-        <v>-6719.974009523292</v>
+        <v>-6719.974009523291</v>
       </c>
     </row>
     <row r="444">
@@ -16800,13 +16800,13 @@
         <v>-358.52847554</v>
       </c>
       <c r="E449" t="n">
-        <v>-359.0495285917405</v>
+        <v>-359.0495285917406</v>
       </c>
       <c r="F449" t="n">
         <v>-6639.416213703704</v>
       </c>
       <c r="G449" t="n">
-        <v>-6649.065344291491</v>
+        <v>-6649.065344291494</v>
       </c>
     </row>
     <row r="450">
@@ -16850,7 +16850,7 @@
         <v>-356.35511839</v>
       </c>
       <c r="E451" t="n">
-        <v>-357.0287886510417</v>
+        <v>-357.0287886510416</v>
       </c>
       <c r="F451" t="n">
         <v>-6599.168859074073</v>
@@ -16906,7 +16906,7 @@
         <v>-6604.08564</v>
       </c>
       <c r="G453" t="n">
-        <v>-6528.424987000352</v>
+        <v>-6528.424987000351</v>
       </c>
     </row>
     <row r="454">
@@ -16975,13 +16975,13 @@
         <v>-362.22169785</v>
       </c>
       <c r="E456" t="n">
-        <v>-362.9769545333174</v>
+        <v>-362.9769545333175</v>
       </c>
       <c r="F456" t="n">
         <v>-6707.809219444444</v>
       </c>
       <c r="G456" t="n">
-        <v>-6721.795454320693</v>
+        <v>-6721.795454320694</v>
       </c>
     </row>
     <row r="457">
@@ -17000,13 +17000,13 @@
         <v>-360.06069404</v>
       </c>
       <c r="E457" t="n">
-        <v>-360.9865494715219</v>
+        <v>-360.986549471522</v>
       </c>
       <c r="F457" t="n">
         <v>-6667.79063037037</v>
       </c>
       <c r="G457" t="n">
-        <v>-6684.93610132448</v>
+        <v>-6684.936101324482</v>
       </c>
     </row>
     <row r="458">
@@ -17200,13 +17200,13 @@
         <v>-360.47226347</v>
       </c>
       <c r="E465" t="n">
-        <v>-361.193807140387</v>
+        <v>-361.1938071403871</v>
       </c>
       <c r="F465" t="n">
         <v>-6675.412286481481</v>
       </c>
       <c r="G465" t="n">
-        <v>-6688.774206303463</v>
+        <v>-6688.774206303464</v>
       </c>
     </row>
     <row r="466">
@@ -17250,13 +17250,13 @@
         <v>-359.80939502</v>
       </c>
       <c r="E467" t="n">
-        <v>-360.5452778668381</v>
+        <v>-360.545277866838</v>
       </c>
       <c r="F467" t="n">
         <v>-6663.136944814814</v>
       </c>
       <c r="G467" t="n">
-        <v>-6676.764404941446</v>
+        <v>-6676.764404941445</v>
       </c>
     </row>
     <row r="468">
@@ -17275,13 +17275,13 @@
         <v>-353.72261577</v>
       </c>
       <c r="E468" t="n">
-        <v>-354.2951746750014</v>
+        <v>-354.2951746750012</v>
       </c>
       <c r="F468" t="n">
         <v>-6550.418810555556</v>
       </c>
       <c r="G468" t="n">
-        <v>-6561.021753240766</v>
+        <v>-6561.021753240763</v>
       </c>
     </row>
     <row r="469">
@@ -17356,7 +17356,7 @@
         <v>-6639.702792777778</v>
       </c>
       <c r="G471" t="n">
-        <v>-6653.5653706857</v>
+        <v>-6653.565370685701</v>
       </c>
     </row>
     <row r="472">
@@ -17481,7 +17481,7 @@
         <v>-6552.421909814815</v>
       </c>
       <c r="G476" t="n">
-        <v>-6573.611593129461</v>
+        <v>-6573.611593129459</v>
       </c>
     </row>
     <row r="477">
@@ -17550,13 +17550,13 @@
         <v>-365.41040556</v>
       </c>
       <c r="E479" t="n">
-        <v>-365.9359184267609</v>
+        <v>-365.935918426761</v>
       </c>
       <c r="F479" t="n">
         <v>-6766.859362222223</v>
       </c>
       <c r="G479" t="n">
-        <v>-6776.591081977053</v>
+        <v>-6776.591081977054</v>
       </c>
     </row>
     <row r="480">
@@ -17656,7 +17656,7 @@
         <v>-6830.977800555555</v>
       </c>
       <c r="G483" t="n">
-        <v>-6744.355251599951</v>
+        <v>-6744.35525159995</v>
       </c>
     </row>
     <row r="484">
@@ -17681,7 +17681,7 @@
         <v>-6817.374236111111</v>
       </c>
       <c r="G484" t="n">
-        <v>-6736.728551761951</v>
+        <v>-6736.728551761949</v>
       </c>
     </row>
     <row r="485">
@@ -17700,13 +17700,13 @@
         <v>-363.71967731</v>
       </c>
       <c r="E485" t="n">
-        <v>-364.1574006677397</v>
+        <v>-364.1574006677396</v>
       </c>
       <c r="F485" t="n">
         <v>-6735.549579814815</v>
       </c>
       <c r="G485" t="n">
-        <v>-6743.655567921105</v>
+        <v>-6743.655567921104</v>
       </c>
     </row>
     <row r="486">
@@ -17731,7 +17731,7 @@
         <v>-6755.194235555556</v>
       </c>
       <c r="G486" t="n">
-        <v>-6775.624343038236</v>
+        <v>-6775.624343038235</v>
       </c>
     </row>
     <row r="487">
@@ -17850,13 +17850,13 @@
         <v>-363.27423588</v>
       </c>
       <c r="E491" t="n">
-        <v>-363.7037866684512</v>
+        <v>-363.7037866684511</v>
       </c>
       <c r="F491" t="n">
         <v>-6727.300664444444</v>
       </c>
       <c r="G491" t="n">
-        <v>-6735.255308675022</v>
+        <v>-6735.255308675021</v>
       </c>
     </row>
     <row r="492">
@@ -17981,7 +17981,7 @@
         <v>-6736.377025555556</v>
       </c>
       <c r="G496" t="n">
-        <v>-6649.800958320582</v>
+        <v>-6649.800958320581</v>
       </c>
     </row>
     <row r="497">
@@ -18006,7 +18006,7 @@
         <v>-6877.485633518519</v>
       </c>
       <c r="G497" t="n">
-        <v>-6890.417189967166</v>
+        <v>-6890.417189967165</v>
       </c>
     </row>
     <row r="498">
@@ -18031,7 +18031,7 @@
         <v>-6853.988946111112</v>
       </c>
       <c r="G498" t="n">
-        <v>-6771.977088487429</v>
+        <v>-6771.977088487427</v>
       </c>
     </row>
     <row r="499">
@@ -18100,7 +18100,7 @@
         <v>-366.59658401</v>
       </c>
       <c r="E501" t="n">
-        <v>-367.0155567412464</v>
+        <v>-367.0155567412465</v>
       </c>
       <c r="F501" t="n">
         <v>-6788.825629814814</v>
@@ -18125,13 +18125,13 @@
         <v>-363.26320365</v>
       </c>
       <c r="E502" t="n">
-        <v>-363.8728044837539</v>
+        <v>-363.8728044837538</v>
       </c>
       <c r="F502" t="n">
         <v>-6727.096363888889</v>
       </c>
       <c r="G502" t="n">
-        <v>-6738.385268217665</v>
+        <v>-6738.385268217664</v>
       </c>
     </row>
     <row r="503">
@@ -18206,7 +18206,7 @@
         <v>-6761.878717777778</v>
       </c>
       <c r="G505" t="n">
-        <v>-6681.380830419409</v>
+        <v>-6681.380830419411</v>
       </c>
     </row>
     <row r="506">
@@ -18300,13 +18300,13 @@
         <v>-363.60867981</v>
       </c>
       <c r="E509" t="n">
-        <v>-364.2785504299717</v>
+        <v>-364.2785504299716</v>
       </c>
       <c r="F509" t="n">
         <v>-6733.494070555555</v>
       </c>
       <c r="G509" t="n">
-        <v>-6745.899082036513</v>
+        <v>-6745.899082036512</v>
       </c>
     </row>
     <row r="510">
@@ -18356,7 +18356,7 @@
         <v>-6752.294239444444</v>
       </c>
       <c r="G511" t="n">
-        <v>-6668.374120315819</v>
+        <v>-6668.374120315817</v>
       </c>
     </row>
     <row r="512">
@@ -18400,13 +18400,13 @@
         <v>-364.23859016</v>
       </c>
       <c r="E513" t="n">
-        <v>-365.2824001069428</v>
+        <v>-365.2824001069426</v>
       </c>
       <c r="F513" t="n">
         <v>-6745.159077037038</v>
       </c>
       <c r="G513" t="n">
-        <v>-6764.48889086931</v>
+        <v>-6764.488890869308</v>
       </c>
     </row>
     <row r="514">
@@ -18431,7 +18431,7 @@
         <v>-6733.671805000001</v>
       </c>
       <c r="G514" t="n">
-        <v>-6654.903801742341</v>
+        <v>-6654.903801742339</v>
       </c>
     </row>
     <row r="515">
@@ -18450,13 +18450,13 @@
         <v>-362.78238625</v>
       </c>
       <c r="E515" t="n">
-        <v>-364.0321914582211</v>
+        <v>-364.032191458221</v>
       </c>
       <c r="F515" t="n">
         <v>-6718.192337962962</v>
       </c>
       <c r="G515" t="n">
-        <v>-6741.336878855946</v>
+        <v>-6741.336878855944</v>
       </c>
     </row>
     <row r="516">
@@ -18525,13 +18525,13 @@
         <v>-121.56966149</v>
       </c>
       <c r="E518" t="n">
-        <v>-120.0861575655171</v>
+        <v>-120.086157565517</v>
       </c>
       <c r="F518" t="n">
         <v>-6753.870082777777</v>
       </c>
       <c r="G518" t="n">
-        <v>-6671.453198084281</v>
+        <v>-6671.453198084279</v>
       </c>
     </row>
     <row r="519">
@@ -18550,13 +18550,13 @@
         <v>-362.51402626</v>
       </c>
       <c r="E519" t="n">
-        <v>-362.7864180475962</v>
+        <v>-362.7864180475963</v>
       </c>
       <c r="F519" t="n">
         <v>-6713.222708518518</v>
       </c>
       <c r="G519" t="n">
-        <v>-6718.267000881412</v>
+        <v>-6718.267000881413</v>
       </c>
     </row>
     <row r="520">
@@ -18581,7 +18581,7 @@
         <v>-6805.989281666666</v>
       </c>
       <c r="G520" t="n">
-        <v>-6722.222198552364</v>
+        <v>-6722.222198552362</v>
       </c>
     </row>
     <row r="521">
@@ -18600,7 +18600,7 @@
         <v>-362.89913261</v>
       </c>
       <c r="E521" t="n">
-        <v>-363.7534805722506</v>
+        <v>-363.7534805722507</v>
       </c>
       <c r="F521" t="n">
         <v>-6720.354307592592</v>
@@ -18631,7 +18631,7 @@
         <v>-6739.580045</v>
       </c>
       <c r="G522" t="n">
-        <v>-6663.73825657677</v>
+        <v>-6663.738256576772</v>
       </c>
     </row>
     <row r="523">
@@ -18706,7 +18706,7 @@
         <v>-6798.027550740741</v>
       </c>
       <c r="G525" t="n">
-        <v>-6808.683305302825</v>
+        <v>-6808.683305302823</v>
       </c>
     </row>
     <row r="526">
@@ -18750,13 +18750,13 @@
         <v>-368.52269109</v>
       </c>
       <c r="E527" t="n">
-        <v>-369.0974262619833</v>
+        <v>-369.0974262619834</v>
       </c>
       <c r="F527" t="n">
         <v>-6824.494279444445</v>
       </c>
       <c r="G527" t="n">
-        <v>-6835.137523370062</v>
+        <v>-6835.137523370063</v>
       </c>
     </row>
     <row r="528">
@@ -18775,13 +18775,13 @@
         <v>-363.87208615</v>
       </c>
       <c r="E528" t="n">
-        <v>-364.7862484752382</v>
+        <v>-364.786248475238</v>
       </c>
       <c r="F528" t="n">
         <v>-6738.371965740741</v>
       </c>
       <c r="G528" t="n">
-        <v>-6755.300897689595</v>
+        <v>-6755.300897689594</v>
       </c>
     </row>
     <row r="529">
@@ -18956,7 +18956,7 @@
         <v>-6736.367434074075</v>
       </c>
       <c r="G535" t="n">
-        <v>-6758.193323677006</v>
+        <v>-6758.193323677008</v>
       </c>
     </row>
     <row r="536">
@@ -19081,7 +19081,7 @@
         <v>-6770.507091481481</v>
       </c>
       <c r="G540" t="n">
-        <v>-6788.586479912388</v>
+        <v>-6788.586479912389</v>
       </c>
     </row>
     <row r="541">
@@ -19106,7 +19106,7 @@
         <v>-6796.189723888889</v>
       </c>
       <c r="G541" t="n">
-        <v>-6724.75442895241</v>
+        <v>-6724.754428952408</v>
       </c>
     </row>
     <row r="542">
@@ -19156,7 +19156,7 @@
         <v>-6745.408045925927</v>
       </c>
       <c r="G543" t="n">
-        <v>-6760.866357015711</v>
+        <v>-6760.866357015712</v>
       </c>
     </row>
     <row r="544">
@@ -19256,7 +19256,7 @@
         <v>-6837.662044259259</v>
       </c>
       <c r="G547" t="n">
-        <v>-6855.468410160176</v>
+        <v>-6855.468410160175</v>
       </c>
     </row>
     <row r="548">
@@ -19281,7 +19281,7 @@
         <v>-6880.462152222222</v>
       </c>
       <c r="G548" t="n">
-        <v>-6784.01760785439</v>
+        <v>-6784.017607854392</v>
       </c>
     </row>
     <row r="549">
@@ -19300,13 +19300,13 @@
         <v>-363.24694169</v>
       </c>
       <c r="E549" t="n">
-        <v>-363.756101604927</v>
+        <v>-363.7561016049271</v>
       </c>
       <c r="F549" t="n">
         <v>-6726.795216481481</v>
       </c>
       <c r="G549" t="n">
-        <v>-6736.224103794945</v>
+        <v>-6736.224103794946</v>
       </c>
     </row>
     <row r="550">
@@ -19325,13 +19325,13 @@
         <v>-366.62790669</v>
       </c>
       <c r="E550" t="n">
-        <v>-367.6967898109817</v>
+        <v>-367.6967898109816</v>
       </c>
       <c r="F550" t="n">
         <v>-6789.405679444444</v>
       </c>
       <c r="G550" t="n">
-        <v>-6809.199811314475</v>
+        <v>-6809.199811314474</v>
       </c>
     </row>
     <row r="551">
@@ -19450,13 +19450,13 @@
         <v>-363.30853792</v>
       </c>
       <c r="E555" t="n">
-        <v>-363.8907837506134</v>
+        <v>-363.8907837506135</v>
       </c>
       <c r="F555" t="n">
         <v>-6727.935887407407</v>
       </c>
       <c r="G555" t="n">
-        <v>-6738.718217603951</v>
+        <v>-6738.718217603953</v>
       </c>
     </row>
     <row r="556">
@@ -19481,7 +19481,7 @@
         <v>-6752.315878148149</v>
       </c>
       <c r="G556" t="n">
-        <v>-6772.018622894653</v>
+        <v>-6772.018622894654</v>
       </c>
     </row>
     <row r="557">
@@ -19506,7 +19506,7 @@
         <v>-6769.881743888889</v>
       </c>
       <c r="G557" t="n">
-        <v>-6687.283547920148</v>
+        <v>-6687.283547920146</v>
       </c>
     </row>
     <row r="558">
@@ -19556,7 +19556,7 @@
         <v>-6754.827330740741</v>
       </c>
       <c r="G559" t="n">
-        <v>-6765.260329408064</v>
+        <v>-6765.260329408063</v>
       </c>
     </row>
     <row r="560">
@@ -19631,7 +19631,7 @@
         <v>-6719.568811666667</v>
       </c>
       <c r="G562" t="n">
-        <v>-6735.236221604626</v>
+        <v>-6735.236221604625</v>
       </c>
     </row>
     <row r="563">
@@ -19675,13 +19675,13 @@
         <v>-364.09723483</v>
       </c>
       <c r="E564" t="n">
-        <v>-364.755886928851</v>
+        <v>-364.7558869288509</v>
       </c>
       <c r="F564" t="n">
         <v>-6742.54138574074</v>
       </c>
       <c r="G564" t="n">
-        <v>-6754.738646830574</v>
+        <v>-6754.738646830572</v>
       </c>
     </row>
     <row r="565">
@@ -19725,13 +19725,13 @@
         <v>-368.42958085</v>
       </c>
       <c r="E566" t="n">
-        <v>-369.4772896753833</v>
+        <v>-369.4772896753832</v>
       </c>
       <c r="F566" t="n">
         <v>-6822.77001574074</v>
       </c>
       <c r="G566" t="n">
-        <v>-6842.172031025617</v>
+        <v>-6842.172031025616</v>
       </c>
     </row>
     <row r="567">
@@ -19900,13 +19900,13 @@
         <v>-365.5672135</v>
       </c>
       <c r="E573" t="n">
-        <v>-365.9679791296635</v>
+        <v>-365.9679791296634</v>
       </c>
       <c r="F573" t="n">
         <v>-6769.763212962962</v>
       </c>
       <c r="G573" t="n">
-        <v>-6777.184798697472</v>
+        <v>-6777.184798697471</v>
       </c>
     </row>
     <row r="574">
@@ -19931,7 +19931,7 @@
         <v>-6768.527379814815</v>
       </c>
       <c r="G574" t="n">
-        <v>-6788.773440886858</v>
+        <v>-6788.773440886857</v>
       </c>
     </row>
     <row r="575">
@@ -19981,7 +19981,7 @@
         <v>-6883.550936111112</v>
       </c>
       <c r="G576" t="n">
-        <v>-6796.004559228057</v>
+        <v>-6796.004559228055</v>
       </c>
     </row>
     <row r="577">
@@ -20125,13 +20125,13 @@
         <v>-366.67947125</v>
       </c>
       <c r="E582" t="n">
-        <v>-367.6228094969</v>
+        <v>-367.6228094969001</v>
       </c>
       <c r="F582" t="n">
         <v>-6790.360578703704</v>
       </c>
       <c r="G582" t="n">
-        <v>-6807.829805498149</v>
+        <v>-6807.829805498151</v>
       </c>
     </row>
     <row r="583">
@@ -20225,13 +20225,13 @@
         <v>-122.43053405</v>
       </c>
       <c r="E586" t="n">
-        <v>-121.055408479225</v>
+        <v>-121.0554084792249</v>
       </c>
       <c r="F586" t="n">
         <v>-6801.696336111111</v>
       </c>
       <c r="G586" t="n">
-        <v>-6725.300471068053</v>
+        <v>-6725.300471068051</v>
       </c>
     </row>
     <row r="587">
@@ -20250,7 +20250,7 @@
         <v>-362.71891586</v>
       </c>
       <c r="E587" t="n">
-        <v>-363.4839574201014</v>
+        <v>-363.4839574201015</v>
       </c>
       <c r="F587" t="n">
         <v>-6717.016960370371</v>
@@ -20350,13 +20350,13 @@
         <v>-368.2403116</v>
       </c>
       <c r="E591" t="n">
-        <v>-369.1383767698767</v>
+        <v>-369.1383767698768</v>
       </c>
       <c r="F591" t="n">
         <v>-6819.265029629629</v>
       </c>
       <c r="G591" t="n">
-        <v>-6835.895866108829</v>
+        <v>-6835.89586610883</v>
       </c>
     </row>
     <row r="592">
@@ -20381,7 +20381,7 @@
         <v>-6718.991848333333</v>
       </c>
       <c r="G592" t="n">
-        <v>-6629.509498545289</v>
+        <v>-6629.509498545287</v>
       </c>
     </row>
     <row r="593">
@@ -20450,13 +20450,13 @@
         <v>-366.76419016</v>
       </c>
       <c r="E595" t="n">
-        <v>-367.3405381294279</v>
+        <v>-367.340538129428</v>
       </c>
       <c r="F595" t="n">
         <v>-6791.929447407408</v>
       </c>
       <c r="G595" t="n">
-        <v>-6802.602557952368</v>
+        <v>-6802.602557952369</v>
       </c>
     </row>
     <row r="596">
@@ -20506,7 +20506,7 @@
         <v>-6758.308479814815</v>
       </c>
       <c r="G597" t="n">
-        <v>-6771.498065022668</v>
+        <v>-6771.498065022669</v>
       </c>
     </row>
     <row r="598">
@@ -20556,7 +20556,7 @@
         <v>-6820.877762222222</v>
       </c>
       <c r="G599" t="n">
-        <v>-6735.364986066816</v>
+        <v>-6735.364986066814</v>
       </c>
     </row>
     <row r="600">
@@ -20575,13 +20575,13 @@
         <v>-122.65356535</v>
       </c>
       <c r="E600" t="n">
-        <v>-120.9603775878591</v>
+        <v>-120.960377587859</v>
       </c>
       <c r="F600" t="n">
         <v>-6814.086963888888</v>
       </c>
       <c r="G600" t="n">
-        <v>-6720.020977103281</v>
+        <v>-6720.020977103279</v>
       </c>
     </row>
     <row r="601">
@@ -20656,7 +20656,7 @@
         <v>-6827.405846111111</v>
       </c>
       <c r="G603" t="n">
-        <v>-6747.268121910535</v>
+        <v>-6747.268121910533</v>
       </c>
     </row>
     <row r="604">
@@ -20725,13 +20725,13 @@
         <v>-364.98923488</v>
       </c>
       <c r="E606" t="n">
-        <v>-365.0927051235131</v>
+        <v>-365.0927051235132</v>
       </c>
       <c r="F606" t="n">
         <v>-6759.059905185185</v>
       </c>
       <c r="G606" t="n">
-        <v>-6760.976020805799</v>
+        <v>-6760.9760208058</v>
       </c>
     </row>
     <row r="607">
@@ -20850,7 +20850,7 @@
         <v>-366.69303484</v>
       </c>
       <c r="E611" t="n">
-        <v>-367.6461179447155</v>
+        <v>-367.6461179447154</v>
       </c>
       <c r="F611" t="n">
         <v>-6790.611756296296</v>
@@ -20906,7 +20906,7 @@
         <v>-6731.300144259259</v>
       </c>
       <c r="G613" t="n">
-        <v>-6745.64109044659</v>
+        <v>-6745.641090446592</v>
       </c>
     </row>
     <row r="614">
@@ -20981,7 +20981,7 @@
         <v>-6879.104282222223</v>
       </c>
       <c r="G616" t="n">
-        <v>-6890.892210812924</v>
+        <v>-6890.892210812925</v>
       </c>
     </row>
     <row r="617">
@@ -21200,13 +21200,13 @@
         <v>-363.60348382</v>
       </c>
       <c r="E625" t="n">
-        <v>-363.9869435193565</v>
+        <v>-363.9869435193564</v>
       </c>
       <c r="F625" t="n">
         <v>-6733.397848518519</v>
       </c>
       <c r="G625" t="n">
-        <v>-6740.498954062157</v>
+        <v>-6740.498954062156</v>
       </c>
     </row>
     <row r="626">
@@ -21231,7 +21231,7 @@
         <v>-6784.519828333334</v>
       </c>
       <c r="G626" t="n">
-        <v>-6698.653899434716</v>
+        <v>-6698.653899434714</v>
       </c>
     </row>
     <row r="627">
@@ -21325,13 +21325,13 @@
         <v>-370.46294146</v>
       </c>
       <c r="E630" t="n">
-        <v>-371.1013557160672</v>
+        <v>-371.1013557160673</v>
       </c>
       <c r="F630" t="n">
         <v>-6860.424841851852</v>
       </c>
       <c r="G630" t="n">
-        <v>-6872.247328075319</v>
+        <v>-6872.24732807532</v>
       </c>
     </row>
     <row r="631">
@@ -21525,13 +21525,13 @@
         <v>-362.77391588</v>
       </c>
       <c r="E638" t="n">
-        <v>-363.7299157616625</v>
+        <v>-363.7299157616624</v>
       </c>
       <c r="F638" t="n">
         <v>-6718.035479259259</v>
       </c>
       <c r="G638" t="n">
-        <v>-6735.739180771528</v>
+        <v>-6735.739180771526</v>
       </c>
     </row>
     <row r="639">
@@ -21550,13 +21550,13 @@
         <v>-367.84326054</v>
       </c>
       <c r="E639" t="n">
-        <v>-368.5616464291238</v>
+        <v>-368.5616464291237</v>
       </c>
       <c r="F639" t="n">
         <v>-6811.912232222222</v>
       </c>
       <c r="G639" t="n">
-        <v>-6825.215674613403</v>
+        <v>-6825.215674613402</v>
       </c>
     </row>
     <row r="640">
@@ -21650,13 +21650,13 @@
         <v>-365.87074682</v>
       </c>
       <c r="E643" t="n">
-        <v>-366.504088948914</v>
+        <v>-366.5040889489139</v>
       </c>
       <c r="F643" t="n">
         <v>-6775.38420037037</v>
       </c>
       <c r="G643" t="n">
-        <v>-6787.112758313222</v>
+        <v>-6787.112758313219</v>
       </c>
     </row>
     <row r="644">
@@ -21681,7 +21681,7 @@
         <v>-6810.506632777778</v>
       </c>
       <c r="G644" t="n">
-        <v>-6724.855729803347</v>
+        <v>-6724.855729803345</v>
       </c>
     </row>
     <row r="645">
@@ -21706,7 +21706,7 @@
         <v>-6741.466001851852</v>
       </c>
       <c r="G645" t="n">
-        <v>-6754.214908108186</v>
+        <v>-6754.214908108187</v>
       </c>
     </row>
     <row r="646">
@@ -21775,13 +21775,13 @@
         <v>-362.54308031</v>
       </c>
       <c r="E648" t="n">
-        <v>-363.1672530181949</v>
+        <v>-363.1672530181948</v>
       </c>
       <c r="F648" t="n">
         <v>-6713.760746481481</v>
       </c>
       <c r="G648" t="n">
-        <v>-6725.319500336942</v>
+        <v>-6725.319500336941</v>
       </c>
     </row>
     <row r="649">
@@ -21956,7 +21956,7 @@
         <v>-6836.240636666666</v>
       </c>
       <c r="G655" t="n">
-        <v>-6738.307555195561</v>
+        <v>-6738.30755519556</v>
       </c>
     </row>
     <row r="656">
@@ -22006,7 +22006,7 @@
         <v>-6748.454712592593</v>
       </c>
       <c r="G657" t="n">
-        <v>-6761.865184374927</v>
+        <v>-6761.865184374926</v>
       </c>
     </row>
     <row r="658">
@@ -22056,7 +22056,7 @@
         <v>-6742.741334074074</v>
       </c>
       <c r="G659" t="n">
-        <v>-6755.121115345842</v>
+        <v>-6755.121115345843</v>
       </c>
     </row>
     <row r="660">
@@ -22075,13 +22075,13 @@
         <v>-122.75608817</v>
       </c>
       <c r="E660" t="n">
-        <v>-121.195778826711</v>
+        <v>-121.1957788267109</v>
       </c>
       <c r="F660" t="n">
         <v>-6819.782676111111</v>
       </c>
       <c r="G660" t="n">
-        <v>-6733.098823706165</v>
+        <v>-6733.098823706164</v>
       </c>
     </row>
     <row r="661">
@@ -22131,7 +22131,7 @@
         <v>-6714.143529444445</v>
       </c>
       <c r="G662" t="n">
-        <v>-6633.634218804919</v>
+        <v>-6633.634218804918</v>
       </c>
     </row>
     <row r="663">
@@ -22150,13 +22150,13 @@
         <v>-363.13345652</v>
       </c>
       <c r="E663" t="n">
-        <v>-363.1517313734263</v>
+        <v>-363.1517313734262</v>
       </c>
       <c r="F663" t="n">
         <v>-6724.69363925926</v>
       </c>
       <c r="G663" t="n">
-        <v>-6725.032062470857</v>
+        <v>-6725.032062470856</v>
       </c>
     </row>
     <row r="664">
@@ -22200,13 +22200,13 @@
         <v>-363.58577539</v>
       </c>
       <c r="E665" t="n">
-        <v>-364.6512094977252</v>
+        <v>-364.6512094977253</v>
       </c>
       <c r="F665" t="n">
         <v>-6733.069914629629</v>
       </c>
       <c r="G665" t="n">
-        <v>-6752.800175883801</v>
+        <v>-6752.800175883802</v>
       </c>
     </row>
     <row r="666">
@@ -22231,7 +22231,7 @@
         <v>-6718.635703333333</v>
       </c>
       <c r="G666" t="n">
-        <v>-6730.595370935505</v>
+        <v>-6730.595370935504</v>
       </c>
     </row>
     <row r="667">
@@ -22250,13 +22250,13 @@
         <v>-364.45363802</v>
       </c>
       <c r="E667" t="n">
-        <v>-365.1119355939956</v>
+        <v>-365.1119355939957</v>
       </c>
       <c r="F667" t="n">
         <v>-6749.141444814815</v>
       </c>
       <c r="G667" t="n">
-        <v>-6761.332140629548</v>
+        <v>-6761.33214062955</v>
       </c>
     </row>
     <row r="668">
@@ -22400,13 +22400,13 @@
         <v>-364.62451789</v>
       </c>
       <c r="E673" t="n">
-        <v>-365.744408899639</v>
+        <v>-365.7444088996389</v>
       </c>
       <c r="F673" t="n">
         <v>-6752.305886851852</v>
       </c>
       <c r="G673" t="n">
-        <v>-6773.044609252574</v>
+        <v>-6773.044609252572</v>
       </c>
     </row>
     <row r="674">
@@ -22456,7 +22456,7 @@
         <v>-6804.002129444445</v>
       </c>
       <c r="G675" t="n">
-        <v>-6723.734651870489</v>
+        <v>-6723.734651870487</v>
       </c>
     </row>
     <row r="676">
@@ -22525,13 +22525,13 @@
         <v>-123.44244111</v>
       </c>
       <c r="E678" t="n">
-        <v>-121.936677025577</v>
+        <v>-121.9366770255769</v>
       </c>
       <c r="F678" t="n">
         <v>-6857.913395</v>
       </c>
       <c r="G678" t="n">
-        <v>-6774.259834754275</v>
+        <v>-6774.259834754273</v>
       </c>
     </row>
     <row r="679">
@@ -22581,7 +22581,7 @@
         <v>-6836.987929444444</v>
       </c>
       <c r="G680" t="n">
-        <v>-6749.424068880247</v>
+        <v>-6749.424068880245</v>
       </c>
     </row>
     <row r="681">
@@ -22650,13 +22650,13 @@
         <v>-371.92449998</v>
       </c>
       <c r="E683" t="n">
-        <v>-372.4186342447713</v>
+        <v>-372.4186342447714</v>
       </c>
       <c r="F683" t="n">
         <v>-6887.490740370371</v>
       </c>
       <c r="G683" t="n">
-        <v>-6896.641374903173</v>
+        <v>-6896.641374903174</v>
       </c>
     </row>
     <row r="684">
@@ -22675,13 +22675,13 @@
         <v>-362.50578148</v>
       </c>
       <c r="E684" t="n">
-        <v>-362.7896098357536</v>
+        <v>-362.7896098357535</v>
       </c>
       <c r="F684" t="n">
         <v>-6713.070027407408</v>
       </c>
       <c r="G684" t="n">
-        <v>-6718.32610806951</v>
+        <v>-6718.326108069509</v>
       </c>
     </row>
     <row r="685">
@@ -22756,7 +22756,7 @@
         <v>-6721.880250925926</v>
       </c>
       <c r="G687" t="n">
-        <v>-6745.063936955499</v>
+        <v>-6745.0639369555</v>
       </c>
     </row>
     <row r="688">
@@ -22775,13 +22775,13 @@
         <v>-121.8946505</v>
       </c>
       <c r="E688" t="n">
-        <v>-120.2732352102185</v>
+        <v>-120.2732352102184</v>
       </c>
       <c r="F688" t="n">
         <v>-6771.925027777778</v>
       </c>
       <c r="G688" t="n">
-        <v>-6681.846400567692</v>
+        <v>-6681.846400567691</v>
       </c>
     </row>
     <row r="689">
@@ -22806,7 +22806,7 @@
         <v>-6727.117746851852</v>
       </c>
       <c r="G689" t="n">
-        <v>-6738.343272227253</v>
+        <v>-6738.343272227254</v>
       </c>
     </row>
     <row r="690">
@@ -22831,7 +22831,7 @@
         <v>-6835.931640555556</v>
       </c>
       <c r="G690" t="n">
-        <v>-6759.617059312573</v>
+        <v>-6759.617059312572</v>
       </c>
     </row>
     <row r="691">
@@ -23081,7 +23081,7 @@
         <v>-6743.860521481482</v>
       </c>
       <c r="G700" t="n">
-        <v>-6761.112207053776</v>
+        <v>-6761.112207053777</v>
       </c>
     </row>
     <row r="701">
@@ -23100,13 +23100,13 @@
         <v>-121.28020916</v>
       </c>
       <c r="E701" t="n">
-        <v>-119.8701193239763</v>
+        <v>-119.8701193239762</v>
       </c>
       <c r="F701" t="n">
         <v>-6737.789397777778</v>
       </c>
       <c r="G701" t="n">
-        <v>-6659.451073554237</v>
+        <v>-6659.451073554235</v>
       </c>
     </row>
     <row r="702">
@@ -23156,7 +23156,7 @@
         <v>-6820.851470555555</v>
       </c>
       <c r="G703" t="n">
-        <v>-6739.979735930158</v>
+        <v>-6739.979735930156</v>
       </c>
     </row>
     <row r="704">
@@ -23175,13 +23175,13 @@
         <v>-369.52145964</v>
       </c>
       <c r="E704" t="n">
-        <v>-370.2338132997747</v>
+        <v>-370.2338132997748</v>
       </c>
       <c r="F704" t="n">
         <v>-6842.989993333334</v>
       </c>
       <c r="G704" t="n">
-        <v>-6856.181727773605</v>
+        <v>-6856.181727773607</v>
       </c>
     </row>
     <row r="705">
@@ -23281,7 +23281,7 @@
         <v>-6811.124255925925</v>
       </c>
       <c r="G708" t="n">
-        <v>-6827.004618108808</v>
+        <v>-6827.004618108807</v>
       </c>
     </row>
     <row r="709">
@@ -23306,7 +23306,7 @@
         <v>-6715.929516666667</v>
       </c>
       <c r="G709" t="n">
-        <v>-6633.953014554417</v>
+        <v>-6633.953014554416</v>
       </c>
     </row>
     <row r="710">
@@ -23456,7 +23456,7 @@
         <v>-6802.049861851852</v>
       </c>
       <c r="G715" t="n">
-        <v>-6815.429951746354</v>
+        <v>-6815.429951746353</v>
       </c>
     </row>
     <row r="716">
@@ -23525,13 +23525,13 @@
         <v>-364.02607498</v>
       </c>
       <c r="E718" t="n">
-        <v>-364.7870933526099</v>
+        <v>-364.78709335261</v>
       </c>
       <c r="F718" t="n">
         <v>-6741.223610740741</v>
       </c>
       <c r="G718" t="n">
-        <v>-6755.316543566851</v>
+        <v>-6755.316543566852</v>
       </c>
     </row>
     <row r="719">
@@ -23581,7 +23581,7 @@
         <v>-6742.593829629629</v>
       </c>
       <c r="G720" t="n">
-        <v>-6758.340939367236</v>
+        <v>-6758.340939367235</v>
       </c>
     </row>
     <row r="721">
@@ -23606,7 +23606,7 @@
         <v>-6762.309055</v>
       </c>
       <c r="G721" t="n">
-        <v>-6670.370088552507</v>
+        <v>-6670.370088552506</v>
       </c>
     </row>
     <row r="722">
@@ -23631,7 +23631,7 @@
         <v>-7201.673554375</v>
       </c>
       <c r="G722" t="n">
-        <v>-7191.813193166691</v>
+        <v>-7191.813193166692</v>
       </c>
     </row>
     <row r="723">
@@ -23756,7 +23756,7 @@
         <v>-7481.561064375</v>
       </c>
       <c r="G727" t="n">
-        <v>-7475.395404891851</v>
+        <v>-7475.395404891852</v>
       </c>
     </row>
     <row r="728">
@@ -23831,7 +23831,7 @@
         <v>-7166.744106481481</v>
       </c>
       <c r="G730" t="n">
-        <v>-7170.284306071455</v>
+        <v>-7170.284306071456</v>
       </c>
     </row>
     <row r="731">
@@ -23856,7 +23856,7 @@
         <v>-7499.621015625</v>
       </c>
       <c r="G731" t="n">
-        <v>-7492.63893764631</v>
+        <v>-7492.638937646311</v>
       </c>
     </row>
     <row r="732">
@@ -23900,13 +23900,13 @@
         <v>-117.98965993</v>
       </c>
       <c r="E733" t="n">
-        <v>-117.8447047014841</v>
+        <v>-117.8447047014842</v>
       </c>
       <c r="F733" t="n">
         <v>-7374.353745625001</v>
       </c>
       <c r="G733" t="n">
-        <v>-7365.294043842759</v>
+        <v>-7365.294043842761</v>
       </c>
     </row>
     <row r="734">
@@ -23931,7 +23931,7 @@
         <v>-7336.593401874999</v>
       </c>
       <c r="G734" t="n">
-        <v>-7331.960728571584</v>
+        <v>-7331.960728571582</v>
       </c>
     </row>
     <row r="735">
@@ -23975,13 +23975,13 @@
         <v>-115.65963517</v>
       </c>
       <c r="E736" t="n">
-        <v>-115.6070577089218</v>
+        <v>-115.6070577089219</v>
       </c>
       <c r="F736" t="n">
         <v>-7228.727198125</v>
       </c>
       <c r="G736" t="n">
-        <v>-7225.441106807615</v>
+        <v>-7225.441106807616</v>
       </c>
     </row>
     <row r="737">
@@ -24006,7 +24006,7 @@
         <v>-7231.777866875001</v>
       </c>
       <c r="G737" t="n">
-        <v>-7221.529259543029</v>
+        <v>-7221.529259543028</v>
       </c>
     </row>
     <row r="738">
@@ -24031,7 +24031,7 @@
         <v>-7337.577519375001</v>
       </c>
       <c r="G738" t="n">
-        <v>-7326.702504634388</v>
+        <v>-7326.702504634387</v>
       </c>
     </row>
     <row r="739">
@@ -24050,13 +24050,13 @@
         <v>-119.35354065</v>
       </c>
       <c r="E739" t="n">
-        <v>-119.2604973537</v>
+        <v>-119.2604973537001</v>
       </c>
       <c r="F739" t="n">
         <v>-7459.596290625</v>
       </c>
       <c r="G739" t="n">
-        <v>-7453.781084606253</v>
+        <v>-7453.781084606254</v>
       </c>
     </row>
     <row r="740">
@@ -24256,7 +24256,7 @@
         <v>-7998.250366249999</v>
       </c>
       <c r="G747" t="n">
-        <v>-8026.47985977091</v>
+        <v>-8026.479859770912</v>
       </c>
     </row>
     <row r="748">
@@ -24306,7 +24306,7 @@
         <v>-8002.959103125001</v>
       </c>
       <c r="G749" t="n">
-        <v>-8016.351377657332</v>
+        <v>-8016.351377657334</v>
       </c>
     </row>
     <row r="750">
@@ -24356,7 +24356,7 @@
         <v>-8143.484071250001</v>
       </c>
       <c r="G751" t="n">
-        <v>-8163.479458147338</v>
+        <v>-8163.47945814734</v>
       </c>
     </row>
     <row r="752">
@@ -24531,7 +24531,7 @@
         <v>-7997.004129375</v>
       </c>
       <c r="G758" t="n">
-        <v>-8020.99420704543</v>
+        <v>-8020.994207045432</v>
       </c>
     </row>
     <row r="759">
@@ -24581,7 +24581,7 @@
         <v>-8000.238890000001</v>
       </c>
       <c r="G760" t="n">
-        <v>-8012.85468957556</v>
+        <v>-8012.854689575562</v>
       </c>
     </row>
     <row r="761">
@@ -24650,13 +24650,13 @@
         <v>-131.79708208</v>
       </c>
       <c r="E763" t="n">
-        <v>-132.2090136937999</v>
+        <v>-132.2090136937998</v>
       </c>
       <c r="F763" t="n">
         <v>-8237.31763</v>
       </c>
       <c r="G763" t="n">
-        <v>-8263.063355862492</v>
+        <v>-8263.06335586249</v>
       </c>
     </row>
     <row r="764">
@@ -24781,7 +24781,7 @@
         <v>-7984.5798975</v>
       </c>
       <c r="G768" t="n">
-        <v>-8007.916368427342</v>
+        <v>-8007.916368427344</v>
       </c>
     </row>
     <row r="769">
@@ -24806,7 +24806,7 @@
         <v>-7996.033085625</v>
       </c>
       <c r="G769" t="n">
-        <v>-8026.53440590303</v>
+        <v>-8026.534405903032</v>
       </c>
     </row>
     <row r="770">
@@ -25075,13 +25075,13 @@
         <v>-127.96761438</v>
       </c>
       <c r="E780" t="n">
-        <v>-128.3019382152694</v>
+        <v>-128.3019382152695</v>
       </c>
       <c r="F780" t="n">
         <v>-7997.97589875</v>
       </c>
       <c r="G780" t="n">
-        <v>-8018.87113845434</v>
+        <v>-8018.871138454342</v>
       </c>
     </row>
     <row r="781">
@@ -25131,7 +25131,7 @@
         <v>-8122.566376875</v>
       </c>
       <c r="G782" t="n">
-        <v>-8142.993339476971</v>
+        <v>-8142.99333947697</v>
       </c>
     </row>
     <row r="783">
@@ -25256,7 +25256,7 @@
         <v>-7691.932011875</v>
       </c>
       <c r="G787" t="n">
-        <v>-7680.894900224155</v>
+        <v>-7680.894900224156</v>
       </c>
     </row>
     <row r="788">
@@ -25456,7 +25456,7 @@
         <v>-7916.48088375</v>
       </c>
       <c r="G795" t="n">
-        <v>-7926.796951275965</v>
+        <v>-7926.796951275966</v>
       </c>
     </row>
     <row r="796">
@@ -25481,7 +25481,7 @@
         <v>-7804.841740625</v>
       </c>
       <c r="G796" t="n">
-        <v>-7793.352448149463</v>
+        <v>-7793.352448149461</v>
       </c>
     </row>
     <row r="797">
@@ -25631,7 +25631,7 @@
         <v>-6294.801362222222</v>
       </c>
       <c r="G802" t="n">
-        <v>-6213.565281601845</v>
+        <v>-6213.565281601844</v>
       </c>
     </row>
   </sheetData>
@@ -25680,13 +25680,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41.9826862274925</v>
+        <v>41.98268622749266</v>
       </c>
       <c r="D2" t="n">
-        <v>29.65271549685626</v>
+        <v>29.65271549685644</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9877985536754599</v>
+        <v>0.9877985536754598</v>
       </c>
     </row>
     <row r="3">
@@ -25699,10 +25699,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.27250259232432</v>
+        <v>36.27250259232452</v>
       </c>
       <c r="D3" t="n">
-        <v>24.82274733456027</v>
+        <v>24.82274733456041</v>
       </c>
       <c r="E3" t="n">
         <v>0.990245830911735</v>
@@ -25805,10 +25805,10 @@
         <v>48</v>
       </c>
       <c r="E2" t="n">
-        <v>82.567311745891</v>
+        <v>82.56731174589125</v>
       </c>
       <c r="F2" t="n">
-        <v>82.23658855164012</v>
+        <v>82.23658855164037</v>
       </c>
     </row>
     <row r="3">
@@ -25829,10 +25829,10 @@
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>9.56782690870385</v>
+        <v>9.567826908704136</v>
       </c>
       <c r="F3" t="n">
-        <v>9.288901338848367</v>
+        <v>9.288901338848595</v>
       </c>
     </row>
     <row r="4">
@@ -25853,10 +25853,10 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>23.30231791431743</v>
+        <v>23.30231791431833</v>
       </c>
       <c r="F4" t="n">
-        <v>23.14869963095688</v>
+        <v>23.14869963095771</v>
       </c>
     </row>
     <row r="5">
@@ -25877,10 +25877,10 @@
         <v>133</v>
       </c>
       <c r="E5" t="n">
-        <v>13.77983376549245</v>
+        <v>13.77983376549253</v>
       </c>
       <c r="F5" t="n">
-        <v>13.05033984115221</v>
+        <v>13.05033984115232</v>
       </c>
     </row>
     <row r="6">
@@ -25901,10 +25901,10 @@
         <v>132</v>
       </c>
       <c r="E6" t="n">
-        <v>83.36717151735193</v>
+        <v>83.3671715173524</v>
       </c>
       <c r="F6" t="n">
-        <v>83.08482653625023</v>
+        <v>83.0848265362507</v>
       </c>
     </row>
     <row r="7">
@@ -25925,10 +25925,10 @@
         <v>39</v>
       </c>
       <c r="E7" t="n">
-        <v>9.745290242236049</v>
+        <v>9.745290242235997</v>
       </c>
       <c r="F7" t="n">
-        <v>9.396849869687008</v>
+        <v>9.396849869686939</v>
       </c>
     </row>
     <row r="8">
@@ -25949,10 +25949,10 @@
         <v>40</v>
       </c>
       <c r="E8" t="n">
-        <v>22.17536832431286</v>
+        <v>22.17536832431313</v>
       </c>
       <c r="F8" t="n">
-        <v>21.46486241884559</v>
+        <v>21.46486241884588</v>
       </c>
     </row>
     <row r="9">
@@ -25973,10 +25973,10 @@
         <v>590</v>
       </c>
       <c r="E9" t="n">
-        <v>13.84455207221181</v>
+        <v>13.84455207221187</v>
       </c>
       <c r="F9" t="n">
-        <v>13.0351726619087</v>
+        <v>13.03517266190877</v>
       </c>
     </row>
   </sheetData>

--- a/new_model/model_Fe_Si_B_260311/fine_tuning/matpes_nofe8b4_0.0001_40_10_rnd_e/test_res/model_rnd_e_matpes_nofe8b4_lr0.0001_40_10_test.xlsx
+++ b/new_model/model_Fe_Si_B_260311/fine_tuning/matpes_nofe8b4_0.0001_40_10_rnd_e/test_res/model_rnd_e_matpes_nofe8b4_lr0.0001_40_10_test.xlsx
@@ -479,7 +479,7 @@
         <v>-352.89092233</v>
       </c>
       <c r="E2" t="n">
-        <v>-353.1501167440814</v>
+        <v>-353.1501167440813</v>
       </c>
       <c r="F2" t="n">
         <v>-6535.017080185185</v>
@@ -504,13 +504,13 @@
         <v>-354.71875992</v>
       </c>
       <c r="E3" t="n">
-        <v>-355.2591225083599</v>
+        <v>-355.25912250836</v>
       </c>
       <c r="F3" t="n">
         <v>-6568.865924444445</v>
       </c>
       <c r="G3" t="n">
-        <v>-6578.872639043701</v>
+        <v>-6578.872639043703</v>
       </c>
     </row>
     <row r="4">
@@ -554,13 +554,13 @@
         <v>-356.0869274</v>
       </c>
       <c r="E5" t="n">
-        <v>-356.9276013540674</v>
+        <v>-356.9276013540673</v>
       </c>
       <c r="F5" t="n">
         <v>-6594.202359259259</v>
       </c>
       <c r="G5" t="n">
-        <v>-6609.770395445692</v>
+        <v>-6609.770395445691</v>
       </c>
     </row>
     <row r="6">
@@ -579,13 +579,13 @@
         <v>-359.84864784</v>
       </c>
       <c r="E6" t="n">
-        <v>-360.3461800199903</v>
+        <v>-360.3461800199902</v>
       </c>
       <c r="F6" t="n">
         <v>-6663.863848888889</v>
       </c>
       <c r="G6" t="n">
-        <v>-6673.077407777599</v>
+        <v>-6673.077407777597</v>
       </c>
     </row>
     <row r="7">
@@ -604,13 +604,13 @@
         <v>-358.03511683</v>
       </c>
       <c r="E7" t="n">
-        <v>-358.7227010745768</v>
+        <v>-358.7227010745767</v>
       </c>
       <c r="F7" t="n">
         <v>-6630.279941296297</v>
       </c>
       <c r="G7" t="n">
-        <v>-6643.012982862532</v>
+        <v>-6643.012982862531</v>
       </c>
     </row>
     <row r="8">
@@ -635,7 +635,7 @@
         <v>-6510.964588333333</v>
       </c>
       <c r="G8" t="n">
-        <v>-6531.113731740918</v>
+        <v>-6531.113731740919</v>
       </c>
     </row>
     <row r="9">
@@ -679,13 +679,13 @@
         <v>-353.47168566</v>
       </c>
       <c r="E10" t="n">
-        <v>-353.8294118059554</v>
+        <v>-353.8294118059555</v>
       </c>
       <c r="F10" t="n">
         <v>-6545.771956666667</v>
       </c>
       <c r="G10" t="n">
-        <v>-6552.3965149251</v>
+        <v>-6552.396514925101</v>
       </c>
     </row>
     <row r="11">
@@ -729,13 +729,13 @@
         <v>-354.27371606</v>
       </c>
       <c r="E12" t="n">
-        <v>-355.3908315985237</v>
+        <v>-355.3908315985238</v>
       </c>
       <c r="F12" t="n">
         <v>-6560.624371481482</v>
       </c>
       <c r="G12" t="n">
-        <v>-6581.311696268957</v>
+        <v>-6581.311696268959</v>
       </c>
     </row>
     <row r="13">
@@ -760,7 +760,7 @@
         <v>-6702.166977777778</v>
       </c>
       <c r="G13" t="n">
-        <v>-6615.364008262506</v>
+        <v>-6615.364008262508</v>
       </c>
     </row>
     <row r="14">
@@ -804,13 +804,13 @@
         <v>-355.98978912</v>
       </c>
       <c r="E15" t="n">
-        <v>-357.0619284816953</v>
+        <v>-357.0619284816954</v>
       </c>
       <c r="F15" t="n">
         <v>-6592.403502222222</v>
       </c>
       <c r="G15" t="n">
-        <v>-6612.25793484621</v>
+        <v>-6612.257934846211</v>
       </c>
     </row>
     <row r="16">
@@ -829,13 +829,13 @@
         <v>-357.2238307</v>
       </c>
       <c r="E16" t="n">
-        <v>-357.9362960685456</v>
+        <v>-357.9362960685457</v>
       </c>
       <c r="F16" t="n">
         <v>-6615.256124074074</v>
       </c>
       <c r="G16" t="n">
-        <v>-6628.449927195289</v>
+        <v>-6628.44992719529</v>
       </c>
     </row>
     <row r="17">
@@ -860,7 +860,7 @@
         <v>-6615.419764444444</v>
       </c>
       <c r="G17" t="n">
-        <v>-6624.117859991322</v>
+        <v>-6624.117859991324</v>
       </c>
     </row>
     <row r="18">
@@ -879,13 +879,13 @@
         <v>-355.71595759</v>
       </c>
       <c r="E18" t="n">
-        <v>-356.5621092495736</v>
+        <v>-356.5621092495737</v>
       </c>
       <c r="F18" t="n">
         <v>-6587.332547962963</v>
       </c>
       <c r="G18" t="n">
-        <v>-6603.002023140252</v>
+        <v>-6603.002023140254</v>
       </c>
     </row>
     <row r="19">
@@ -960,7 +960,7 @@
         <v>-6678.663742777778</v>
       </c>
       <c r="G21" t="n">
-        <v>-6594.38836826209</v>
+        <v>-6594.388368262091</v>
       </c>
     </row>
     <row r="22">
@@ -979,13 +979,13 @@
         <v>-348.44390711</v>
       </c>
       <c r="E22" t="n">
-        <v>-349.8059788481088</v>
+        <v>-349.8059788481089</v>
       </c>
       <c r="F22" t="n">
         <v>-6452.664946481481</v>
       </c>
       <c r="G22" t="n">
-        <v>-6477.888497187199</v>
+        <v>-6477.888497187202</v>
       </c>
     </row>
     <row r="23">
@@ -1035,7 +1035,7 @@
         <v>-6654.565425740741</v>
       </c>
       <c r="G24" t="n">
-        <v>-6668.350645117132</v>
+        <v>-6668.350645117131</v>
       </c>
     </row>
     <row r="25">
@@ -1054,13 +1054,13 @@
         <v>-357.66477533</v>
       </c>
       <c r="E25" t="n">
-        <v>-358.3794679939108</v>
+        <v>-358.3794679939109</v>
       </c>
       <c r="F25" t="n">
         <v>-6623.42176537037</v>
       </c>
       <c r="G25" t="n">
-        <v>-6636.656814702052</v>
+        <v>-6636.656814702053</v>
       </c>
     </row>
     <row r="26">
@@ -1104,13 +1104,13 @@
         <v>-356.21036234</v>
       </c>
       <c r="E27" t="n">
-        <v>-356.9815735842491</v>
+        <v>-356.9815735842492</v>
       </c>
       <c r="F27" t="n">
         <v>-6596.488191481481</v>
       </c>
       <c r="G27" t="n">
-        <v>-6610.769881189797</v>
+        <v>-6610.7698811898</v>
       </c>
     </row>
     <row r="28">
@@ -1129,13 +1129,13 @@
         <v>-356.21541885</v>
       </c>
       <c r="E28" t="n">
-        <v>-356.9925960439958</v>
+        <v>-356.9925960439959</v>
       </c>
       <c r="F28" t="n">
         <v>-6596.581830555556</v>
       </c>
       <c r="G28" t="n">
-        <v>-6610.974000814737</v>
+        <v>-6610.974000814739</v>
       </c>
     </row>
     <row r="29">
@@ -1154,13 +1154,13 @@
         <v>-362.16073209</v>
       </c>
       <c r="E29" t="n">
-        <v>-362.5710886919696</v>
+        <v>-362.5710886919695</v>
       </c>
       <c r="F29" t="n">
         <v>-6706.680223888889</v>
       </c>
       <c r="G29" t="n">
-        <v>-6714.27942022166</v>
+        <v>-6714.279420221657</v>
       </c>
     </row>
     <row r="30">
@@ -1260,7 +1260,7 @@
         <v>-6653.362622037036</v>
       </c>
       <c r="G33" t="n">
-        <v>-6668.413637339387</v>
+        <v>-6668.413637339388</v>
       </c>
     </row>
     <row r="34">
@@ -1354,13 +1354,13 @@
         <v>-349.52822987</v>
       </c>
       <c r="E37" t="n">
-        <v>-349.9955617967836</v>
+        <v>-349.9955617967837</v>
       </c>
       <c r="F37" t="n">
         <v>-6472.744997592593</v>
       </c>
       <c r="G37" t="n">
-        <v>-6481.39929253303</v>
+        <v>-6481.399292533031</v>
       </c>
     </row>
     <row r="38">
@@ -1379,13 +1379,13 @@
         <v>-355.68126147</v>
       </c>
       <c r="E38" t="n">
-        <v>-356.2630976392939</v>
+        <v>-356.263097639294</v>
       </c>
       <c r="F38" t="n">
         <v>-6586.690027222222</v>
       </c>
       <c r="G38" t="n">
-        <v>-6597.464771098034</v>
+        <v>-6597.464771098036</v>
       </c>
     </row>
     <row r="39">
@@ -1454,13 +1454,13 @@
         <v>-361.12052669</v>
       </c>
       <c r="E41" t="n">
-        <v>-361.9341177822772</v>
+        <v>-361.9341177822771</v>
       </c>
       <c r="F41" t="n">
         <v>-6687.417160925927</v>
       </c>
       <c r="G41" t="n">
-        <v>-6702.483662634762</v>
+        <v>-6702.483662634761</v>
       </c>
     </row>
     <row r="42">
@@ -1479,13 +1479,13 @@
         <v>-356.97023688</v>
       </c>
       <c r="E42" t="n">
-        <v>-358.0660511734705</v>
+        <v>-358.0660511734706</v>
       </c>
       <c r="F42" t="n">
         <v>-6610.559942222223</v>
       </c>
       <c r="G42" t="n">
-        <v>-6630.852799508713</v>
+        <v>-6630.852799508714</v>
       </c>
     </row>
     <row r="43">
@@ -1529,13 +1529,13 @@
         <v>-361.89954578</v>
       </c>
       <c r="E44" t="n">
-        <v>-362.3820846812479</v>
+        <v>-362.382084681248</v>
       </c>
       <c r="F44" t="n">
         <v>-6701.84344037037</v>
       </c>
       <c r="G44" t="n">
-        <v>-6710.779345949035</v>
+        <v>-6710.779345949037</v>
       </c>
     </row>
     <row r="45">
@@ -1554,13 +1554,13 @@
         <v>-352.31647211</v>
       </c>
       <c r="E45" t="n">
-        <v>-352.9806564064084</v>
+        <v>-352.9806564064085</v>
       </c>
       <c r="F45" t="n">
         <v>-6524.379113148148</v>
       </c>
       <c r="G45" t="n">
-        <v>-6536.678822340897</v>
+        <v>-6536.678822340898</v>
       </c>
     </row>
     <row r="46">
@@ -1610,7 +1610,7 @@
         <v>-6662.989622592593</v>
       </c>
       <c r="G47" t="n">
-        <v>-6680.224623482348</v>
+        <v>-6680.224623482349</v>
       </c>
     </row>
     <row r="48">
@@ -1629,13 +1629,13 @@
         <v>-360.60945936</v>
       </c>
       <c r="E48" t="n">
-        <v>-361.6454543831994</v>
+        <v>-361.6454543831995</v>
       </c>
       <c r="F48" t="n">
         <v>-6677.952951111111</v>
       </c>
       <c r="G48" t="n">
-        <v>-6697.138044133322</v>
+        <v>-6697.138044133323</v>
       </c>
     </row>
     <row r="49">
@@ -1704,13 +1704,13 @@
         <v>-361.85477759</v>
       </c>
       <c r="E51" t="n">
-        <v>-362.7626179540711</v>
+        <v>-362.762617954071</v>
       </c>
       <c r="F51" t="n">
         <v>-6701.014399814815</v>
       </c>
       <c r="G51" t="n">
-        <v>-6717.826258408724</v>
+        <v>-6717.826258408722</v>
       </c>
     </row>
     <row r="52">
@@ -1754,13 +1754,13 @@
         <v>-361.18775715</v>
       </c>
       <c r="E53" t="n">
-        <v>-362.0164485183249</v>
+        <v>-362.016448518325</v>
       </c>
       <c r="F53" t="n">
         <v>-6688.662169444444</v>
       </c>
       <c r="G53" t="n">
-        <v>-6704.008305894906</v>
+        <v>-6704.008305894908</v>
       </c>
     </row>
     <row r="54">
@@ -1779,7 +1779,7 @@
         <v>-351.98155875</v>
       </c>
       <c r="E54" t="n">
-        <v>-353.0550278442254</v>
+        <v>-353.0550278442255</v>
       </c>
       <c r="F54" t="n">
         <v>-6518.177013888889</v>
@@ -1804,13 +1804,13 @@
         <v>-120.07763673</v>
       </c>
       <c r="E55" t="n">
-        <v>-118.7481098874554</v>
+        <v>-118.7481098874555</v>
       </c>
       <c r="F55" t="n">
         <v>-6670.979818333333</v>
       </c>
       <c r="G55" t="n">
-        <v>-6597.117215969746</v>
+        <v>-6597.117215969748</v>
       </c>
     </row>
     <row r="56">
@@ -1929,13 +1929,13 @@
         <v>-348.73229168</v>
       </c>
       <c r="E60" t="n">
-        <v>-349.4156733629104</v>
+        <v>-349.4156733629105</v>
       </c>
       <c r="F60" t="n">
         <v>-6458.005401481482</v>
       </c>
       <c r="G60" t="n">
-        <v>-6470.660617831674</v>
+        <v>-6470.660617831676</v>
       </c>
     </row>
     <row r="61">
@@ -2029,13 +2029,13 @@
         <v>-359.57758351</v>
       </c>
       <c r="E64" t="n">
-        <v>-360.1457005641231</v>
+        <v>-360.1457005641232</v>
       </c>
       <c r="F64" t="n">
         <v>-6658.844139074075</v>
       </c>
       <c r="G64" t="n">
-        <v>-6669.364825261539</v>
+        <v>-6669.36482526154</v>
       </c>
     </row>
     <row r="65">
@@ -2129,13 +2129,13 @@
         <v>-120.39927863</v>
       </c>
       <c r="E68" t="n">
-        <v>-118.8884523499015</v>
+        <v>-118.8884523499016</v>
       </c>
       <c r="F68" t="n">
         <v>-6688.848812777778</v>
       </c>
       <c r="G68" t="n">
-        <v>-6604.914019438975</v>
+        <v>-6604.914019438976</v>
       </c>
     </row>
     <row r="69">
@@ -2179,13 +2179,13 @@
         <v>-361.82007421</v>
       </c>
       <c r="E70" t="n">
-        <v>-362.6513408472436</v>
+        <v>-362.6513408472435</v>
       </c>
       <c r="F70" t="n">
         <v>-6700.37174462963</v>
       </c>
       <c r="G70" t="n">
-        <v>-6715.765571245252</v>
+        <v>-6715.765571245251</v>
       </c>
     </row>
     <row r="71">
@@ -2204,13 +2204,13 @@
         <v>-351.34183157</v>
       </c>
       <c r="E71" t="n">
-        <v>-352.1448617265716</v>
+        <v>-352.1448617265715</v>
       </c>
       <c r="F71" t="n">
         <v>-6506.33021425926</v>
       </c>
       <c r="G71" t="n">
-        <v>-6521.20114308466</v>
+        <v>-6521.201143084659</v>
       </c>
     </row>
     <row r="72">
@@ -2235,7 +2235,7 @@
         <v>-6657.520538333333</v>
       </c>
       <c r="G72" t="n">
-        <v>-6668.194349846622</v>
+        <v>-6668.194349846621</v>
       </c>
     </row>
     <row r="73">
@@ -2254,13 +2254,13 @@
         <v>-350.51577832</v>
       </c>
       <c r="E73" t="n">
-        <v>-350.917046707924</v>
+        <v>-350.9170467079241</v>
       </c>
       <c r="F73" t="n">
         <v>-6491.032931851852</v>
       </c>
       <c r="G73" t="n">
-        <v>-6498.463827924519</v>
+        <v>-6498.46382792452</v>
       </c>
     </row>
     <row r="74">
@@ -2304,13 +2304,13 @@
         <v>-359.85594239</v>
       </c>
       <c r="E75" t="n">
-        <v>-360.3250567797265</v>
+        <v>-360.3250567797266</v>
       </c>
       <c r="F75" t="n">
         <v>-6663.998933148147</v>
       </c>
       <c r="G75" t="n">
-        <v>-6672.686236661602</v>
+        <v>-6672.686236661603</v>
       </c>
     </row>
     <row r="76">
@@ -2385,7 +2385,7 @@
         <v>-6630.712915740741</v>
       </c>
       <c r="G78" t="n">
-        <v>-6648.042515255463</v>
+        <v>-6648.042515255464</v>
       </c>
     </row>
     <row r="79">
@@ -2404,13 +2404,13 @@
         <v>-351.98465025</v>
       </c>
       <c r="E79" t="n">
-        <v>-352.9192041528399</v>
+        <v>-352.91920415284</v>
       </c>
       <c r="F79" t="n">
         <v>-6518.234263888889</v>
       </c>
       <c r="G79" t="n">
-        <v>-6535.540817645183</v>
+        <v>-6535.540817645186</v>
       </c>
     </row>
     <row r="80">
@@ -2454,13 +2454,13 @@
         <v>-356.91773061</v>
       </c>
       <c r="E81" t="n">
-        <v>-357.4991637718226</v>
+        <v>-357.4991637718227</v>
       </c>
       <c r="F81" t="n">
         <v>-6609.587603888888</v>
       </c>
       <c r="G81" t="n">
-        <v>-6620.354884663382</v>
+        <v>-6620.354884663385</v>
       </c>
     </row>
     <row r="82">
@@ -2479,13 +2479,13 @@
         <v>-359.02627606</v>
       </c>
       <c r="E82" t="n">
-        <v>-359.7419932949488</v>
+        <v>-359.7419932949487</v>
       </c>
       <c r="F82" t="n">
         <v>-6648.634741851852</v>
       </c>
       <c r="G82" t="n">
-        <v>-6661.888764721273</v>
+        <v>-6661.888764721272</v>
       </c>
     </row>
     <row r="83">
@@ -2504,13 +2504,13 @@
         <v>-357.07680184</v>
       </c>
       <c r="E83" t="n">
-        <v>-357.7451810073043</v>
+        <v>-357.7451810073044</v>
       </c>
       <c r="F83" t="n">
         <v>-6612.533367407407</v>
       </c>
       <c r="G83" t="n">
-        <v>-6624.910759394525</v>
+        <v>-6624.910759394526</v>
       </c>
     </row>
     <row r="84">
@@ -2560,7 +2560,7 @@
         <v>-6669.518325925926</v>
       </c>
       <c r="G85" t="n">
-        <v>-6677.968788788158</v>
+        <v>-6677.968788788157</v>
       </c>
     </row>
     <row r="86">
@@ -2585,7 +2585,7 @@
         <v>-6574.283485740742</v>
       </c>
       <c r="G86" t="n">
-        <v>-6580.742720475675</v>
+        <v>-6580.742720475676</v>
       </c>
     </row>
     <row r="87">
@@ -2679,13 +2679,13 @@
         <v>-356.23105557</v>
       </c>
       <c r="E90" t="n">
-        <v>-356.65187794867</v>
+        <v>-356.6518779486701</v>
       </c>
       <c r="F90" t="n">
         <v>-6596.871399444445</v>
       </c>
       <c r="G90" t="n">
-        <v>-6604.664406456852</v>
+        <v>-6604.664406456853</v>
       </c>
     </row>
     <row r="91">
@@ -2729,13 +2729,13 @@
         <v>-358.13900723</v>
       </c>
       <c r="E92" t="n">
-        <v>-358.9787654012067</v>
+        <v>-358.9787654012068</v>
       </c>
       <c r="F92" t="n">
         <v>-6632.203837592592</v>
       </c>
       <c r="G92" t="n">
-        <v>-6647.754914837162</v>
+        <v>-6647.754914837163</v>
       </c>
     </row>
     <row r="93">
@@ -2854,13 +2854,13 @@
         <v>-361.53601897</v>
       </c>
       <c r="E97" t="n">
-        <v>-362.0314612329048</v>
+        <v>-362.0314612329049</v>
       </c>
       <c r="F97" t="n">
         <v>-6695.111462407407</v>
       </c>
       <c r="G97" t="n">
-        <v>-6704.286319127867</v>
+        <v>-6704.286319127868</v>
       </c>
     </row>
     <row r="98">
@@ -2879,13 +2879,13 @@
         <v>-357.02872271</v>
       </c>
       <c r="E98" t="n">
-        <v>-358.6804432164061</v>
+        <v>-358.6804432164062</v>
       </c>
       <c r="F98" t="n">
         <v>-6611.643013148148</v>
       </c>
       <c r="G98" t="n">
-        <v>-6642.230429933446</v>
+        <v>-6642.230429933447</v>
       </c>
     </row>
     <row r="99">
@@ -2904,13 +2904,13 @@
         <v>-346.29628625</v>
       </c>
       <c r="E99" t="n">
-        <v>-346.7019606716754</v>
+        <v>-346.7019606716755</v>
       </c>
       <c r="F99" t="n">
         <v>-6412.894189814815</v>
       </c>
       <c r="G99" t="n">
-        <v>-6420.4066791051</v>
+        <v>-6420.406679105101</v>
       </c>
     </row>
     <row r="100">
@@ -2954,13 +2954,13 @@
         <v>-353.96251689</v>
       </c>
       <c r="E101" t="n">
-        <v>-354.5928741918952</v>
+        <v>-354.5928741918953</v>
       </c>
       <c r="F101" t="n">
         <v>-6554.861423888889</v>
       </c>
       <c r="G101" t="n">
-        <v>-6566.534707257319</v>
+        <v>-6566.53470725732</v>
       </c>
     </row>
     <row r="102">
@@ -2979,13 +2979,13 @@
         <v>-114.83091136</v>
       </c>
       <c r="E102" t="n">
-        <v>-113.1496028966573</v>
+        <v>-113.1496028966574</v>
       </c>
       <c r="F102" t="n">
         <v>-6379.495075555556</v>
       </c>
       <c r="G102" t="n">
-        <v>-6286.089049814296</v>
+        <v>-6286.089049814298</v>
       </c>
     </row>
     <row r="103">
@@ -3079,13 +3079,13 @@
         <v>-360.11768403</v>
       </c>
       <c r="E106" t="n">
-        <v>-360.715964484118</v>
+        <v>-360.7159644841181</v>
       </c>
       <c r="F106" t="n">
         <v>-6668.846000555555</v>
       </c>
       <c r="G106" t="n">
-        <v>-6679.925268224408</v>
+        <v>-6679.92526822441</v>
       </c>
     </row>
     <row r="107">
@@ -3104,13 +3104,13 @@
         <v>-360.89120086</v>
       </c>
       <c r="E107" t="n">
-        <v>-361.5524745875354</v>
+        <v>-361.5524745875355</v>
       </c>
       <c r="F107" t="n">
         <v>-6683.170386296297</v>
       </c>
       <c r="G107" t="n">
-        <v>-6695.416196065471</v>
+        <v>-6695.416196065472</v>
       </c>
     </row>
     <row r="108">
@@ -3160,7 +3160,7 @@
         <v>-6617.695571851852</v>
       </c>
       <c r="G109" t="n">
-        <v>-6631.345413063033</v>
+        <v>-6631.345413063034</v>
       </c>
     </row>
     <row r="110">
@@ -3279,13 +3279,13 @@
         <v>-116.35009772</v>
       </c>
       <c r="E114" t="n">
-        <v>-115.1605792324751</v>
+        <v>-115.1605792324752</v>
       </c>
       <c r="F114" t="n">
         <v>-6463.894317777777</v>
       </c>
       <c r="G114" t="n">
-        <v>-6397.809957359729</v>
+        <v>-6397.809957359731</v>
       </c>
     </row>
     <row r="115">
@@ -3310,7 +3310,7 @@
         <v>-6616.523669814814</v>
       </c>
       <c r="G115" t="n">
-        <v>-6627.345903207824</v>
+        <v>-6627.345903207825</v>
       </c>
     </row>
     <row r="116">
@@ -3354,13 +3354,13 @@
         <v>-359.47908079</v>
       </c>
       <c r="E117" t="n">
-        <v>-360.3489592076209</v>
+        <v>-360.3489592076208</v>
       </c>
       <c r="F117" t="n">
         <v>-6657.02001462963</v>
       </c>
       <c r="G117" t="n">
-        <v>-6673.128874215202</v>
+        <v>-6673.1288742152</v>
       </c>
     </row>
     <row r="118">
@@ -3385,7 +3385,7 @@
         <v>-6603.396217777778</v>
       </c>
       <c r="G118" t="n">
-        <v>-6613.964421712444</v>
+        <v>-6613.964421712445</v>
       </c>
     </row>
     <row r="119">
@@ -3404,13 +3404,13 @@
         <v>-352.75395071</v>
       </c>
       <c r="E119" t="n">
-        <v>-353.5856663204294</v>
+        <v>-353.5856663204293</v>
       </c>
       <c r="F119" t="n">
         <v>-6532.480568703704</v>
       </c>
       <c r="G119" t="n">
-        <v>-6547.882709637581</v>
+        <v>-6547.88270963758</v>
       </c>
     </row>
     <row r="120">
@@ -3454,13 +3454,13 @@
         <v>-357.45867594</v>
       </c>
       <c r="E121" t="n">
-        <v>-358.0924017255901</v>
+        <v>-358.0924017255902</v>
       </c>
       <c r="F121" t="n">
         <v>-6619.60511</v>
       </c>
       <c r="G121" t="n">
-        <v>-6631.340772696113</v>
+        <v>-6631.340772696114</v>
       </c>
     </row>
     <row r="122">
@@ -3510,7 +3510,7 @@
         <v>-6811.255107777778</v>
       </c>
       <c r="G123" t="n">
-        <v>-6725.100935508704</v>
+        <v>-6725.100935508706</v>
       </c>
     </row>
     <row r="124">
@@ -3535,7 +3535,7 @@
         <v>-6842.795679444444</v>
       </c>
       <c r="G124" t="n">
-        <v>-6757.576971415473</v>
+        <v>-6757.576971415475</v>
       </c>
     </row>
     <row r="125">
@@ -3629,13 +3629,13 @@
         <v>-122.68057153</v>
       </c>
       <c r="E128" t="n">
-        <v>-121.1835496571461</v>
+        <v>-121.1835496571462</v>
       </c>
       <c r="F128" t="n">
         <v>-6815.587307222222</v>
       </c>
       <c r="G128" t="n">
-        <v>-6732.419425397007</v>
+        <v>-6732.419425397009</v>
       </c>
     </row>
     <row r="129">
@@ -3660,7 +3660,7 @@
         <v>-6731.819887222223</v>
       </c>
       <c r="G129" t="n">
-        <v>-6654.751576975908</v>
+        <v>-6654.751576975909</v>
       </c>
     </row>
     <row r="130">
@@ -3685,7 +3685,7 @@
         <v>-6798.320042222223</v>
       </c>
       <c r="G130" t="n">
-        <v>-6705.589855181151</v>
+        <v>-6705.589855181152</v>
       </c>
     </row>
     <row r="131">
@@ -3704,13 +3704,13 @@
         <v>-362.74498218</v>
       </c>
       <c r="E131" t="n">
-        <v>-363.3062865829412</v>
+        <v>-363.3062865829411</v>
       </c>
       <c r="F131" t="n">
         <v>-6717.499670000001</v>
       </c>
       <c r="G131" t="n">
-        <v>-6727.894195980392</v>
+        <v>-6727.894195980391</v>
       </c>
     </row>
     <row r="132">
@@ -3729,13 +3729,13 @@
         <v>-121.03497159</v>
       </c>
       <c r="E132" t="n">
-        <v>-119.6952707698351</v>
+        <v>-119.6952707698352</v>
       </c>
       <c r="F132" t="n">
         <v>-6724.165088333333</v>
       </c>
       <c r="G132" t="n">
-        <v>-6649.73726499084</v>
+        <v>-6649.737264990842</v>
       </c>
     </row>
     <row r="133">
@@ -3760,7 +3760,7 @@
         <v>-6733.266356851852</v>
       </c>
       <c r="G133" t="n">
-        <v>-6744.644428879746</v>
+        <v>-6744.644428879747</v>
       </c>
     </row>
     <row r="134">
@@ -3785,7 +3785,7 @@
         <v>-6804.727030555556</v>
       </c>
       <c r="G134" t="n">
-        <v>-6732.59021699606</v>
+        <v>-6732.590216996062</v>
       </c>
     </row>
     <row r="135">
@@ -3829,13 +3829,13 @@
         <v>-123.4300494</v>
       </c>
       <c r="E136" t="n">
-        <v>-121.7692223305329</v>
+        <v>-121.769222330533</v>
       </c>
       <c r="F136" t="n">
         <v>-6857.224966666667</v>
       </c>
       <c r="G136" t="n">
-        <v>-6764.956796140718</v>
+        <v>-6764.956796140719</v>
       </c>
     </row>
     <row r="137">
@@ -3879,13 +3879,13 @@
         <v>-364.81041283</v>
       </c>
       <c r="E138" t="n">
-        <v>-365.29906964462</v>
+        <v>-365.2990696446201</v>
       </c>
       <c r="F138" t="n">
         <v>-6755.748385740741</v>
       </c>
       <c r="G138" t="n">
-        <v>-6764.797586011483</v>
+        <v>-6764.797586011484</v>
       </c>
     </row>
     <row r="139">
@@ -3979,13 +3979,13 @@
         <v>-365.9082522</v>
       </c>
       <c r="E142" t="n">
-        <v>-367.0522705049174</v>
+        <v>-367.0522705049175</v>
       </c>
       <c r="F142" t="n">
         <v>-6776.078744444444</v>
       </c>
       <c r="G142" t="n">
-        <v>-6797.264268609582</v>
+        <v>-6797.264268609583</v>
       </c>
     </row>
     <row r="143">
@@ -4035,7 +4035,7 @@
         <v>-6843.828052777778</v>
       </c>
       <c r="G144" t="n">
-        <v>-6773.336161526765</v>
+        <v>-6773.336161526767</v>
       </c>
     </row>
     <row r="145">
@@ -4060,7 +4060,7 @@
         <v>-6757.151481481483</v>
       </c>
       <c r="G145" t="n">
-        <v>-6762.918925659762</v>
+        <v>-6762.918925659764</v>
       </c>
     </row>
     <row r="146">
@@ -4135,7 +4135,7 @@
         <v>-6729.986600925926</v>
       </c>
       <c r="G148" t="n">
-        <v>-6744.620720257923</v>
+        <v>-6744.620720257924</v>
       </c>
     </row>
     <row r="149">
@@ -4310,7 +4310,7 @@
         <v>-6730.011221111111</v>
       </c>
       <c r="G155" t="n">
-        <v>-6737.968847623473</v>
+        <v>-6737.968847623474</v>
       </c>
     </row>
     <row r="156">
@@ -4354,13 +4354,13 @@
         <v>-362.56642406</v>
       </c>
       <c r="E157" t="n">
-        <v>-363.3016557216392</v>
+        <v>-363.3016557216393</v>
       </c>
       <c r="F157" t="n">
         <v>-6714.193038148148</v>
       </c>
       <c r="G157" t="n">
-        <v>-6727.808439289615</v>
+        <v>-6727.808439289617</v>
       </c>
     </row>
     <row r="158">
@@ -4410,7 +4410,7 @@
         <v>-6870.915102592593</v>
       </c>
       <c r="G159" t="n">
-        <v>-6886.36486849031</v>
+        <v>-6886.364868490309</v>
       </c>
     </row>
     <row r="160">
@@ -4460,7 +4460,7 @@
         <v>-6753.823457592592</v>
       </c>
       <c r="G161" t="n">
-        <v>-6765.872973401757</v>
+        <v>-6765.872973401758</v>
       </c>
     </row>
     <row r="162">
@@ -4504,13 +4504,13 @@
         <v>-122.80565701</v>
       </c>
       <c r="E163" t="n">
-        <v>-121.3721357271583</v>
+        <v>-121.3721357271584</v>
       </c>
       <c r="F163" t="n">
         <v>-6822.536500555556</v>
       </c>
       <c r="G163" t="n">
-        <v>-6742.896429286575</v>
+        <v>-6742.896429286576</v>
       </c>
     </row>
     <row r="164">
@@ -4529,13 +4529,13 @@
         <v>-364.035281</v>
       </c>
       <c r="E164" t="n">
-        <v>-364.9406146994786</v>
+        <v>-364.9406146994785</v>
       </c>
       <c r="F164" t="n">
         <v>-6741.394092592593</v>
       </c>
       <c r="G164" t="n">
-        <v>-6758.159531471826</v>
+        <v>-6758.159531471825</v>
       </c>
     </row>
     <row r="165">
@@ -4554,13 +4554,13 @@
         <v>-364.95483665</v>
       </c>
       <c r="E165" t="n">
-        <v>-365.7755289575667</v>
+        <v>-365.7755289575668</v>
       </c>
       <c r="F165" t="n">
         <v>-6758.422900925926</v>
       </c>
       <c r="G165" t="n">
-        <v>-6773.620906621606</v>
+        <v>-6773.620906621607</v>
       </c>
     </row>
     <row r="166">
@@ -4579,13 +4579,13 @@
         <v>-123.43375618</v>
       </c>
       <c r="E166" t="n">
-        <v>-122.025453800471</v>
+        <v>-122.0254538004711</v>
       </c>
       <c r="F166" t="n">
         <v>-6857.430898888889</v>
       </c>
       <c r="G166" t="n">
-        <v>-6779.191877803946</v>
+        <v>-6779.191877803948</v>
       </c>
     </row>
     <row r="167">
@@ -4635,7 +4635,7 @@
         <v>-6740.186312037037</v>
       </c>
       <c r="G168" t="n">
-        <v>-6762.073021073589</v>
+        <v>-6762.073021073588</v>
       </c>
     </row>
     <row r="169">
@@ -4760,7 +4760,7 @@
         <v>-6717.623897962963</v>
       </c>
       <c r="G173" t="n">
-        <v>-6730.496192630714</v>
+        <v>-6730.496192630716</v>
       </c>
     </row>
     <row r="174">
@@ -4785,7 +4785,7 @@
         <v>-6837.48243</v>
       </c>
       <c r="G174" t="n">
-        <v>-6744.872025512329</v>
+        <v>-6744.87202551233</v>
       </c>
     </row>
     <row r="175">
@@ -4835,7 +4835,7 @@
         <v>-6834.667679444445</v>
       </c>
       <c r="G176" t="n">
-        <v>-6750.454404835117</v>
+        <v>-6750.454404835119</v>
       </c>
     </row>
     <row r="177">
@@ -4854,13 +4854,13 @@
         <v>-123.58707573</v>
       </c>
       <c r="E177" t="n">
-        <v>-122.3085696619095</v>
+        <v>-122.3085696619096</v>
       </c>
       <c r="F177" t="n">
         <v>-6865.948651666667</v>
       </c>
       <c r="G177" t="n">
-        <v>-6794.920536772752</v>
+        <v>-6794.920536772753</v>
       </c>
     </row>
     <row r="178">
@@ -4885,7 +4885,7 @@
         <v>-6718.793581666667</v>
       </c>
       <c r="G178" t="n">
-        <v>-6646.302258678828</v>
+        <v>-6646.30225867883</v>
       </c>
     </row>
     <row r="179">
@@ -4910,7 +4910,7 @@
         <v>-6783.603670185186</v>
       </c>
       <c r="G179" t="n">
-        <v>-6797.294409794709</v>
+        <v>-6797.29440979471</v>
       </c>
     </row>
     <row r="180">
@@ -4929,13 +4929,13 @@
         <v>-121.0848282</v>
       </c>
       <c r="E180" t="n">
-        <v>-119.656803807489</v>
+        <v>-119.6568038074891</v>
       </c>
       <c r="F180" t="n">
         <v>-6726.9349</v>
       </c>
       <c r="G180" t="n">
-        <v>-6647.600211527169</v>
+        <v>-6647.60021152717</v>
       </c>
     </row>
     <row r="181">
@@ -4985,7 +4985,7 @@
         <v>-6839.787872222222</v>
       </c>
       <c r="G182" t="n">
-        <v>-6752.128279006251</v>
+        <v>-6752.128279006252</v>
       </c>
     </row>
     <row r="183">
@@ -5004,13 +5004,13 @@
         <v>-117.30923366</v>
       </c>
       <c r="E183" t="n">
-        <v>-117.1221181529108</v>
+        <v>-117.1221181529109</v>
       </c>
       <c r="F183" t="n">
         <v>-7331.82710375</v>
       </c>
       <c r="G183" t="n">
-        <v>-7320.132384556927</v>
+        <v>-7320.132384556929</v>
       </c>
     </row>
     <row r="184">
@@ -5110,7 +5110,7 @@
         <v>-7439.337563749999</v>
       </c>
       <c r="G187" t="n">
-        <v>-7433.117358871893</v>
+        <v>-7433.117358871894</v>
       </c>
     </row>
     <row r="188">
@@ -5135,7 +5135,7 @@
         <v>-7398.061030625</v>
       </c>
       <c r="G188" t="n">
-        <v>-7389.41803807085</v>
+        <v>-7389.418038070851</v>
       </c>
     </row>
     <row r="189">
@@ -5179,13 +5179,13 @@
         <v>-127.76199014</v>
       </c>
       <c r="E190" t="n">
-        <v>-128.2368811596605</v>
+        <v>-128.2368811596604</v>
       </c>
       <c r="F190" t="n">
         <v>-7985.12438375</v>
       </c>
       <c r="G190" t="n">
-        <v>-8014.805072478779</v>
+        <v>-8014.805072478777</v>
       </c>
     </row>
     <row r="191">
@@ -5260,7 +5260,7 @@
         <v>-7996.698743749999</v>
       </c>
       <c r="G193" t="n">
-        <v>-8023.083340579135</v>
+        <v>-8023.083340579136</v>
       </c>
     </row>
     <row r="194">
@@ -5279,13 +5279,13 @@
         <v>-128.10507773</v>
       </c>
       <c r="E194" t="n">
-        <v>-128.4470838466717</v>
+        <v>-128.4470838466718</v>
       </c>
       <c r="F194" t="n">
         <v>-8006.567358125</v>
       </c>
       <c r="G194" t="n">
-        <v>-8027.942740416984</v>
+        <v>-8027.942740416986</v>
       </c>
     </row>
     <row r="195">
@@ -5460,7 +5460,7 @@
         <v>-7758.30833875</v>
       </c>
       <c r="G201" t="n">
-        <v>-7748.812407009507</v>
+        <v>-7748.812407009508</v>
       </c>
     </row>
     <row r="202">
@@ -5485,7 +5485,7 @@
         <v>-7669.8874375</v>
       </c>
       <c r="G202" t="n">
-        <v>-7660.331739080919</v>
+        <v>-7660.33173908092</v>
       </c>
     </row>
     <row r="203">
@@ -5510,7 +5510,7 @@
         <v>-7687.946486875</v>
       </c>
       <c r="G203" t="n">
-        <v>-7676.597854044147</v>
+        <v>-7676.597854044149</v>
       </c>
     </row>
     <row r="204">
@@ -5529,13 +5529,13 @@
         <v>-122.06782885</v>
       </c>
       <c r="E204" t="n">
-        <v>-121.8656776189735</v>
+        <v>-121.8656776189736</v>
       </c>
       <c r="F204" t="n">
         <v>-7629.239303124999</v>
       </c>
       <c r="G204" t="n">
-        <v>-7616.604851185847</v>
+        <v>-7616.604851185848</v>
       </c>
     </row>
     <row r="205">
@@ -5675,13 +5675,13 @@
         <v>-356.06789658</v>
       </c>
       <c r="E4" t="n">
-        <v>-356.9529941870293</v>
+        <v>-356.9529941870292</v>
       </c>
       <c r="F4" t="n">
         <v>-6593.849936666667</v>
       </c>
       <c r="G4" t="n">
-        <v>-6610.240633093135</v>
+        <v>-6610.240633093134</v>
       </c>
     </row>
     <row r="5">
@@ -5700,13 +5700,13 @@
         <v>-362.11692484</v>
       </c>
       <c r="E5" t="n">
-        <v>-362.786352506485</v>
+        <v>-362.7863525064851</v>
       </c>
       <c r="F5" t="n">
         <v>-6705.86897851852</v>
       </c>
       <c r="G5" t="n">
-        <v>-6718.26578715713</v>
+        <v>-6718.265787157131</v>
       </c>
     </row>
     <row r="6">
@@ -5806,7 +5806,7 @@
         <v>-6699.46757</v>
       </c>
       <c r="G9" t="n">
-        <v>-6604.002601642107</v>
+        <v>-6604.002601642108</v>
       </c>
     </row>
     <row r="10">
@@ -5825,13 +5825,13 @@
         <v>-355.0396538</v>
       </c>
       <c r="E10" t="n">
-        <v>-355.6522099871881</v>
+        <v>-355.6522099871882</v>
       </c>
       <c r="F10" t="n">
         <v>-6574.808403703703</v>
       </c>
       <c r="G10" t="n">
-        <v>-6586.152036799781</v>
+        <v>-6586.152036799782</v>
       </c>
     </row>
     <row r="11">
@@ -5875,13 +5875,13 @@
         <v>-359.64958881</v>
       </c>
       <c r="E12" t="n">
-        <v>-360.3732749287002</v>
+        <v>-360.3732749287003</v>
       </c>
       <c r="F12" t="n">
         <v>-6660.177570555556</v>
       </c>
       <c r="G12" t="n">
-        <v>-6673.579165346299</v>
+        <v>-6673.579165346301</v>
       </c>
     </row>
     <row r="13">
@@ -5900,13 +5900,13 @@
         <v>-360.30951792</v>
       </c>
       <c r="E13" t="n">
-        <v>-360.8039915251229</v>
+        <v>-360.803991525123</v>
       </c>
       <c r="F13" t="n">
         <v>-6672.39848</v>
       </c>
       <c r="G13" t="n">
-        <v>-6681.555398613385</v>
+        <v>-6681.555398613388</v>
       </c>
     </row>
     <row r="14">
@@ -5931,7 +5931,7 @@
         <v>-6659.996884814815</v>
       </c>
       <c r="G14" t="n">
-        <v>-6671.711512507346</v>
+        <v>-6671.711512507347</v>
       </c>
     </row>
     <row r="15">
@@ -5950,13 +5950,13 @@
         <v>-357.36948484</v>
       </c>
       <c r="E15" t="n">
-        <v>-358.2118210559655</v>
+        <v>-358.2118210559656</v>
       </c>
       <c r="F15" t="n">
         <v>-6617.953422962963</v>
       </c>
       <c r="G15" t="n">
-        <v>-6633.552241777139</v>
+        <v>-6633.55224177714</v>
       </c>
     </row>
     <row r="16">
@@ -5981,7 +5981,7 @@
         <v>-6676.132954074074</v>
       </c>
       <c r="G16" t="n">
-        <v>-6693.184736047324</v>
+        <v>-6693.184736047323</v>
       </c>
     </row>
     <row r="17">
@@ -6100,7 +6100,7 @@
         <v>-352.58836677</v>
       </c>
       <c r="E21" t="n">
-        <v>-353.2580117091504</v>
+        <v>-353.2580117091505</v>
       </c>
       <c r="F21" t="n">
         <v>-6529.414199444444</v>
@@ -6125,13 +6125,13 @@
         <v>-355.98886066</v>
       </c>
       <c r="E22" t="n">
-        <v>-356.7557519549429</v>
+        <v>-356.755751954943</v>
       </c>
       <c r="F22" t="n">
         <v>-6592.386308518518</v>
       </c>
       <c r="G22" t="n">
-        <v>-6606.587999165609</v>
+        <v>-6606.587999165611</v>
       </c>
     </row>
     <row r="23">
@@ -6175,13 +6175,13 @@
         <v>-355.21734672</v>
       </c>
       <c r="E24" t="n">
-        <v>-355.8161057487614</v>
+        <v>-355.8161057487613</v>
       </c>
       <c r="F24" t="n">
         <v>-6578.099013333333</v>
       </c>
       <c r="G24" t="n">
-        <v>-6589.187143495581</v>
+        <v>-6589.18714349558</v>
       </c>
     </row>
     <row r="25">
@@ -6206,7 +6206,7 @@
         <v>-6413.788642777778</v>
       </c>
       <c r="G25" t="n">
-        <v>-6431.922172799082</v>
+        <v>-6431.922172799083</v>
       </c>
     </row>
     <row r="26">
@@ -6231,7 +6231,7 @@
         <v>-6711.944562777778</v>
       </c>
       <c r="G26" t="n">
-        <v>-6630.069406629403</v>
+        <v>-6630.069406629405</v>
       </c>
     </row>
     <row r="27">
@@ -6275,13 +6275,13 @@
         <v>-355.95275363</v>
       </c>
       <c r="E28" t="n">
-        <v>-356.7857620951827</v>
+        <v>-356.7857620951828</v>
       </c>
       <c r="F28" t="n">
         <v>-6591.717659814814</v>
       </c>
       <c r="G28" t="n">
-        <v>-6607.143742503384</v>
+        <v>-6607.143742503385</v>
       </c>
     </row>
     <row r="29">
@@ -6306,7 +6306,7 @@
         <v>-6338.850982037036</v>
       </c>
       <c r="G29" t="n">
-        <v>-6353.066196432668</v>
+        <v>-6353.066196432669</v>
       </c>
     </row>
     <row r="30">
@@ -6331,7 +6331,7 @@
         <v>-6571.443849814815</v>
       </c>
       <c r="G30" t="n">
-        <v>-6579.115446469899</v>
+        <v>-6579.1154464699</v>
       </c>
     </row>
     <row r="31">
@@ -6406,7 +6406,7 @@
         <v>-6540.25940574074</v>
       </c>
       <c r="G33" t="n">
-        <v>-6554.482353331725</v>
+        <v>-6554.482353331726</v>
       </c>
     </row>
     <row r="34">
@@ -6450,13 +6450,13 @@
         <v>-357.30992288</v>
       </c>
       <c r="E35" t="n">
-        <v>-358.0357307145593</v>
+        <v>-358.0357307145594</v>
       </c>
       <c r="F35" t="n">
         <v>-6616.850423703703</v>
       </c>
       <c r="G35" t="n">
-        <v>-6630.291309528876</v>
+        <v>-6630.291309528878</v>
       </c>
     </row>
     <row r="36">
@@ -6506,7 +6506,7 @@
         <v>-6608.123420185184</v>
       </c>
       <c r="G37" t="n">
-        <v>-6626.443566375739</v>
+        <v>-6626.44356637574</v>
       </c>
     </row>
     <row r="38">
@@ -6600,13 +6600,13 @@
         <v>-360.47912628</v>
       </c>
       <c r="E41" t="n">
-        <v>-361.1174639905843</v>
+        <v>-361.1174639905844</v>
       </c>
       <c r="F41" t="n">
         <v>-6675.539375555556</v>
       </c>
       <c r="G41" t="n">
-        <v>-6687.36044427008</v>
+        <v>-6687.360444270082</v>
       </c>
     </row>
     <row r="42">
@@ -6700,13 +6700,13 @@
         <v>-351.65762208</v>
       </c>
       <c r="E45" t="n">
-        <v>-352.4077012999642</v>
+        <v>-352.4077012999643</v>
       </c>
       <c r="F45" t="n">
         <v>-6512.178186666667</v>
       </c>
       <c r="G45" t="n">
-        <v>-6526.06854259193</v>
+        <v>-6526.068542591931</v>
       </c>
     </row>
     <row r="46">
@@ -6731,7 +6731,7 @@
         <v>-6633.513137777778</v>
       </c>
       <c r="G46" t="n">
-        <v>-6650.822376032981</v>
+        <v>-6650.822376032982</v>
       </c>
     </row>
     <row r="47">
@@ -6750,13 +6750,13 @@
         <v>-354.80805708</v>
       </c>
       <c r="E47" t="n">
-        <v>-355.6075244082413</v>
+        <v>-355.6075244082414</v>
       </c>
       <c r="F47" t="n">
         <v>-6570.519575555555</v>
       </c>
       <c r="G47" t="n">
-        <v>-6585.324526078543</v>
+        <v>-6585.324526078544</v>
       </c>
     </row>
     <row r="48">
@@ -6850,13 +6850,13 @@
         <v>-361.00187758</v>
       </c>
       <c r="E51" t="n">
-        <v>-361.9815707799807</v>
+        <v>-361.9815707799808</v>
       </c>
       <c r="F51" t="n">
         <v>-6685.219955185185</v>
       </c>
       <c r="G51" t="n">
-        <v>-6703.362421851494</v>
+        <v>-6703.362421851495</v>
       </c>
     </row>
     <row r="52">
@@ -6906,7 +6906,7 @@
         <v>-6682.77031</v>
       </c>
       <c r="G53" t="n">
-        <v>-6687.900516199366</v>
+        <v>-6687.900516199367</v>
       </c>
     </row>
     <row r="54">
@@ -6931,7 +6931,7 @@
         <v>-6628.397512962963</v>
       </c>
       <c r="G54" t="n">
-        <v>-6644.556852700416</v>
+        <v>-6644.556852700417</v>
       </c>
     </row>
     <row r="55">
@@ -6950,13 +6950,13 @@
         <v>-358.5348658</v>
       </c>
       <c r="E55" t="n">
-        <v>-359.5403114186554</v>
+        <v>-359.5403114186556</v>
       </c>
       <c r="F55" t="n">
         <v>-6639.534551851852</v>
       </c>
       <c r="G55" t="n">
-        <v>-6658.153915160286</v>
+        <v>-6658.153915160288</v>
       </c>
     </row>
     <row r="56">
@@ -6981,7 +6981,7 @@
         <v>-6520.350406111112</v>
       </c>
       <c r="G56" t="n">
-        <v>-6529.4709315058</v>
+        <v>-6529.470931505801</v>
       </c>
     </row>
     <row r="57">
@@ -7000,13 +7000,13 @@
         <v>-362.37033473</v>
       </c>
       <c r="E57" t="n">
-        <v>-363.0242378931013</v>
+        <v>-363.0242378931014</v>
       </c>
       <c r="F57" t="n">
         <v>-6710.561754259259</v>
       </c>
       <c r="G57" t="n">
-        <v>-6722.671072094467</v>
+        <v>-6722.671072094469</v>
       </c>
     </row>
     <row r="58">
@@ -7025,13 +7025,13 @@
         <v>-362.17224142</v>
       </c>
       <c r="E58" t="n">
-        <v>-362.880198794152</v>
+        <v>-362.8801987941521</v>
       </c>
       <c r="F58" t="n">
         <v>-6706.893359629629</v>
       </c>
       <c r="G58" t="n">
-        <v>-6720.003681373185</v>
+        <v>-6720.003681373187</v>
       </c>
     </row>
     <row r="59">
@@ -7075,13 +7075,13 @@
         <v>-357.29565214</v>
       </c>
       <c r="E60" t="n">
-        <v>-357.8724487371209</v>
+        <v>-357.872448737121</v>
       </c>
       <c r="F60" t="n">
         <v>-6616.586150740741</v>
       </c>
       <c r="G60" t="n">
-        <v>-6627.267569205943</v>
+        <v>-6627.267569205944</v>
       </c>
     </row>
     <row r="61">
@@ -7106,7 +7106,7 @@
         <v>-6692.750853703705</v>
       </c>
       <c r="G61" t="n">
-        <v>-6700.054905023996</v>
+        <v>-6700.054905023997</v>
       </c>
     </row>
     <row r="62">
@@ -7125,13 +7125,13 @@
         <v>-359.72982609</v>
       </c>
       <c r="E62" t="n">
-        <v>-360.1498900661695</v>
+        <v>-360.1498900661696</v>
       </c>
       <c r="F62" t="n">
         <v>-6661.663446111112</v>
       </c>
       <c r="G62" t="n">
-        <v>-6669.442408632768</v>
+        <v>-6669.44240863277</v>
       </c>
     </row>
     <row r="63">
@@ -7206,7 +7206,7 @@
         <v>-6673.96832962963</v>
       </c>
       <c r="G65" t="n">
-        <v>-6684.404071198319</v>
+        <v>-6684.404071198321</v>
       </c>
     </row>
     <row r="66">
@@ -7231,7 +7231,7 @@
         <v>-6616.321117407408</v>
       </c>
       <c r="G66" t="n">
-        <v>-6634.617461697915</v>
+        <v>-6634.617461697914</v>
       </c>
     </row>
     <row r="67">
@@ -7250,13 +7250,13 @@
         <v>-360.60102876</v>
       </c>
       <c r="E67" t="n">
-        <v>-361.1956441695064</v>
+        <v>-361.1956441695065</v>
       </c>
       <c r="F67" t="n">
         <v>-6677.796828888889</v>
       </c>
       <c r="G67" t="n">
-        <v>-6688.808225361229</v>
+        <v>-6688.80822536123</v>
       </c>
     </row>
     <row r="68">
@@ -7300,13 +7300,13 @@
         <v>-354.25473134</v>
       </c>
       <c r="E69" t="n">
-        <v>-355.2212562654361</v>
+        <v>-355.2212562654362</v>
       </c>
       <c r="F69" t="n">
         <v>-6560.272802592593</v>
       </c>
       <c r="G69" t="n">
-        <v>-6578.171412322891</v>
+        <v>-6578.171412322892</v>
       </c>
     </row>
     <row r="70">
@@ -7331,7 +7331,7 @@
         <v>-6707.832794999999</v>
       </c>
       <c r="G70" t="n">
-        <v>-6612.219512127175</v>
+        <v>-6612.219512127176</v>
       </c>
     </row>
     <row r="71">
@@ -7350,13 +7350,13 @@
         <v>-120.17862857</v>
       </c>
       <c r="E71" t="n">
-        <v>-118.7765419063564</v>
+        <v>-118.7765419063565</v>
       </c>
       <c r="F71" t="n">
         <v>-6676.590476111111</v>
       </c>
       <c r="G71" t="n">
-        <v>-6598.696772575358</v>
+        <v>-6598.69677257536</v>
       </c>
     </row>
     <row r="72">
@@ -7375,13 +7375,13 @@
         <v>-358.25200504</v>
       </c>
       <c r="E72" t="n">
-        <v>-358.8672355049002</v>
+        <v>-358.8672355049003</v>
       </c>
       <c r="F72" t="n">
         <v>-6634.296389629629</v>
       </c>
       <c r="G72" t="n">
-        <v>-6645.689546387041</v>
+        <v>-6645.689546387043</v>
       </c>
     </row>
     <row r="73">
@@ -7400,13 +7400,13 @@
         <v>-345.68177126</v>
       </c>
       <c r="E73" t="n">
-        <v>-346.1178033781255</v>
+        <v>-346.1178033781256</v>
       </c>
       <c r="F73" t="n">
         <v>-6401.514282592593</v>
       </c>
       <c r="G73" t="n">
-        <v>-6409.588951446769</v>
+        <v>-6409.58895144677</v>
       </c>
     </row>
     <row r="74">
@@ -7425,13 +7425,13 @@
         <v>-359.5675028</v>
       </c>
       <c r="E74" t="n">
-        <v>-360.199296053779</v>
+        <v>-360.1992960537791</v>
       </c>
       <c r="F74" t="n">
         <v>-6658.65745925926</v>
       </c>
       <c r="G74" t="n">
-        <v>-6670.357334329241</v>
+        <v>-6670.357334329242</v>
       </c>
     </row>
     <row r="75">
@@ -7475,13 +7475,13 @@
         <v>-116.22590605</v>
       </c>
       <c r="E76" t="n">
-        <v>-114.635578869445</v>
+        <v>-114.6355788694451</v>
       </c>
       <c r="F76" t="n">
         <v>-6456.994780555556</v>
       </c>
       <c r="G76" t="n">
-        <v>-6368.643270524724</v>
+        <v>-6368.643270524725</v>
       </c>
     </row>
     <row r="77">
@@ -7575,13 +7575,13 @@
         <v>-361.44721308</v>
       </c>
       <c r="E80" t="n">
-        <v>-362.4425063569064</v>
+        <v>-362.4425063569063</v>
       </c>
       <c r="F80" t="n">
         <v>-6693.466908888888</v>
       </c>
       <c r="G80" t="n">
-        <v>-6711.898265868636</v>
+        <v>-6711.898265868635</v>
       </c>
     </row>
     <row r="81">
@@ -7631,7 +7631,7 @@
         <v>-6488.593758333333</v>
       </c>
       <c r="G82" t="n">
-        <v>-6396.603154013086</v>
+        <v>-6396.603154013088</v>
       </c>
     </row>
     <row r="83">
@@ -7675,13 +7675,13 @@
         <v>-347.45164105</v>
       </c>
       <c r="E84" t="n">
-        <v>-347.9806820444998</v>
+        <v>-347.9806820444999</v>
       </c>
       <c r="F84" t="n">
         <v>-6434.289649074074</v>
       </c>
       <c r="G84" t="n">
-        <v>-6444.086704527774</v>
+        <v>-6444.086704527775</v>
       </c>
     </row>
     <row r="85">
@@ -7700,7 +7700,7 @@
         <v>-353.56670719</v>
       </c>
       <c r="E85" t="n">
-        <v>-354.4619947825852</v>
+        <v>-354.4619947825853</v>
       </c>
       <c r="F85" t="n">
         <v>-6547.531614629629</v>
@@ -7725,13 +7725,13 @@
         <v>-359.72823077</v>
       </c>
       <c r="E86" t="n">
-        <v>-360.3915773148599</v>
+        <v>-360.39157731486</v>
       </c>
       <c r="F86" t="n">
         <v>-6661.633903148148</v>
       </c>
       <c r="G86" t="n">
-        <v>-6673.918098423333</v>
+        <v>-6673.918098423334</v>
       </c>
     </row>
     <row r="87">
@@ -7806,7 +7806,7 @@
         <v>-6608.85421</v>
       </c>
       <c r="G89" t="n">
-        <v>-6630.570357644301</v>
+        <v>-6630.570357644302</v>
       </c>
     </row>
     <row r="90">
@@ -7825,13 +7825,13 @@
         <v>-357.3736637</v>
       </c>
       <c r="E90" t="n">
-        <v>-357.6333684392426</v>
+        <v>-357.6333684392427</v>
       </c>
       <c r="F90" t="n">
         <v>-6618.03080925926</v>
       </c>
       <c r="G90" t="n">
-        <v>-6622.840156282271</v>
+        <v>-6622.840156282273</v>
       </c>
     </row>
     <row r="91">
@@ -7856,7 +7856,7 @@
         <v>-6351.866335000001</v>
       </c>
       <c r="G91" t="n">
-        <v>-6289.625978084359</v>
+        <v>-6289.625978084361</v>
       </c>
     </row>
     <row r="92">
@@ -8000,13 +8000,13 @@
         <v>-353.59017061</v>
       </c>
       <c r="E97" t="n">
-        <v>-354.3862619598779</v>
+        <v>-354.386261959878</v>
       </c>
       <c r="F97" t="n">
         <v>-6547.966122407407</v>
       </c>
       <c r="G97" t="n">
-        <v>-6562.708554812554</v>
+        <v>-6562.708554812556</v>
       </c>
     </row>
     <row r="98">
@@ -8025,13 +8025,13 @@
         <v>-341.07639222</v>
       </c>
       <c r="E98" t="n">
-        <v>-342.1598472246727</v>
+        <v>-342.1598472246728</v>
       </c>
       <c r="F98" t="n">
         <v>-6316.229485555556</v>
       </c>
       <c r="G98" t="n">
-        <v>-6336.293467123569</v>
+        <v>-6336.29346712357</v>
       </c>
     </row>
     <row r="99">
@@ -8125,13 +8125,13 @@
         <v>-360.11042278</v>
       </c>
       <c r="E102" t="n">
-        <v>-360.5622151338652</v>
+        <v>-360.5622151338653</v>
       </c>
       <c r="F102" t="n">
         <v>-6668.711532962963</v>
       </c>
       <c r="G102" t="n">
-        <v>-6677.078058034541</v>
+        <v>-6677.078058034543</v>
       </c>
     </row>
     <row r="103">
@@ -8175,13 +8175,13 @@
         <v>-356.72071018</v>
       </c>
       <c r="E104" t="n">
-        <v>-357.802723772566</v>
+        <v>-357.8027237725661</v>
       </c>
       <c r="F104" t="n">
         <v>-6605.939077407408</v>
       </c>
       <c r="G104" t="n">
-        <v>-6625.976366158629</v>
+        <v>-6625.976366158631</v>
       </c>
     </row>
     <row r="105">
@@ -8250,13 +8250,13 @@
         <v>-360.57348558</v>
       </c>
       <c r="E107" t="n">
-        <v>-361.4948578651444</v>
+        <v>-361.4948578651445</v>
       </c>
       <c r="F107" t="n">
         <v>-6677.286770000001</v>
       </c>
       <c r="G107" t="n">
-        <v>-6694.349219724896</v>
+        <v>-6694.349219724897</v>
       </c>
     </row>
     <row r="108">
@@ -8281,7 +8281,7 @@
         <v>-6537.778917037037</v>
       </c>
       <c r="G108" t="n">
-        <v>-6556.518335497505</v>
+        <v>-6556.518335497506</v>
       </c>
     </row>
     <row r="109">
@@ -8325,13 +8325,13 @@
         <v>-359.42987083</v>
       </c>
       <c r="E110" t="n">
-        <v>-359.9660578084381</v>
+        <v>-359.9660578084379</v>
       </c>
       <c r="F110" t="n">
         <v>-6656.108719074075</v>
       </c>
       <c r="G110" t="n">
-        <v>-6666.038107563667</v>
+        <v>-6666.038107563666</v>
       </c>
     </row>
     <row r="111">
@@ -8350,13 +8350,13 @@
         <v>-357.6263799</v>
       </c>
       <c r="E111" t="n">
-        <v>-358.2640736936893</v>
+        <v>-358.2640736936892</v>
       </c>
       <c r="F111" t="n">
         <v>-6622.710738888889</v>
       </c>
       <c r="G111" t="n">
-        <v>-6634.519883216469</v>
+        <v>-6634.519883216468</v>
       </c>
     </row>
     <row r="112">
@@ -8381,7 +8381,7 @@
         <v>-6677.026069444445</v>
       </c>
       <c r="G112" t="n">
-        <v>-6690.893022061456</v>
+        <v>-6690.893022061455</v>
       </c>
     </row>
     <row r="113">
@@ -8400,13 +8400,13 @@
         <v>-353.61915703</v>
       </c>
       <c r="E113" t="n">
-        <v>-354.5149510199618</v>
+        <v>-354.5149510199619</v>
       </c>
       <c r="F113" t="n">
         <v>-6548.502907962963</v>
       </c>
       <c r="G113" t="n">
-        <v>-6565.091685554848</v>
+        <v>-6565.091685554849</v>
       </c>
     </row>
     <row r="114">
@@ -8475,13 +8475,13 @@
         <v>-362.13216511</v>
       </c>
       <c r="E116" t="n">
-        <v>-362.5078600729984</v>
+        <v>-362.5078600729985</v>
       </c>
       <c r="F116" t="n">
         <v>-6706.151205740741</v>
       </c>
       <c r="G116" t="n">
-        <v>-6713.108519870341</v>
+        <v>-6713.108519870344</v>
       </c>
     </row>
     <row r="117">
@@ -8506,7 +8506,7 @@
         <v>-6616.29926537037</v>
       </c>
       <c r="G117" t="n">
-        <v>-6628.87846057784</v>
+        <v>-6628.878460577841</v>
       </c>
     </row>
     <row r="118">
@@ -8575,13 +8575,13 @@
         <v>-361.38015447</v>
       </c>
       <c r="E120" t="n">
-        <v>-362.1362570705439</v>
+        <v>-362.136257070544</v>
       </c>
       <c r="F120" t="n">
         <v>-6692.225082777777</v>
       </c>
       <c r="G120" t="n">
-        <v>-6706.22698278785</v>
+        <v>-6706.226982787853</v>
       </c>
     </row>
     <row r="121">
@@ -8606,7 +8606,7 @@
         <v>-6684.163082222221</v>
       </c>
       <c r="G121" t="n">
-        <v>-6699.3931204096</v>
+        <v>-6699.393120409601</v>
       </c>
     </row>
     <row r="122">
@@ -8650,13 +8650,13 @@
         <v>-119.65101334</v>
       </c>
       <c r="E123" t="n">
-        <v>-118.2882935804134</v>
+        <v>-118.2882935804135</v>
       </c>
       <c r="F123" t="n">
         <v>-6647.278518888889</v>
       </c>
       <c r="G123" t="n">
-        <v>-6571.571865578524</v>
+        <v>-6571.571865578526</v>
       </c>
     </row>
     <row r="124">
@@ -8756,7 +8756,7 @@
         <v>-6583.545548148149</v>
       </c>
       <c r="G127" t="n">
-        <v>-6584.778144910232</v>
+        <v>-6584.778144910231</v>
       </c>
     </row>
     <row r="128">
@@ -8775,13 +8775,13 @@
         <v>-345.53105924</v>
       </c>
       <c r="E128" t="n">
-        <v>-346.1503939894889</v>
+        <v>-346.1503939894888</v>
       </c>
       <c r="F128" t="n">
         <v>-6398.723319259258</v>
       </c>
       <c r="G128" t="n">
-        <v>-6410.192481286831</v>
+        <v>-6410.19248128683</v>
       </c>
     </row>
     <row r="129">
@@ -8850,13 +8850,13 @@
         <v>-346.60481576</v>
       </c>
       <c r="E131" t="n">
-        <v>-347.0642761562748</v>
+        <v>-347.0642761562749</v>
       </c>
       <c r="F131" t="n">
         <v>-6418.60769925926</v>
       </c>
       <c r="G131" t="n">
-        <v>-6427.1162251162</v>
+        <v>-6427.116225116201</v>
       </c>
     </row>
     <row r="132">
@@ -8925,13 +8925,13 @@
         <v>-358.62694514</v>
       </c>
       <c r="E134" t="n">
-        <v>-359.2970117893739</v>
+        <v>-359.297011789374</v>
       </c>
       <c r="F134" t="n">
         <v>-6641.239724814815</v>
       </c>
       <c r="G134" t="n">
-        <v>-6653.648366469886</v>
+        <v>-6653.648366469889</v>
       </c>
     </row>
     <row r="135">
@@ -8956,7 +8956,7 @@
         <v>-6633.717807962963</v>
       </c>
       <c r="G135" t="n">
-        <v>-6635.960590179092</v>
+        <v>-6635.960590179094</v>
       </c>
     </row>
     <row r="136">
@@ -9031,7 +9031,7 @@
         <v>-6704.49773462963</v>
       </c>
       <c r="G138" t="n">
-        <v>-6714.111690489087</v>
+        <v>-6714.111690489088</v>
       </c>
     </row>
     <row r="139">
@@ -9050,13 +9050,13 @@
         <v>-358.56445817</v>
       </c>
       <c r="E139" t="n">
-        <v>-359.410315786779</v>
+        <v>-359.4103157867791</v>
       </c>
       <c r="F139" t="n">
         <v>-6640.082558703703</v>
       </c>
       <c r="G139" t="n">
-        <v>-6655.746588644055</v>
+        <v>-6655.746588644056</v>
       </c>
     </row>
     <row r="140">
@@ -9125,13 +9125,13 @@
         <v>-361.80382835</v>
       </c>
       <c r="E142" t="n">
-        <v>-362.4930096173428</v>
+        <v>-362.4930096173427</v>
       </c>
       <c r="F142" t="n">
         <v>-6700.070895370371</v>
       </c>
       <c r="G142" t="n">
-        <v>-6712.833511432273</v>
+        <v>-6712.833511432272</v>
       </c>
     </row>
     <row r="143">
@@ -9150,13 +9150,13 @@
         <v>-349.44108375</v>
       </c>
       <c r="E143" t="n">
-        <v>-350.1471713431104</v>
+        <v>-350.1471713431105</v>
       </c>
       <c r="F143" t="n">
         <v>-6471.131180555555</v>
       </c>
       <c r="G143" t="n">
-        <v>-6484.206876724267</v>
+        <v>-6484.206876724268</v>
       </c>
     </row>
     <row r="144">
@@ -9181,7 +9181,7 @@
         <v>-6481.306668703703</v>
       </c>
       <c r="G144" t="n">
-        <v>-6500.767032899445</v>
+        <v>-6500.767032899446</v>
       </c>
     </row>
     <row r="145">
@@ -9200,13 +9200,13 @@
         <v>-351.01881719</v>
       </c>
       <c r="E145" t="n">
-        <v>-351.4198490472595</v>
+        <v>-351.4198490472596</v>
       </c>
       <c r="F145" t="n">
         <v>-6500.348466481481</v>
       </c>
       <c r="G145" t="n">
-        <v>-6507.774982356657</v>
+        <v>-6507.774982356659</v>
       </c>
     </row>
     <row r="146">
@@ -9225,13 +9225,13 @@
         <v>-358.16349788</v>
       </c>
       <c r="E146" t="n">
-        <v>-358.6665613937567</v>
+        <v>-358.6665613937568</v>
       </c>
       <c r="F146" t="n">
         <v>-6632.657368148149</v>
       </c>
       <c r="G146" t="n">
-        <v>-6641.973359143642</v>
+        <v>-6641.973359143645</v>
       </c>
     </row>
     <row r="147">
@@ -9275,13 +9275,13 @@
         <v>-347.99439697</v>
       </c>
       <c r="E148" t="n">
-        <v>-349.1693595583554</v>
+        <v>-349.1693595583553</v>
       </c>
       <c r="F148" t="n">
         <v>-6444.340684629629</v>
       </c>
       <c r="G148" t="n">
-        <v>-6466.099251080655</v>
+        <v>-6466.099251080654</v>
       </c>
     </row>
     <row r="149">
@@ -9306,7 +9306,7 @@
         <v>-6674.405261296296</v>
       </c>
       <c r="G149" t="n">
-        <v>-6684.553337981064</v>
+        <v>-6684.553337981065</v>
       </c>
     </row>
     <row r="150">
@@ -9356,7 +9356,7 @@
         <v>-6518.427655</v>
       </c>
       <c r="G151" t="n">
-        <v>-6431.120167394118</v>
+        <v>-6431.12016739412</v>
       </c>
     </row>
     <row r="152">
@@ -9375,13 +9375,13 @@
         <v>-355.84612331</v>
       </c>
       <c r="E152" t="n">
-        <v>-356.3204630376619</v>
+        <v>-356.3204630376618</v>
       </c>
       <c r="F152" t="n">
         <v>-6589.743024259259</v>
       </c>
       <c r="G152" t="n">
-        <v>-6598.527093290035</v>
+        <v>-6598.527093290033</v>
       </c>
     </row>
     <row r="153">
@@ -9400,13 +9400,13 @@
         <v>-360.34569153</v>
       </c>
       <c r="E153" t="n">
-        <v>-360.836662515655</v>
+        <v>-360.8366625156551</v>
       </c>
       <c r="F153" t="n">
         <v>-6673.068361666667</v>
       </c>
       <c r="G153" t="n">
-        <v>-6682.160416956573</v>
+        <v>-6682.160416956575</v>
       </c>
     </row>
     <row r="154">
@@ -9450,13 +9450,13 @@
         <v>-351.520342</v>
       </c>
       <c r="E155" t="n">
-        <v>-352.1350199172733</v>
+        <v>-352.1350199172732</v>
       </c>
       <c r="F155" t="n">
         <v>-6509.635962962963</v>
       </c>
       <c r="G155" t="n">
-        <v>-6521.018887356912</v>
+        <v>-6521.018887356911</v>
       </c>
     </row>
     <row r="156">
@@ -9475,13 +9475,13 @@
         <v>-358.19964863</v>
       </c>
       <c r="E156" t="n">
-        <v>-358.6300129678536</v>
+        <v>-358.6300129678537</v>
       </c>
       <c r="F156" t="n">
         <v>-6633.326826481481</v>
       </c>
       <c r="G156" t="n">
-        <v>-6641.296536441734</v>
+        <v>-6641.296536441735</v>
       </c>
     </row>
     <row r="157">
@@ -9525,13 +9525,13 @@
         <v>-357.07776735</v>
       </c>
       <c r="E158" t="n">
-        <v>-358.1099447854353</v>
+        <v>-358.1099447854354</v>
       </c>
       <c r="F158" t="n">
         <v>-6612.551247222222</v>
       </c>
       <c r="G158" t="n">
-        <v>-6631.665644174728</v>
+        <v>-6631.665644174729</v>
       </c>
     </row>
     <row r="159">
@@ -9581,7 +9581,7 @@
         <v>-6639.420017777778</v>
       </c>
       <c r="G160" t="n">
-        <v>-6647.507510984235</v>
+        <v>-6647.507510984236</v>
       </c>
     </row>
     <row r="161">
@@ -9600,13 +9600,13 @@
         <v>-355.10697324</v>
       </c>
       <c r="E161" t="n">
-        <v>-355.805291823863</v>
+        <v>-355.8052918238631</v>
       </c>
       <c r="F161" t="n">
         <v>-6576.055060000001</v>
       </c>
       <c r="G161" t="n">
-        <v>-6588.986885627092</v>
+        <v>-6588.986885627093</v>
       </c>
     </row>
     <row r="162">
@@ -9625,13 +9625,13 @@
         <v>-120.81618523</v>
       </c>
       <c r="E162" t="n">
-        <v>-119.3922289764823</v>
+        <v>-119.3922289764824</v>
       </c>
       <c r="F162" t="n">
         <v>-6712.010290555556</v>
       </c>
       <c r="G162" t="n">
-        <v>-6632.901609804573</v>
+        <v>-6632.901609804577</v>
       </c>
     </row>
     <row r="163">
@@ -9750,13 +9750,13 @@
         <v>-352.46805444</v>
       </c>
       <c r="E167" t="n">
-        <v>-353.1523753317095</v>
+        <v>-353.1523753317097</v>
       </c>
       <c r="F167" t="n">
         <v>-6527.186193333333</v>
       </c>
       <c r="G167" t="n">
-        <v>-6539.858802439066</v>
+        <v>-6539.858802439068</v>
       </c>
     </row>
     <row r="168">
@@ -9800,13 +9800,13 @@
         <v>-351.33761365</v>
       </c>
       <c r="E169" t="n">
-        <v>-352.4257820103476</v>
+        <v>-352.4257820103477</v>
       </c>
       <c r="F169" t="n">
         <v>-6506.252104629629</v>
       </c>
       <c r="G169" t="n">
-        <v>-6526.403370561993</v>
+        <v>-6526.403370561994</v>
       </c>
     </row>
     <row r="170">
@@ -9831,7 +9831,7 @@
         <v>-6524.96741037037</v>
       </c>
       <c r="G170" t="n">
-        <v>-6534.764222612874</v>
+        <v>-6534.764222612875</v>
       </c>
     </row>
     <row r="171">
@@ -9881,7 +9881,7 @@
         <v>-6670.068251666667</v>
       </c>
       <c r="G172" t="n">
-        <v>-6683.123443893769</v>
+        <v>-6683.12344389377</v>
       </c>
     </row>
     <row r="173">
@@ -10000,13 +10000,13 @@
         <v>-362.48597006</v>
       </c>
       <c r="E177" t="n">
-        <v>-363.0336038458439</v>
+        <v>-363.0336038458438</v>
       </c>
       <c r="F177" t="n">
         <v>-6712.70314925926</v>
       </c>
       <c r="G177" t="n">
-        <v>-6722.844515663775</v>
+        <v>-6722.844515663774</v>
       </c>
     </row>
     <row r="178">
@@ -10025,13 +10025,13 @@
         <v>-359.20854795</v>
       </c>
       <c r="E178" t="n">
-        <v>-359.7997862092691</v>
+        <v>-359.799786209269</v>
       </c>
       <c r="F178" t="n">
         <v>-6652.010147222223</v>
       </c>
       <c r="G178" t="n">
-        <v>-6662.959003875353</v>
+        <v>-6662.959003875352</v>
       </c>
     </row>
     <row r="179">
@@ -10100,13 +10100,13 @@
         <v>-360.2242802</v>
       </c>
       <c r="E181" t="n">
-        <v>-360.8941162296749</v>
+        <v>-360.894116229675</v>
       </c>
       <c r="F181" t="n">
         <v>-6670.820003703704</v>
       </c>
       <c r="G181" t="n">
-        <v>-6683.224374623609</v>
+        <v>-6683.22437462361</v>
       </c>
     </row>
     <row r="182">
@@ -10125,13 +10125,13 @@
         <v>-360.4803276</v>
       </c>
       <c r="E182" t="n">
-        <v>-361.0385676603124</v>
+        <v>-361.0385676603123</v>
       </c>
       <c r="F182" t="n">
         <v>-6675.561622222222</v>
       </c>
       <c r="G182" t="n">
-        <v>-6685.899401116895</v>
+        <v>-6685.899401116894</v>
       </c>
     </row>
     <row r="183">
@@ -10150,13 +10150,13 @@
         <v>-359.09828233</v>
       </c>
       <c r="E183" t="n">
-        <v>-359.8321631186642</v>
+        <v>-359.8321631186643</v>
       </c>
       <c r="F183" t="n">
         <v>-6649.968191296297</v>
       </c>
       <c r="G183" t="n">
-        <v>-6663.558576271559</v>
+        <v>-6663.55857627156</v>
       </c>
     </row>
     <row r="184">
@@ -10175,13 +10175,13 @@
         <v>-359.89041757</v>
       </c>
       <c r="E184" t="n">
-        <v>-360.5756236232698</v>
+        <v>-360.5756236232699</v>
       </c>
       <c r="F184" t="n">
         <v>-6664.637362407408</v>
       </c>
       <c r="G184" t="n">
-        <v>-6677.326363393886</v>
+        <v>-6677.326363393887</v>
       </c>
     </row>
     <row r="185">
@@ -10200,13 +10200,13 @@
         <v>-361.8094646</v>
       </c>
       <c r="E185" t="n">
-        <v>-362.6093123624146</v>
+        <v>-362.6093123624147</v>
       </c>
       <c r="F185" t="n">
         <v>-6700.175270370371</v>
       </c>
       <c r="G185" t="n">
-        <v>-6714.987265970641</v>
+        <v>-6714.987265970643</v>
       </c>
     </row>
     <row r="186">
@@ -10256,7 +10256,7 @@
         <v>-6628.65737962963</v>
       </c>
       <c r="G187" t="n">
-        <v>-6649.34876774669</v>
+        <v>-6649.348767746692</v>
       </c>
     </row>
     <row r="188">
@@ -10275,13 +10275,13 @@
         <v>-355.42074312</v>
       </c>
       <c r="E188" t="n">
-        <v>-355.6160452080032</v>
+        <v>-355.6160452080033</v>
       </c>
       <c r="F188" t="n">
         <v>-6581.865613333333</v>
       </c>
       <c r="G188" t="n">
-        <v>-6585.482318666727</v>
+        <v>-6585.482318666728</v>
       </c>
     </row>
     <row r="189">
@@ -10325,13 +10325,13 @@
         <v>-355.96990275</v>
       </c>
       <c r="E190" t="n">
-        <v>-356.1805948239515</v>
+        <v>-356.1805948239516</v>
       </c>
       <c r="F190" t="n">
         <v>-6592.035236111111</v>
       </c>
       <c r="G190" t="n">
-        <v>-6595.936941184288</v>
+        <v>-6595.936941184289</v>
       </c>
     </row>
     <row r="191">
@@ -10356,7 +10356,7 @@
         <v>-6474.220371666667</v>
       </c>
       <c r="G191" t="n">
-        <v>-6484.829883845674</v>
+        <v>-6484.829883845673</v>
       </c>
     </row>
     <row r="192">
@@ -10375,13 +10375,13 @@
         <v>-358.81818973</v>
       </c>
       <c r="E192" t="n">
-        <v>-359.4437069362394</v>
+        <v>-359.4437069362395</v>
       </c>
       <c r="F192" t="n">
         <v>-6644.781291296296</v>
       </c>
       <c r="G192" t="n">
-        <v>-6656.364943263692</v>
+        <v>-6656.364943263695</v>
       </c>
     </row>
     <row r="193">
@@ -10525,13 +10525,13 @@
         <v>-358.12975928</v>
       </c>
       <c r="E198" t="n">
-        <v>-358.8431566132163</v>
+        <v>-358.8431566132164</v>
       </c>
       <c r="F198" t="n">
         <v>-6632.032579259259</v>
       </c>
       <c r="G198" t="n">
-        <v>-6645.243640985487</v>
+        <v>-6645.243640985489</v>
       </c>
     </row>
     <row r="199">
@@ -10556,7 +10556,7 @@
         <v>-6710.797518518519</v>
       </c>
       <c r="G199" t="n">
-        <v>-6721.035026982942</v>
+        <v>-6721.035026982943</v>
       </c>
     </row>
     <row r="200">
@@ -10600,13 +10600,13 @@
         <v>-354.76928935</v>
       </c>
       <c r="E201" t="n">
-        <v>-355.5977835646044</v>
+        <v>-355.5977835646045</v>
       </c>
       <c r="F201" t="n">
         <v>-6569.80165462963</v>
       </c>
       <c r="G201" t="n">
-        <v>-6585.144140085267</v>
+        <v>-6585.144140085268</v>
       </c>
     </row>
     <row r="202">
@@ -10625,13 +10625,13 @@
         <v>-361.95135052</v>
       </c>
       <c r="E202" t="n">
-        <v>-362.7045954409256</v>
+        <v>-362.7045954409257</v>
       </c>
       <c r="F202" t="n">
         <v>-6702.802787407407</v>
       </c>
       <c r="G202" t="n">
-        <v>-6716.751767424547</v>
+        <v>-6716.75176742455</v>
       </c>
     </row>
     <row r="203">
@@ -10656,7 +10656,7 @@
         <v>-6693.127338518519</v>
       </c>
       <c r="G203" t="n">
-        <v>-6708.137911172699</v>
+        <v>-6708.1379111727</v>
       </c>
     </row>
     <row r="204">
@@ -10681,7 +10681,7 @@
         <v>-6635.505766481481</v>
       </c>
       <c r="G204" t="n">
-        <v>-6657.809227660437</v>
+        <v>-6657.809227660438</v>
       </c>
     </row>
     <row r="205">
@@ -10700,13 +10700,13 @@
         <v>-357.15426002</v>
       </c>
       <c r="E205" t="n">
-        <v>-357.8593531493707</v>
+        <v>-357.8593531493708</v>
       </c>
       <c r="F205" t="n">
         <v>-6613.967778148148</v>
       </c>
       <c r="G205" t="n">
-        <v>-6627.02505832168</v>
+        <v>-6627.025058321682</v>
       </c>
     </row>
     <row r="206">
@@ -10781,7 +10781,7 @@
         <v>-6659.74552574074</v>
       </c>
       <c r="G208" t="n">
-        <v>-6671.122301350149</v>
+        <v>-6671.12230135015</v>
       </c>
     </row>
     <row r="209">
@@ -10850,13 +10850,13 @@
         <v>-349.76647314</v>
       </c>
       <c r="E211" t="n">
-        <v>-350.8962085160285</v>
+        <v>-350.8962085160287</v>
       </c>
       <c r="F211" t="n">
         <v>-6477.156910000001</v>
       </c>
       <c r="G211" t="n">
-        <v>-6498.07793548201</v>
+        <v>-6498.077935482012</v>
       </c>
     </row>
     <row r="212">
@@ -10881,7 +10881,7 @@
         <v>-6692.505493148148</v>
       </c>
       <c r="G212" t="n">
-        <v>-6701.429824634323</v>
+        <v>-6701.429824634325</v>
       </c>
     </row>
     <row r="213">
@@ -10906,7 +10906,7 @@
         <v>-6686.634161851852</v>
       </c>
       <c r="G213" t="n">
-        <v>-6706.756038839397</v>
+        <v>-6706.756038839395</v>
       </c>
     </row>
     <row r="214">
@@ -10956,7 +10956,7 @@
         <v>-6662.474972777778</v>
       </c>
       <c r="G215" t="n">
-        <v>-6674.671970038178</v>
+        <v>-6674.671970038179</v>
       </c>
     </row>
     <row r="216">
@@ -11056,7 +11056,7 @@
         <v>-6652.059008518519</v>
       </c>
       <c r="G219" t="n">
-        <v>-6660.180221791735</v>
+        <v>-6660.180221791736</v>
       </c>
     </row>
     <row r="220">
@@ -11075,13 +11075,13 @@
         <v>-354.89811044</v>
       </c>
       <c r="E220" t="n">
-        <v>-355.5283131908577</v>
+        <v>-355.5283131908578</v>
       </c>
       <c r="F220" t="n">
         <v>-6572.187230370369</v>
       </c>
       <c r="G220" t="n">
-        <v>-6583.85765168255</v>
+        <v>-6583.857651682551</v>
       </c>
     </row>
     <row r="221">
@@ -11131,7 +11131,7 @@
         <v>-6498.769825185185</v>
       </c>
       <c r="G222" t="n">
-        <v>-6512.192953632537</v>
+        <v>-6512.192953632538</v>
       </c>
     </row>
     <row r="223">
@@ -11150,13 +11150,13 @@
         <v>-358.74295443</v>
       </c>
       <c r="E223" t="n">
-        <v>-359.5558116960973</v>
+        <v>-359.5558116960974</v>
       </c>
       <c r="F223" t="n">
         <v>-6643.388045</v>
       </c>
       <c r="G223" t="n">
-        <v>-6658.440957335136</v>
+        <v>-6658.440957335137</v>
       </c>
     </row>
     <row r="224">
@@ -11225,13 +11225,13 @@
         <v>-359.54295294</v>
       </c>
       <c r="E226" t="n">
-        <v>-360.4945343857681</v>
+        <v>-360.494534385768</v>
       </c>
       <c r="F226" t="n">
         <v>-6658.202832222223</v>
       </c>
       <c r="G226" t="n">
-        <v>-6675.824710847556</v>
+        <v>-6675.824710847555</v>
       </c>
     </row>
     <row r="227">
@@ -11275,7 +11275,7 @@
         <v>-359.17955389</v>
       </c>
       <c r="E228" t="n">
-        <v>-359.8328371650207</v>
+        <v>-359.8328371650208</v>
       </c>
       <c r="F228" t="n">
         <v>-6651.473220185186</v>
@@ -11300,13 +11300,13 @@
         <v>-350.81393328</v>
       </c>
       <c r="E229" t="n">
-        <v>-351.764980919323</v>
+        <v>-351.7649809193231</v>
       </c>
       <c r="F229" t="n">
         <v>-6496.55432</v>
       </c>
       <c r="G229" t="n">
-        <v>-6514.166313320798</v>
+        <v>-6514.166313320799</v>
       </c>
     </row>
     <row r="230">
@@ -11331,7 +11331,7 @@
         <v>-6517.223547407408</v>
       </c>
       <c r="G230" t="n">
-        <v>-6531.508432044893</v>
+        <v>-6531.508432044894</v>
       </c>
     </row>
     <row r="231">
@@ -11356,7 +11356,7 @@
         <v>-6685.489936666667</v>
       </c>
       <c r="G231" t="n">
-        <v>-6608.943193917854</v>
+        <v>-6608.943193917856</v>
       </c>
     </row>
     <row r="232">
@@ -11406,7 +11406,7 @@
         <v>-6577.748740185185</v>
       </c>
       <c r="G233" t="n">
-        <v>-6592.570774152253</v>
+        <v>-6592.570774152254</v>
       </c>
     </row>
     <row r="234">
@@ -11475,13 +11475,13 @@
         <v>-360.4185147</v>
       </c>
       <c r="E236" t="n">
-        <v>-360.9269003339566</v>
+        <v>-360.9269003339567</v>
       </c>
       <c r="F236" t="n">
         <v>-6674.416938888889</v>
       </c>
       <c r="G236" t="n">
-        <v>-6683.831487665861</v>
+        <v>-6683.831487665863</v>
       </c>
     </row>
     <row r="237">
@@ -11500,13 +11500,13 @@
         <v>-362.03007744</v>
       </c>
       <c r="E237" t="n">
-        <v>-362.5809621987612</v>
+        <v>-362.5809621987613</v>
       </c>
       <c r="F237" t="n">
         <v>-6704.260693333334</v>
       </c>
       <c r="G237" t="n">
-        <v>-6714.462262940022</v>
+        <v>-6714.462262940023</v>
       </c>
     </row>
     <row r="238">
@@ -11531,7 +11531,7 @@
         <v>-6672.635843888889</v>
       </c>
       <c r="G238" t="n">
-        <v>-6599.031363932707</v>
+        <v>-6599.031363932709</v>
       </c>
     </row>
     <row r="239">
@@ -11550,13 +11550,13 @@
         <v>-120.27784045</v>
       </c>
       <c r="E239" t="n">
-        <v>-119.0795759766233</v>
+        <v>-119.0795759766234</v>
       </c>
       <c r="F239" t="n">
         <v>-6682.102247222222</v>
       </c>
       <c r="G239" t="n">
-        <v>-6615.531998701296</v>
+        <v>-6615.531998701298</v>
       </c>
     </row>
     <row r="240">
@@ -11581,7 +11581,7 @@
         <v>-6635.795803703704</v>
       </c>
       <c r="G240" t="n">
-        <v>-6649.814902177475</v>
+        <v>-6649.814902177476</v>
       </c>
     </row>
     <row r="241">
@@ -11650,13 +11650,13 @@
         <v>-357.49335822</v>
       </c>
       <c r="E243" t="n">
-        <v>-357.8607714770734</v>
+        <v>-357.8607714770736</v>
       </c>
       <c r="F243" t="n">
         <v>-6620.247374444444</v>
       </c>
       <c r="G243" t="n">
-        <v>-6627.051323649507</v>
+        <v>-6627.05132364951</v>
       </c>
     </row>
     <row r="244">
@@ -11675,13 +11675,13 @@
         <v>-357.12004006</v>
       </c>
       <c r="E244" t="n">
-        <v>-357.8813032062849</v>
+        <v>-357.881303206285</v>
       </c>
       <c r="F244" t="n">
         <v>-6613.334075185186</v>
       </c>
       <c r="G244" t="n">
-        <v>-6627.431540857127</v>
+        <v>-6627.431540857129</v>
       </c>
     </row>
     <row r="245">
@@ -11700,13 +11700,13 @@
         <v>-359.35100753</v>
       </c>
       <c r="E245" t="n">
-        <v>-359.9932841781184</v>
+        <v>-359.9932841781185</v>
       </c>
       <c r="F245" t="n">
         <v>-6654.648287592593</v>
       </c>
       <c r="G245" t="n">
-        <v>-6666.542299594785</v>
+        <v>-6666.542299594787</v>
       </c>
     </row>
     <row r="246">
@@ -11725,13 +11725,13 @@
         <v>-356.44114165</v>
       </c>
       <c r="E246" t="n">
-        <v>-356.9102922643097</v>
+        <v>-356.9102922643098</v>
       </c>
       <c r="F246" t="n">
         <v>-6600.761882407408</v>
       </c>
       <c r="G246" t="n">
-        <v>-6609.449856746476</v>
+        <v>-6609.449856746477</v>
       </c>
     </row>
     <row r="247">
@@ -11750,13 +11750,13 @@
         <v>-361.18732978</v>
       </c>
       <c r="E247" t="n">
-        <v>-362.2307537247343</v>
+        <v>-362.2307537247344</v>
       </c>
       <c r="F247" t="n">
         <v>-6688.654255185185</v>
       </c>
       <c r="G247" t="n">
-        <v>-6707.976920828413</v>
+        <v>-6707.976920828414</v>
       </c>
     </row>
     <row r="248">
@@ -11781,7 +11781,7 @@
         <v>-6641.843339999999</v>
       </c>
       <c r="G248" t="n">
-        <v>-6652.208109502299</v>
+        <v>-6652.2081095023</v>
       </c>
     </row>
     <row r="249">
@@ -11800,13 +11800,13 @@
         <v>-357.52283202</v>
       </c>
       <c r="E249" t="n">
-        <v>-358.1870278220399</v>
+        <v>-358.18702782204</v>
       </c>
       <c r="F249" t="n">
         <v>-6620.793185555556</v>
       </c>
       <c r="G249" t="n">
-        <v>-6633.093107815554</v>
+        <v>-6633.093107815555</v>
       </c>
     </row>
     <row r="250">
@@ -11881,7 +11881,7 @@
         <v>-6681.408308333333</v>
       </c>
       <c r="G252" t="n">
-        <v>-6699.083065979864</v>
+        <v>-6699.083065979865</v>
       </c>
     </row>
     <row r="253">
@@ -11900,13 +11900,13 @@
         <v>-354.59755358</v>
       </c>
       <c r="E253" t="n">
-        <v>-355.813082788251</v>
+        <v>-355.8130827882511</v>
       </c>
       <c r="F253" t="n">
         <v>-6566.621362592593</v>
       </c>
       <c r="G253" t="n">
-        <v>-6589.131162745389</v>
+        <v>-6589.131162745391</v>
       </c>
     </row>
     <row r="254">
@@ -11925,13 +11925,13 @@
         <v>-361.19015213</v>
       </c>
       <c r="E254" t="n">
-        <v>-361.6167226447428</v>
+        <v>-361.6167226447427</v>
       </c>
       <c r="F254" t="n">
         <v>-6688.706520925926</v>
       </c>
       <c r="G254" t="n">
-        <v>-6696.605974902644</v>
+        <v>-6696.605974902643</v>
       </c>
     </row>
     <row r="255">
@@ -11956,7 +11956,7 @@
         <v>-6688.760788518518</v>
       </c>
       <c r="G255" t="n">
-        <v>-6696.005578807066</v>
+        <v>-6696.005578807067</v>
       </c>
     </row>
     <row r="256">
@@ -11975,13 +11975,13 @@
         <v>-362.24209641</v>
       </c>
       <c r="E256" t="n">
-        <v>-362.965310455067</v>
+        <v>-362.9653104550669</v>
       </c>
       <c r="F256" t="n">
         <v>-6708.186970555555</v>
       </c>
       <c r="G256" t="n">
-        <v>-6721.579823241981</v>
+        <v>-6721.57982324198</v>
       </c>
     </row>
     <row r="257">
@@ -12025,13 +12025,13 @@
         <v>-355.81934591</v>
       </c>
       <c r="E258" t="n">
-        <v>-356.037657387953</v>
+        <v>-356.0376573879531</v>
       </c>
       <c r="F258" t="n">
         <v>-6589.247146481481</v>
       </c>
       <c r="G258" t="n">
-        <v>-6593.28995162876</v>
+        <v>-6593.289951628761</v>
       </c>
     </row>
     <row r="259">
@@ -12075,7 +12075,7 @@
         <v>-356.09538079</v>
       </c>
       <c r="E260" t="n">
-        <v>-356.5208108874986</v>
+        <v>-356.5208108874987</v>
       </c>
       <c r="F260" t="n">
         <v>-6594.358903518518</v>
@@ -12125,13 +12125,13 @@
         <v>-353.31581914</v>
       </c>
       <c r="E262" t="n">
-        <v>-354.1260403595931</v>
+        <v>-354.1260403595932</v>
       </c>
       <c r="F262" t="n">
         <v>-6542.885539629629</v>
       </c>
       <c r="G262" t="n">
-        <v>-6557.889636288762</v>
+        <v>-6557.889636288763</v>
       </c>
     </row>
     <row r="263">
@@ -12181,7 +12181,7 @@
         <v>-6569.462965555555</v>
       </c>
       <c r="G264" t="n">
-        <v>-6490.070139251039</v>
+        <v>-6490.070139251041</v>
       </c>
     </row>
     <row r="265">
@@ -12231,7 +12231,7 @@
         <v>-6618.107295370371</v>
       </c>
       <c r="G266" t="n">
-        <v>-6623.744132766228</v>
+        <v>-6623.744132766227</v>
       </c>
     </row>
     <row r="267">
@@ -12281,7 +12281,7 @@
         <v>-6625.958594814814</v>
       </c>
       <c r="G268" t="n">
-        <v>-6640.06105768546</v>
+        <v>-6640.061057685461</v>
       </c>
     </row>
     <row r="269">
@@ -12300,13 +12300,13 @@
         <v>-356.41517505</v>
       </c>
       <c r="E269" t="n">
-        <v>-356.6933457290044</v>
+        <v>-356.6933457290046</v>
       </c>
       <c r="F269" t="n">
         <v>-6600.281019444445</v>
       </c>
       <c r="G269" t="n">
-        <v>-6605.432328314897</v>
+        <v>-6605.4323283149</v>
       </c>
     </row>
     <row r="270">
@@ -12325,13 +12325,13 @@
         <v>-355.5830248</v>
       </c>
       <c r="E270" t="n">
-        <v>-355.8882002003236</v>
+        <v>-355.8882002003237</v>
       </c>
       <c r="F270" t="n">
         <v>-6584.870829629629</v>
       </c>
       <c r="G270" t="n">
-        <v>-6590.52222593192</v>
+        <v>-6590.522225931921</v>
       </c>
     </row>
     <row r="271">
@@ -12350,13 +12350,13 @@
         <v>-355.08477173</v>
       </c>
       <c r="E271" t="n">
-        <v>-355.9595669202961</v>
+        <v>-355.959566920296</v>
       </c>
       <c r="F271" t="n">
         <v>-6575.643920925925</v>
       </c>
       <c r="G271" t="n">
-        <v>-6591.843831857334</v>
+        <v>-6591.843831857333</v>
       </c>
     </row>
     <row r="272">
@@ -12375,13 +12375,13 @@
         <v>-351.1397039</v>
       </c>
       <c r="E272" t="n">
-        <v>-351.5548949035722</v>
+        <v>-351.5548949035723</v>
       </c>
       <c r="F272" t="n">
         <v>-6502.587109259259</v>
       </c>
       <c r="G272" t="n">
-        <v>-6510.275831547634</v>
+        <v>-6510.275831547635</v>
       </c>
     </row>
     <row r="273">
@@ -12431,7 +12431,7 @@
         <v>-6589.572875185185</v>
       </c>
       <c r="G274" t="n">
-        <v>-6603.566122591066</v>
+        <v>-6603.566122591067</v>
       </c>
     </row>
     <row r="275">
@@ -12456,7 +12456,7 @@
         <v>-6553.261400555556</v>
       </c>
       <c r="G275" t="n">
-        <v>-6565.167506231081</v>
+        <v>-6565.167506231082</v>
       </c>
     </row>
     <row r="276">
@@ -12475,13 +12475,13 @@
         <v>-120.07659429</v>
       </c>
       <c r="E276" t="n">
-        <v>-118.5666129710442</v>
+        <v>-118.5666129710443</v>
       </c>
       <c r="F276" t="n">
         <v>-6670.921905</v>
       </c>
       <c r="G276" t="n">
-        <v>-6587.034053946902</v>
+        <v>-6587.034053946903</v>
       </c>
     </row>
     <row r="277">
@@ -12500,13 +12500,13 @@
         <v>-355.62140019</v>
       </c>
       <c r="E277" t="n">
-        <v>-356.2691629064742</v>
+        <v>-356.2691629064743</v>
       </c>
       <c r="F277" t="n">
         <v>-6585.581484999999</v>
       </c>
       <c r="G277" t="n">
-        <v>-6597.577090860634</v>
+        <v>-6597.577090860635</v>
       </c>
     </row>
     <row r="278">
@@ -12606,7 +12606,7 @@
         <v>-6704.784464444445</v>
       </c>
       <c r="G281" t="n">
-        <v>-6707.802096802974</v>
+        <v>-6707.802096802973</v>
       </c>
     </row>
     <row r="282">
@@ -12631,7 +12631,7 @@
         <v>-6628.932908888889</v>
       </c>
       <c r="G282" t="n">
-        <v>-6645.183626103711</v>
+        <v>-6645.183626103712</v>
       </c>
     </row>
     <row r="283">
@@ -12675,13 +12675,13 @@
         <v>-352.88761684</v>
       </c>
       <c r="E284" t="n">
-        <v>-353.6486759975571</v>
+        <v>-353.648675997557</v>
       </c>
       <c r="F284" t="n">
         <v>-6534.955867407408</v>
       </c>
       <c r="G284" t="n">
-        <v>-6549.049555510316</v>
+        <v>-6549.049555510315</v>
       </c>
     </row>
     <row r="285">
@@ -12731,7 +12731,7 @@
         <v>-6647.532409629629</v>
       </c>
       <c r="G286" t="n">
-        <v>-6662.043945121963</v>
+        <v>-6662.043945121964</v>
       </c>
     </row>
     <row r="287">
@@ -12750,13 +12750,13 @@
         <v>-349.12019873</v>
       </c>
       <c r="E287" t="n">
-        <v>-350.2281967233654</v>
+        <v>-350.2281967233655</v>
       </c>
       <c r="F287" t="n">
         <v>-6465.188865370371</v>
       </c>
       <c r="G287" t="n">
-        <v>-6485.70734672899</v>
+        <v>-6485.707346728991</v>
       </c>
     </row>
     <row r="288">
@@ -12800,13 +12800,13 @@
         <v>-356.94098032</v>
       </c>
       <c r="E289" t="n">
-        <v>-357.7348402648011</v>
+        <v>-357.7348402648012</v>
       </c>
       <c r="F289" t="n">
         <v>-6610.018154074073</v>
       </c>
       <c r="G289" t="n">
-        <v>-6624.719264162983</v>
+        <v>-6624.719264162984</v>
       </c>
     </row>
     <row r="290">
@@ -12825,13 +12825,13 @@
         <v>-353.20599382</v>
       </c>
       <c r="E290" t="n">
-        <v>-354.3222778089846</v>
+        <v>-354.3222778089847</v>
       </c>
       <c r="F290" t="n">
         <v>-6540.851737407407</v>
       </c>
       <c r="G290" t="n">
-        <v>-6561.523663129345</v>
+        <v>-6561.523663129346</v>
       </c>
     </row>
     <row r="291">
@@ -12875,7 +12875,7 @@
         <v>-357.66600488</v>
       </c>
       <c r="E292" t="n">
-        <v>-358.694582001993</v>
+        <v>-358.6945820019931</v>
       </c>
       <c r="F292" t="n">
         <v>-6623.444534814816</v>
@@ -12931,7 +12931,7 @@
         <v>-6525.597906296295</v>
       </c>
       <c r="G294" t="n">
-        <v>-6550.400051800115</v>
+        <v>-6550.400051800116</v>
       </c>
     </row>
     <row r="295">
@@ -12950,13 +12950,13 @@
         <v>-359.75758305</v>
       </c>
       <c r="E295" t="n">
-        <v>-360.0984077714051</v>
+        <v>-360.0984077714052</v>
       </c>
       <c r="F295" t="n">
         <v>-6662.177463888889</v>
       </c>
       <c r="G295" t="n">
-        <v>-6668.489032803798</v>
+        <v>-6668.489032803801</v>
       </c>
     </row>
     <row r="296">
@@ -12975,13 +12975,13 @@
         <v>-350.22577124</v>
       </c>
       <c r="E296" t="n">
-        <v>-350.6741730827525</v>
+        <v>-350.6741730827524</v>
       </c>
       <c r="F296" t="n">
         <v>-6485.66243037037</v>
       </c>
       <c r="G296" t="n">
-        <v>-6493.96616819912</v>
+        <v>-6493.966168199119</v>
       </c>
     </row>
     <row r="297">
@@ -13100,13 +13100,13 @@
         <v>-353.97287117</v>
       </c>
       <c r="E301" t="n">
-        <v>-355.10970669735</v>
+        <v>-355.1097066973501</v>
       </c>
       <c r="F301" t="n">
         <v>-6555.053169814815</v>
       </c>
       <c r="G301" t="n">
-        <v>-6576.105679580556</v>
+        <v>-6576.105679580557</v>
       </c>
     </row>
     <row r="302">
@@ -13131,7 +13131,7 @@
         <v>-6701.378289814814</v>
       </c>
       <c r="G302" t="n">
-        <v>-6705.833659297142</v>
+        <v>-6705.833659297143</v>
       </c>
     </row>
     <row r="303">
@@ -13175,13 +13175,13 @@
         <v>-356.09038908</v>
       </c>
       <c r="E304" t="n">
-        <v>-356.8847009282426</v>
+        <v>-356.8847009282427</v>
       </c>
       <c r="F304" t="n">
         <v>-6594.266464444444</v>
       </c>
       <c r="G304" t="n">
-        <v>-6608.975943115604</v>
+        <v>-6608.975943115605</v>
       </c>
     </row>
     <row r="305">
@@ -13256,7 +13256,7 @@
         <v>-6659.484813703703</v>
       </c>
       <c r="G307" t="n">
-        <v>-6668.733992694742</v>
+        <v>-6668.733992694743</v>
       </c>
     </row>
     <row r="308">
@@ -13275,7 +13275,7 @@
         <v>-353.28122136</v>
       </c>
       <c r="E308" t="n">
-        <v>-354.0044013265372</v>
+        <v>-354.0044013265373</v>
       </c>
       <c r="F308" t="n">
         <v>-6542.24484</v>
@@ -13306,7 +13306,7 @@
         <v>-6674.533409629629</v>
       </c>
       <c r="G309" t="n">
-        <v>-6684.34150396166</v>
+        <v>-6684.341503961662</v>
       </c>
     </row>
     <row r="310">
@@ -13331,7 +13331,7 @@
         <v>-6620.349261851852</v>
       </c>
       <c r="G310" t="n">
-        <v>-6630.803675888495</v>
+        <v>-6630.803675888496</v>
       </c>
     </row>
     <row r="311">
@@ -13375,13 +13375,13 @@
         <v>-352.75622344</v>
       </c>
       <c r="E312" t="n">
-        <v>-353.1599618968186</v>
+        <v>-353.1599618968185</v>
       </c>
       <c r="F312" t="n">
         <v>-6532.522656296296</v>
       </c>
       <c r="G312" t="n">
-        <v>-6539.99929438553</v>
+        <v>-6539.999294385529</v>
       </c>
     </row>
     <row r="313">
@@ -13406,7 +13406,7 @@
         <v>-6637.696977592593</v>
       </c>
       <c r="G313" t="n">
-        <v>-6646.971559688075</v>
+        <v>-6646.971559688076</v>
       </c>
     </row>
     <row r="314">
@@ -13431,7 +13431,7 @@
         <v>-6551.348638148147</v>
       </c>
       <c r="G314" t="n">
-        <v>-6561.447184089359</v>
+        <v>-6561.44718408936</v>
       </c>
     </row>
     <row r="315">
@@ -13481,7 +13481,7 @@
         <v>-6552.18938611111</v>
       </c>
       <c r="G316" t="n">
-        <v>-6555.758200293255</v>
+        <v>-6555.758200293256</v>
       </c>
     </row>
     <row r="317">
@@ -13506,7 +13506,7 @@
         <v>-6559.433692962963</v>
       </c>
       <c r="G317" t="n">
-        <v>-6585.811806981246</v>
+        <v>-6585.811806981247</v>
       </c>
     </row>
     <row r="318">
@@ -13531,7 +13531,7 @@
         <v>-6676.284307407407</v>
       </c>
       <c r="G318" t="n">
-        <v>-6692.750111306439</v>
+        <v>-6692.75011130644</v>
       </c>
     </row>
     <row r="319">
@@ -13556,7 +13556,7 @@
         <v>-6669.686216851852</v>
       </c>
       <c r="G319" t="n">
-        <v>-6679.644338194783</v>
+        <v>-6679.644338194784</v>
       </c>
     </row>
     <row r="320">
@@ -13650,13 +13650,13 @@
         <v>-354.89617512</v>
       </c>
       <c r="E323" t="n">
-        <v>-355.7349024639801</v>
+        <v>-355.7349024639802</v>
       </c>
       <c r="F323" t="n">
         <v>-6572.151391111111</v>
       </c>
       <c r="G323" t="n">
-        <v>-6587.683378962594</v>
+        <v>-6587.683378962596</v>
       </c>
     </row>
     <row r="324">
@@ -13706,7 +13706,7 @@
         <v>-6677.431398148148</v>
       </c>
       <c r="G325" t="n">
-        <v>-6688.371063833307</v>
+        <v>-6688.371063833308</v>
       </c>
     </row>
     <row r="326">
@@ -13731,7 +13731,7 @@
         <v>-6453.977895370371</v>
       </c>
       <c r="G326" t="n">
-        <v>-6461.939199552188</v>
+        <v>-6461.939199552189</v>
       </c>
     </row>
     <row r="327">
@@ -13750,13 +13750,13 @@
         <v>-361.12456203</v>
       </c>
       <c r="E327" t="n">
-        <v>-361.8235230713943</v>
+        <v>-361.8235230713945</v>
       </c>
       <c r="F327" t="n">
         <v>-6687.491889444444</v>
       </c>
       <c r="G327" t="n">
-        <v>-6700.435612433229</v>
+        <v>-6700.435612433231</v>
       </c>
     </row>
     <row r="328">
@@ -13781,7 +13781,7 @@
         <v>-6636.321377037037</v>
       </c>
       <c r="G328" t="n">
-        <v>-6646.861978620775</v>
+        <v>-6646.861978620776</v>
       </c>
     </row>
     <row r="329">
@@ -13831,7 +13831,7 @@
         <v>-6650.087916666667</v>
       </c>
       <c r="G330" t="n">
-        <v>-6575.918062691557</v>
+        <v>-6575.918062691559</v>
       </c>
     </row>
     <row r="331">
@@ -13900,13 +13900,13 @@
         <v>-359.35936203</v>
       </c>
       <c r="E333" t="n">
-        <v>-359.7377925538832</v>
+        <v>-359.7377925538831</v>
       </c>
       <c r="F333" t="n">
         <v>-6654.803000555556</v>
       </c>
       <c r="G333" t="n">
-        <v>-6661.81097322006</v>
+        <v>-6661.810973220058</v>
       </c>
     </row>
     <row r="334">
@@ -13981,7 +13981,7 @@
         <v>-6677.417906851852</v>
       </c>
       <c r="G336" t="n">
-        <v>-6692.792209241878</v>
+        <v>-6692.79220924188</v>
       </c>
     </row>
     <row r="337">
@@ -14031,7 +14031,7 @@
         <v>-6682.972284444444</v>
       </c>
       <c r="G338" t="n">
-        <v>-6588.914337299789</v>
+        <v>-6588.91433729979</v>
       </c>
     </row>
     <row r="339">
@@ -14100,13 +14100,13 @@
         <v>-360.55934518</v>
       </c>
       <c r="E341" t="n">
-        <v>-361.351184274922</v>
+        <v>-361.3511842749221</v>
       </c>
       <c r="F341" t="n">
         <v>-6677.024910740741</v>
       </c>
       <c r="G341" t="n">
-        <v>-6691.688597683742</v>
+        <v>-6691.688597683743</v>
       </c>
     </row>
     <row r="342">
@@ -14150,13 +14150,13 @@
         <v>-120.56362079</v>
       </c>
       <c r="E343" t="n">
-        <v>-118.927608709899</v>
+        <v>-118.9276087098991</v>
       </c>
       <c r="F343" t="n">
         <v>-6697.978932777778</v>
       </c>
       <c r="G343" t="n">
-        <v>-6607.089372772169</v>
+        <v>-6607.08937277217</v>
       </c>
     </row>
     <row r="344">
@@ -14175,13 +14175,13 @@
         <v>-357.89701701</v>
       </c>
       <c r="E344" t="n">
-        <v>-358.2959397808414</v>
+        <v>-358.2959397808415</v>
       </c>
       <c r="F344" t="n">
         <v>-6627.722537222223</v>
       </c>
       <c r="G344" t="n">
-        <v>-6635.109995941508</v>
+        <v>-6635.109995941509</v>
       </c>
     </row>
     <row r="345">
@@ -14200,13 +14200,13 @@
         <v>-356.89642233</v>
       </c>
       <c r="E345" t="n">
-        <v>-357.7732853208726</v>
+        <v>-357.7732853208727</v>
       </c>
       <c r="F345" t="n">
         <v>-6609.193006111112</v>
       </c>
       <c r="G345" t="n">
-        <v>-6625.431209645789</v>
+        <v>-6625.431209645792</v>
       </c>
     </row>
     <row r="346">
@@ -14356,7 +14356,7 @@
         <v>-6620.886794814815</v>
       </c>
       <c r="G351" t="n">
-        <v>-6629.589648267511</v>
+        <v>-6629.589648267512</v>
       </c>
     </row>
     <row r="352">
@@ -14381,7 +14381,7 @@
         <v>-6549.613232592593</v>
       </c>
       <c r="G352" t="n">
-        <v>-6563.37575256129</v>
+        <v>-6563.375752561291</v>
       </c>
     </row>
     <row r="353">
@@ -14400,13 +14400,13 @@
         <v>-345.9256201</v>
       </c>
       <c r="E353" t="n">
-        <v>-348.251622878512</v>
+        <v>-348.2516228785119</v>
       </c>
       <c r="F353" t="n">
         <v>-6406.030001851852</v>
       </c>
       <c r="G353" t="n">
-        <v>-6449.104127379851</v>
+        <v>-6449.10412737985</v>
       </c>
     </row>
     <row r="354">
@@ -14475,13 +14475,13 @@
         <v>-356.484623</v>
       </c>
       <c r="E356" t="n">
-        <v>-357.3127057887926</v>
+        <v>-357.3127057887927</v>
       </c>
       <c r="F356" t="n">
         <v>-6601.567092592593</v>
       </c>
       <c r="G356" t="n">
-        <v>-6616.901959051715</v>
+        <v>-6616.901959051716</v>
       </c>
     </row>
     <row r="357">
@@ -14525,13 +14525,13 @@
         <v>-352.22234778</v>
       </c>
       <c r="E358" t="n">
-        <v>-353.0620556170539</v>
+        <v>-353.0620556170538</v>
       </c>
       <c r="F358" t="n">
         <v>-6522.63607</v>
       </c>
       <c r="G358" t="n">
-        <v>-6538.186215130628</v>
+        <v>-6538.186215130626</v>
       </c>
     </row>
     <row r="359">
@@ -14556,7 +14556,7 @@
         <v>-6346.184546666667</v>
       </c>
       <c r="G359" t="n">
-        <v>-6266.829531431628</v>
+        <v>-6266.82953143163</v>
       </c>
     </row>
     <row r="360">
@@ -14581,7 +14581,7 @@
         <v>-6619.281762222223</v>
       </c>
       <c r="G360" t="n">
-        <v>-6630.480917416291</v>
+        <v>-6630.480917416292</v>
       </c>
     </row>
     <row r="361">
@@ -14600,13 +14600,13 @@
         <v>-362.12787936</v>
       </c>
       <c r="E361" t="n">
-        <v>-362.6202709459634</v>
+        <v>-362.6202709459635</v>
       </c>
       <c r="F361" t="n">
         <v>-6706.071840000001</v>
       </c>
       <c r="G361" t="n">
-        <v>-6715.190202703026</v>
+        <v>-6715.190202703028</v>
       </c>
     </row>
     <row r="362">
@@ -14625,13 +14625,13 @@
         <v>-351.70914765</v>
       </c>
       <c r="E362" t="n">
-        <v>-352.2166593879018</v>
+        <v>-352.2166593879019</v>
       </c>
       <c r="F362" t="n">
         <v>-6513.132363888889</v>
       </c>
       <c r="G362" t="n">
-        <v>-6522.530729405589</v>
+        <v>-6522.53072940559</v>
       </c>
     </row>
     <row r="363">
@@ -14650,13 +14650,13 @@
         <v>-351.65777559</v>
       </c>
       <c r="E363" t="n">
-        <v>-352.075566545557</v>
+        <v>-352.0755665455571</v>
       </c>
       <c r="F363" t="n">
         <v>-6512.181029444445</v>
       </c>
       <c r="G363" t="n">
-        <v>-6519.917898991796</v>
+        <v>-6519.917898991797</v>
       </c>
     </row>
     <row r="364">
@@ -14675,13 +14675,13 @@
         <v>-362.45464666</v>
       </c>
       <c r="E364" t="n">
-        <v>-363.1709051948967</v>
+        <v>-363.1709051948968</v>
       </c>
       <c r="F364" t="n">
         <v>-6712.123086296296</v>
       </c>
       <c r="G364" t="n">
-        <v>-6725.387133238827</v>
+        <v>-6725.387133238829</v>
       </c>
     </row>
     <row r="365">
@@ -14700,7 +14700,7 @@
         <v>-351.71595871</v>
       </c>
       <c r="E365" t="n">
-        <v>-352.9310962696775</v>
+        <v>-352.9310962696776</v>
       </c>
       <c r="F365" t="n">
         <v>-6513.258494629629</v>
@@ -14725,13 +14725,13 @@
         <v>-360.54684041</v>
       </c>
       <c r="E366" t="n">
-        <v>-361.5155711683833</v>
+        <v>-361.5155711683832</v>
       </c>
       <c r="F366" t="n">
         <v>-6676.793340925926</v>
       </c>
       <c r="G366" t="n">
-        <v>-6694.732799414505</v>
+        <v>-6694.732799414504</v>
       </c>
     </row>
     <row r="367">
@@ -14781,7 +14781,7 @@
         <v>-6601.91592037037</v>
       </c>
       <c r="G368" t="n">
-        <v>-6614.041022027769</v>
+        <v>-6614.041022027771</v>
       </c>
     </row>
     <row r="369">
@@ -14800,13 +14800,13 @@
         <v>-358.20746424</v>
       </c>
       <c r="E369" t="n">
-        <v>-358.7375737911526</v>
+        <v>-358.7375737911527</v>
       </c>
       <c r="F369" t="n">
         <v>-6633.47156</v>
       </c>
       <c r="G369" t="n">
-        <v>-6643.288403539864</v>
+        <v>-6643.288403539866</v>
       </c>
     </row>
     <row r="370">
@@ -14825,13 +14825,13 @@
         <v>-358.48149619</v>
       </c>
       <c r="E370" t="n">
-        <v>-359.4384914075446</v>
+        <v>-359.4384914075447</v>
       </c>
       <c r="F370" t="n">
         <v>-6638.546225740741</v>
       </c>
       <c r="G370" t="n">
-        <v>-6656.268359398975</v>
+        <v>-6656.268359398976</v>
       </c>
     </row>
     <row r="371">
@@ -14900,13 +14900,13 @@
         <v>-357.56314494</v>
       </c>
       <c r="E373" t="n">
-        <v>-358.2453339305914</v>
+        <v>-358.2453339305915</v>
       </c>
       <c r="F373" t="n">
         <v>-6621.53972111111</v>
       </c>
       <c r="G373" t="n">
-        <v>-6634.172850566508</v>
+        <v>-6634.172850566509</v>
       </c>
     </row>
     <row r="374">
@@ -14925,13 +14925,13 @@
         <v>-353.43565812</v>
       </c>
       <c r="E374" t="n">
-        <v>-354.0722279662874</v>
+        <v>-354.0722279662875</v>
       </c>
       <c r="F374" t="n">
         <v>-6545.104780000001</v>
       </c>
       <c r="G374" t="n">
-        <v>-6556.893110486803</v>
+        <v>-6556.893110486805</v>
       </c>
     </row>
     <row r="375">
@@ -14975,13 +14975,13 @@
         <v>-362.34840671</v>
       </c>
       <c r="E376" t="n">
-        <v>-363.1559021496162</v>
+        <v>-363.1559021496163</v>
       </c>
       <c r="F376" t="n">
         <v>-6710.155679814815</v>
       </c>
       <c r="G376" t="n">
-        <v>-6725.109299066967</v>
+        <v>-6725.109299066968</v>
       </c>
     </row>
     <row r="377">
@@ -15075,13 +15075,13 @@
         <v>-351.13462059</v>
       </c>
       <c r="E380" t="n">
-        <v>-351.7830998887915</v>
+        <v>-351.7830998887916</v>
       </c>
       <c r="F380" t="n">
         <v>-6502.492973888889</v>
       </c>
       <c r="G380" t="n">
-        <v>-6514.501849792436</v>
+        <v>-6514.501849792437</v>
       </c>
     </row>
     <row r="381">
@@ -15125,13 +15125,13 @@
         <v>-355.15466457</v>
       </c>
       <c r="E382" t="n">
-        <v>-355.6967376232912</v>
+        <v>-355.6967376232911</v>
       </c>
       <c r="F382" t="n">
         <v>-6576.938232777778</v>
       </c>
       <c r="G382" t="n">
-        <v>-6586.976622653541</v>
+        <v>-6586.976622653539</v>
       </c>
     </row>
     <row r="383">
@@ -15181,7 +15181,7 @@
         <v>-6676.547492962964</v>
       </c>
       <c r="G384" t="n">
-        <v>-6691.696554028242</v>
+        <v>-6691.696554028241</v>
       </c>
     </row>
     <row r="385">
@@ -15275,13 +15275,13 @@
         <v>-356.58340176</v>
       </c>
       <c r="E388" t="n">
-        <v>-357.2968653753773</v>
+        <v>-357.2968653753772</v>
       </c>
       <c r="F388" t="n">
         <v>-6603.39632888889</v>
       </c>
       <c r="G388" t="n">
-        <v>-6616.608618062542</v>
+        <v>-6616.608618062541</v>
       </c>
     </row>
     <row r="389">
@@ -15300,13 +15300,13 @@
         <v>-359.93362016</v>
       </c>
       <c r="E389" t="n">
-        <v>-360.7284637536935</v>
+        <v>-360.7284637536936</v>
       </c>
       <c r="F389" t="n">
         <v>-6665.43741037037</v>
       </c>
       <c r="G389" t="n">
-        <v>-6680.15673617951</v>
+        <v>-6680.156736179511</v>
       </c>
     </row>
     <row r="390">
@@ -15356,7 +15356,7 @@
         <v>-6603.97549925926</v>
       </c>
       <c r="G391" t="n">
-        <v>-6617.303031405246</v>
+        <v>-6617.303031405247</v>
       </c>
     </row>
     <row r="392">
@@ -15475,13 +15475,13 @@
         <v>-120.39544137</v>
       </c>
       <c r="E396" t="n">
-        <v>-118.9535802277099</v>
+        <v>-118.95358022771</v>
       </c>
       <c r="F396" t="n">
         <v>-6688.635631666667</v>
       </c>
       <c r="G396" t="n">
-        <v>-6608.532234872775</v>
+        <v>-6608.532234872776</v>
       </c>
     </row>
     <row r="397">
@@ -15500,13 +15500,13 @@
         <v>-359.01636409</v>
       </c>
       <c r="E397" t="n">
-        <v>-359.3872599624747</v>
+        <v>-359.3872599624746</v>
       </c>
       <c r="F397" t="n">
         <v>-6648.451186851853</v>
       </c>
       <c r="G397" t="n">
-        <v>-6655.319628934717</v>
+        <v>-6655.319628934715</v>
       </c>
     </row>
     <row r="398">
@@ -15581,7 +15581,7 @@
         <v>-6696.198331666667</v>
       </c>
       <c r="G400" t="n">
-        <v>-6618.871860849732</v>
+        <v>-6618.871860849733</v>
       </c>
     </row>
     <row r="401">
@@ -15675,13 +15675,13 @@
         <v>-357.69553521</v>
       </c>
       <c r="E404" t="n">
-        <v>-358.523965942547</v>
+        <v>-358.5239659425471</v>
       </c>
       <c r="F404" t="n">
         <v>-6623.991392777778</v>
       </c>
       <c r="G404" t="n">
-        <v>-6639.332702639758</v>
+        <v>-6639.332702639761</v>
       </c>
     </row>
     <row r="405">
@@ -15706,7 +15706,7 @@
         <v>-6675.329163703705</v>
       </c>
       <c r="G405" t="n">
-        <v>-6685.229028272056</v>
+        <v>-6685.229028272057</v>
       </c>
     </row>
     <row r="406">
@@ -15725,13 +15725,13 @@
         <v>-359.35636577</v>
       </c>
       <c r="E406" t="n">
-        <v>-359.5790446552742</v>
+        <v>-359.5790446552743</v>
       </c>
       <c r="F406" t="n">
         <v>-6654.74751425926</v>
       </c>
       <c r="G406" t="n">
-        <v>-6658.871197319893</v>
+        <v>-6658.871197319894</v>
       </c>
     </row>
     <row r="407">
@@ -15806,7 +15806,7 @@
         <v>-6628.159470000001</v>
       </c>
       <c r="G409" t="n">
-        <v>-6641.457829677269</v>
+        <v>-6641.457829677268</v>
       </c>
     </row>
     <row r="410">
@@ -15831,7 +15831,7 @@
         <v>-6615.216592962964</v>
       </c>
       <c r="G410" t="n">
-        <v>-6635.33613075355</v>
+        <v>-6635.336130753551</v>
       </c>
     </row>
     <row r="411">
@@ -15906,7 +15906,7 @@
         <v>-6681.38082537037</v>
       </c>
       <c r="G413" t="n">
-        <v>-6691.013690886671</v>
+        <v>-6691.01369088667</v>
       </c>
     </row>
     <row r="414">
@@ -15925,13 +15925,13 @@
         <v>-355.43148182</v>
       </c>
       <c r="E414" t="n">
-        <v>-356.4090471938894</v>
+        <v>-356.4090471938895</v>
       </c>
       <c r="F414" t="n">
         <v>-6582.064478148148</v>
       </c>
       <c r="G414" t="n">
-        <v>-6600.167540627583</v>
+        <v>-6600.167540627584</v>
       </c>
     </row>
     <row r="415">
@@ -15950,13 +15950,13 @@
         <v>-359.29146083</v>
       </c>
       <c r="E415" t="n">
-        <v>-360.3567348140714</v>
+        <v>-360.3567348140715</v>
       </c>
       <c r="F415" t="n">
         <v>-6653.545570925926</v>
       </c>
       <c r="G415" t="n">
-        <v>-6673.272866927249</v>
+        <v>-6673.27286692725</v>
       </c>
     </row>
     <row r="416">
@@ -15975,13 +15975,13 @@
         <v>-352.11080611</v>
       </c>
       <c r="E416" t="n">
-        <v>-352.9855928101557</v>
+        <v>-352.9855928101558</v>
       </c>
       <c r="F416" t="n">
         <v>-6520.570483518519</v>
       </c>
       <c r="G416" t="n">
-        <v>-6536.770237225106</v>
+        <v>-6536.770237225107</v>
       </c>
     </row>
     <row r="417">
@@ -16000,13 +16000,13 @@
         <v>-357.0382745</v>
       </c>
       <c r="E417" t="n">
-        <v>-357.5685135115652</v>
+        <v>-357.5685135115653</v>
       </c>
       <c r="F417" t="n">
         <v>-6611.819898148148</v>
       </c>
       <c r="G417" t="n">
-        <v>-6621.639139103059</v>
+        <v>-6621.639139103061</v>
       </c>
     </row>
     <row r="418">
@@ -16025,13 +16025,13 @@
         <v>-361.72584269</v>
       </c>
       <c r="E418" t="n">
-        <v>-362.1184743793881</v>
+        <v>-362.118474379388</v>
       </c>
       <c r="F418" t="n">
         <v>-6698.626716481481</v>
       </c>
       <c r="G418" t="n">
-        <v>-6705.897673692372</v>
+        <v>-6705.897673692371</v>
       </c>
     </row>
     <row r="419">
@@ -16075,13 +16075,13 @@
         <v>-359.15863453</v>
       </c>
       <c r="E420" t="n">
-        <v>-359.6392289837675</v>
+        <v>-359.6392289837676</v>
       </c>
       <c r="F420" t="n">
         <v>-6651.085824629629</v>
       </c>
       <c r="G420" t="n">
-        <v>-6659.98572192162</v>
+        <v>-6659.985721921622</v>
       </c>
     </row>
     <row r="421">
@@ -16150,13 +16150,13 @@
         <v>-362.38964958</v>
       </c>
       <c r="E423" t="n">
-        <v>-363.123906345514</v>
+        <v>-363.1239063455141</v>
       </c>
       <c r="F423" t="n">
         <v>-6710.919436666667</v>
       </c>
       <c r="G423" t="n">
-        <v>-6724.516784176185</v>
+        <v>-6724.516784176186</v>
       </c>
     </row>
     <row r="424">
@@ -16181,7 +16181,7 @@
         <v>-6673.772548333333</v>
       </c>
       <c r="G424" t="n">
-        <v>-6683.435503926165</v>
+        <v>-6683.435503926167</v>
       </c>
     </row>
     <row r="425">
@@ -16200,13 +16200,13 @@
         <v>-361.78085994</v>
       </c>
       <c r="E425" t="n">
-        <v>-362.3408246713901</v>
+        <v>-362.3408246713902</v>
       </c>
       <c r="F425" t="n">
         <v>-6699.645554444445</v>
       </c>
       <c r="G425" t="n">
-        <v>-6710.015271692409</v>
+        <v>-6710.01527169241</v>
       </c>
     </row>
     <row r="426">
@@ -16250,13 +16250,13 @@
         <v>-358.04002987</v>
       </c>
       <c r="E427" t="n">
-        <v>-358.6664003734572</v>
+        <v>-358.6664003734573</v>
       </c>
       <c r="F427" t="n">
         <v>-6630.370923518519</v>
       </c>
       <c r="G427" t="n">
-        <v>-6641.970377286245</v>
+        <v>-6641.970377286248</v>
       </c>
     </row>
     <row r="428">
@@ -16300,13 +16300,13 @@
         <v>-351.16648144</v>
       </c>
       <c r="E429" t="n">
-        <v>-351.8460576002316</v>
+        <v>-351.8460576002317</v>
       </c>
       <c r="F429" t="n">
         <v>-6503.08298962963</v>
       </c>
       <c r="G429" t="n">
-        <v>-6515.667733337622</v>
+        <v>-6515.667733337624</v>
       </c>
     </row>
     <row r="430">
@@ -16325,13 +16325,13 @@
         <v>-353.16517991</v>
       </c>
       <c r="E430" t="n">
-        <v>-353.6475892788715</v>
+        <v>-353.6475892788716</v>
       </c>
       <c r="F430" t="n">
         <v>-6540.095924259259</v>
       </c>
       <c r="G430" t="n">
-        <v>-6549.029431090214</v>
+        <v>-6549.029431090215</v>
       </c>
     </row>
     <row r="431">
@@ -16350,13 +16350,13 @@
         <v>-358.93973384</v>
       </c>
       <c r="E431" t="n">
-        <v>-359.4798432619026</v>
+        <v>-359.4798432619027</v>
       </c>
       <c r="F431" t="n">
         <v>-6647.032108148148</v>
       </c>
       <c r="G431" t="n">
-        <v>-6657.034134479678</v>
+        <v>-6657.03413447968</v>
       </c>
     </row>
     <row r="432">
@@ -16406,7 +16406,7 @@
         <v>-6558.630405370371</v>
       </c>
       <c r="G433" t="n">
-        <v>-6568.464974086626</v>
+        <v>-6568.464974086627</v>
       </c>
     </row>
     <row r="434">
@@ -16425,13 +16425,13 @@
         <v>-352.72313346</v>
       </c>
       <c r="E434" t="n">
-        <v>-353.390515210812</v>
+        <v>-353.3905152108121</v>
       </c>
       <c r="F434" t="n">
         <v>-6531.909878888889</v>
       </c>
       <c r="G434" t="n">
-        <v>-6544.268800200221</v>
+        <v>-6544.268800200223</v>
       </c>
     </row>
     <row r="435">
@@ -16475,13 +16475,13 @@
         <v>-357.69558866</v>
       </c>
       <c r="E436" t="n">
-        <v>-358.0538041875594</v>
+        <v>-358.0538041875595</v>
       </c>
       <c r="F436" t="n">
         <v>-6623.992382592593</v>
       </c>
       <c r="G436" t="n">
-        <v>-6630.626003473321</v>
+        <v>-6630.626003473324</v>
       </c>
     </row>
     <row r="437">
@@ -16500,13 +16500,13 @@
         <v>-358.72661969</v>
       </c>
       <c r="E437" t="n">
-        <v>-359.227140433972</v>
+        <v>-359.2271404339721</v>
       </c>
       <c r="F437" t="n">
         <v>-6643.085549814815</v>
       </c>
       <c r="G437" t="n">
-        <v>-6652.354452480962</v>
+        <v>-6652.354452480965</v>
       </c>
     </row>
     <row r="438">
@@ -16525,7 +16525,7 @@
         <v>-359.04426592</v>
       </c>
       <c r="E438" t="n">
-        <v>-359.8001724172461</v>
+        <v>-359.8001724172462</v>
       </c>
       <c r="F438" t="n">
         <v>-6648.967887407407</v>
@@ -16631,7 +16631,7 @@
         <v>-6684.637775185185</v>
       </c>
       <c r="G442" t="n">
-        <v>-6698.137836580997</v>
+        <v>-6698.137836580998</v>
       </c>
     </row>
     <row r="443">
@@ -16650,13 +16650,13 @@
         <v>-361.88771205</v>
       </c>
       <c r="E443" t="n">
-        <v>-362.8785965142577</v>
+        <v>-362.8785965142578</v>
       </c>
       <c r="F443" t="n">
         <v>-6701.624297222223</v>
       </c>
       <c r="G443" t="n">
-        <v>-6719.974009523291</v>
+        <v>-6719.974009523292</v>
       </c>
     </row>
     <row r="444">
@@ -16700,13 +16700,13 @@
         <v>-355.8241979</v>
       </c>
       <c r="E445" t="n">
-        <v>-356.7985608239147</v>
+        <v>-356.7985608239148</v>
       </c>
       <c r="F445" t="n">
         <v>-6589.336998148148</v>
       </c>
       <c r="G445" t="n">
-        <v>-6607.38075599842</v>
+        <v>-6607.380755998422</v>
       </c>
     </row>
     <row r="446">
@@ -16725,13 +16725,13 @@
         <v>-359.1335007</v>
       </c>
       <c r="E446" t="n">
-        <v>-359.931813277242</v>
+        <v>-359.9318132772421</v>
       </c>
       <c r="F446" t="n">
         <v>-6650.620383333334</v>
       </c>
       <c r="G446" t="n">
-        <v>-6665.403949578556</v>
+        <v>-6665.403949578558</v>
       </c>
     </row>
     <row r="447">
@@ -16750,13 +16750,13 @@
         <v>-358.17030042</v>
       </c>
       <c r="E447" t="n">
-        <v>-358.8984231970675</v>
+        <v>-358.8984231970674</v>
       </c>
       <c r="F447" t="n">
         <v>-6632.783341111111</v>
       </c>
       <c r="G447" t="n">
-        <v>-6646.267096241991</v>
+        <v>-6646.267096241989</v>
       </c>
     </row>
     <row r="448">
@@ -16806,7 +16806,7 @@
         <v>-6639.416213703704</v>
       </c>
       <c r="G449" t="n">
-        <v>-6649.065344291494</v>
+        <v>-6649.065344291493</v>
       </c>
     </row>
     <row r="450">
@@ -16825,13 +16825,13 @@
         <v>-355.87679639</v>
       </c>
       <c r="E450" t="n">
-        <v>-356.5009750227549</v>
+        <v>-356.5009750227547</v>
       </c>
       <c r="F450" t="n">
         <v>-6590.311044259259</v>
       </c>
       <c r="G450" t="n">
-        <v>-6601.869907828794</v>
+        <v>-6601.869907828792</v>
       </c>
     </row>
     <row r="451">
@@ -16850,7 +16850,7 @@
         <v>-356.35511839</v>
       </c>
       <c r="E451" t="n">
-        <v>-357.0287886510416</v>
+        <v>-357.0287886510417</v>
       </c>
       <c r="F451" t="n">
         <v>-6599.168859074073</v>
@@ -16900,13 +16900,13 @@
         <v>-118.87354152</v>
       </c>
       <c r="E453" t="n">
-        <v>-117.5116497660063</v>
+        <v>-117.5116497660064</v>
       </c>
       <c r="F453" t="n">
         <v>-6604.08564</v>
       </c>
       <c r="G453" t="n">
-        <v>-6528.424987000351</v>
+        <v>-6528.424987000354</v>
       </c>
     </row>
     <row r="454">
@@ -16956,7 +16956,7 @@
         <v>-6559.125949814815</v>
       </c>
       <c r="G455" t="n">
-        <v>-6576.235804944309</v>
+        <v>-6576.23580494431</v>
       </c>
     </row>
     <row r="456">
@@ -16975,13 +16975,13 @@
         <v>-362.22169785</v>
       </c>
       <c r="E456" t="n">
-        <v>-362.9769545333175</v>
+        <v>-362.9769545333174</v>
       </c>
       <c r="F456" t="n">
         <v>-6707.809219444444</v>
       </c>
       <c r="G456" t="n">
-        <v>-6721.795454320694</v>
+        <v>-6721.795454320693</v>
       </c>
     </row>
     <row r="457">
@@ -17056,7 +17056,7 @@
         <v>-6666.367405925926</v>
       </c>
       <c r="G459" t="n">
-        <v>-6672.204467778092</v>
+        <v>-6672.204467778093</v>
       </c>
     </row>
     <row r="460">
@@ -17075,13 +17075,13 @@
         <v>-351.23891841</v>
       </c>
       <c r="E460" t="n">
-        <v>-352.7030680232673</v>
+        <v>-352.7030680232674</v>
       </c>
       <c r="F460" t="n">
         <v>-6504.424414999999</v>
       </c>
       <c r="G460" t="n">
-        <v>-6531.538296727173</v>
+        <v>-6531.538296727174</v>
       </c>
     </row>
     <row r="461">
@@ -17100,13 +17100,13 @@
         <v>-357.42909218</v>
       </c>
       <c r="E461" t="n">
-        <v>-358.1371790223659</v>
+        <v>-358.137179022366</v>
       </c>
       <c r="F461" t="n">
         <v>-6619.057262592592</v>
       </c>
       <c r="G461" t="n">
-        <v>-6632.169981895665</v>
+        <v>-6632.169981895666</v>
       </c>
     </row>
     <row r="462">
@@ -17150,13 +17150,13 @@
         <v>-360.56079538</v>
       </c>
       <c r="E463" t="n">
-        <v>-361.2172661870544</v>
+        <v>-361.2172661870545</v>
       </c>
       <c r="F463" t="n">
         <v>-6677.051766296297</v>
       </c>
       <c r="G463" t="n">
-        <v>-6689.2086330936</v>
+        <v>-6689.208633093601</v>
       </c>
     </row>
     <row r="464">
@@ -17181,7 +17181,7 @@
         <v>-6576.660292777779</v>
       </c>
       <c r="G464" t="n">
-        <v>-6594.676148665702</v>
+        <v>-6594.676148665703</v>
       </c>
     </row>
     <row r="465">
@@ -17200,13 +17200,13 @@
         <v>-360.47226347</v>
       </c>
       <c r="E465" t="n">
-        <v>-361.1938071403871</v>
+        <v>-361.193807140387</v>
       </c>
       <c r="F465" t="n">
         <v>-6675.412286481481</v>
       </c>
       <c r="G465" t="n">
-        <v>-6688.774206303464</v>
+        <v>-6688.774206303463</v>
       </c>
     </row>
     <row r="466">
@@ -17250,13 +17250,13 @@
         <v>-359.80939502</v>
       </c>
       <c r="E467" t="n">
-        <v>-360.545277866838</v>
+        <v>-360.5452778668381</v>
       </c>
       <c r="F467" t="n">
         <v>-6663.136944814814</v>
       </c>
       <c r="G467" t="n">
-        <v>-6676.764404941445</v>
+        <v>-6676.764404941446</v>
       </c>
     </row>
     <row r="468">
@@ -17300,13 +17300,13 @@
         <v>-358.7649163</v>
       </c>
       <c r="E469" t="n">
-        <v>-359.8251457187546</v>
+        <v>-359.8251457187545</v>
       </c>
       <c r="F469" t="n">
         <v>-6643.794746296296</v>
       </c>
       <c r="G469" t="n">
-        <v>-6663.428624421381</v>
+        <v>-6663.42862442138</v>
       </c>
     </row>
     <row r="470">
@@ -17431,7 +17431,7 @@
         <v>-6704.484890185186</v>
       </c>
       <c r="G474" t="n">
-        <v>-6714.149611479522</v>
+        <v>-6714.149611479523</v>
       </c>
     </row>
     <row r="475">
@@ -17481,7 +17481,7 @@
         <v>-6552.421909814815</v>
       </c>
       <c r="G476" t="n">
-        <v>-6573.611593129459</v>
+        <v>-6573.611593129461</v>
       </c>
     </row>
     <row r="477">
@@ -17550,13 +17550,13 @@
         <v>-365.41040556</v>
       </c>
       <c r="E479" t="n">
-        <v>-365.935918426761</v>
+        <v>-365.9359184267612</v>
       </c>
       <c r="F479" t="n">
         <v>-6766.859362222223</v>
       </c>
       <c r="G479" t="n">
-        <v>-6776.591081977054</v>
+        <v>-6776.591081977059</v>
       </c>
     </row>
     <row r="480">
@@ -17581,7 +17581,7 @@
         <v>-6733.032835185185</v>
       </c>
       <c r="G480" t="n">
-        <v>-6745.555837257766</v>
+        <v>-6745.555837257767</v>
       </c>
     </row>
     <row r="481">
@@ -17656,7 +17656,7 @@
         <v>-6830.977800555555</v>
       </c>
       <c r="G483" t="n">
-        <v>-6744.35525159995</v>
+        <v>-6744.355251599951</v>
       </c>
     </row>
     <row r="484">
@@ -17681,7 +17681,7 @@
         <v>-6817.374236111111</v>
       </c>
       <c r="G484" t="n">
-        <v>-6736.728551761949</v>
+        <v>-6736.728551761951</v>
       </c>
     </row>
     <row r="485">
@@ -17700,13 +17700,13 @@
         <v>-363.71967731</v>
       </c>
       <c r="E485" t="n">
-        <v>-364.1574006677396</v>
+        <v>-364.1574006677397</v>
       </c>
       <c r="F485" t="n">
         <v>-6735.549579814815</v>
       </c>
       <c r="G485" t="n">
-        <v>-6743.655567921104</v>
+        <v>-6743.655567921105</v>
       </c>
     </row>
     <row r="486">
@@ -17731,7 +17731,7 @@
         <v>-6755.194235555556</v>
       </c>
       <c r="G486" t="n">
-        <v>-6775.624343038235</v>
+        <v>-6775.624343038236</v>
       </c>
     </row>
     <row r="487">
@@ -17781,7 +17781,7 @@
         <v>-6750.488690185185</v>
       </c>
       <c r="G488" t="n">
-        <v>-6760.617166641872</v>
+        <v>-6760.617166641871</v>
       </c>
     </row>
     <row r="489">
@@ -17800,13 +17800,13 @@
         <v>-364.00273323</v>
       </c>
       <c r="E489" t="n">
-        <v>-364.7945673170807</v>
+        <v>-364.7945673170808</v>
       </c>
       <c r="F489" t="n">
         <v>-6740.791356111112</v>
       </c>
       <c r="G489" t="n">
-        <v>-6755.45495031631</v>
+        <v>-6755.454950316311</v>
       </c>
     </row>
     <row r="490">
@@ -17831,7 +17831,7 @@
         <v>-6897.294763888889</v>
       </c>
       <c r="G490" t="n">
-        <v>-6805.624235163516</v>
+        <v>-6805.624235163517</v>
       </c>
     </row>
     <row r="491">
@@ -17850,13 +17850,13 @@
         <v>-363.27423588</v>
       </c>
       <c r="E491" t="n">
-        <v>-363.7037866684511</v>
+        <v>-363.7037866684512</v>
       </c>
       <c r="F491" t="n">
         <v>-6727.300664444444</v>
       </c>
       <c r="G491" t="n">
-        <v>-6735.255308675021</v>
+        <v>-6735.255308675022</v>
       </c>
     </row>
     <row r="492">
@@ -17875,13 +17875,13 @@
         <v>-122.71773735</v>
       </c>
       <c r="E492" t="n">
-        <v>-121.1621978648171</v>
+        <v>-121.1621978648172</v>
       </c>
       <c r="F492" t="n">
         <v>-6817.652075</v>
       </c>
       <c r="G492" t="n">
-        <v>-6731.233214712063</v>
+        <v>-6731.233214712065</v>
       </c>
     </row>
     <row r="493">
@@ -17956,7 +17956,7 @@
         <v>-6762.375608888889</v>
       </c>
       <c r="G495" t="n">
-        <v>-6770.084348051025</v>
+        <v>-6770.084348051027</v>
       </c>
     </row>
     <row r="496">
@@ -17981,7 +17981,7 @@
         <v>-6736.377025555556</v>
       </c>
       <c r="G496" t="n">
-        <v>-6649.800958320581</v>
+        <v>-6649.800958320582</v>
       </c>
     </row>
     <row r="497">
@@ -18000,13 +18000,13 @@
         <v>-371.38422421</v>
       </c>
       <c r="E497" t="n">
-        <v>-372.0825282582269</v>
+        <v>-372.082528258227</v>
       </c>
       <c r="F497" t="n">
         <v>-6877.485633518519</v>
       </c>
       <c r="G497" t="n">
-        <v>-6890.417189967165</v>
+        <v>-6890.417189967166</v>
       </c>
     </row>
     <row r="498">
@@ -18031,7 +18031,7 @@
         <v>-6853.988946111112</v>
       </c>
       <c r="G498" t="n">
-        <v>-6771.977088487427</v>
+        <v>-6771.977088487429</v>
       </c>
     </row>
     <row r="499">
@@ -18050,13 +18050,13 @@
         <v>-121.0077647</v>
       </c>
       <c r="E499" t="n">
-        <v>-119.5567869353219</v>
+        <v>-119.556786935322</v>
       </c>
       <c r="F499" t="n">
         <v>-6722.653594444444</v>
       </c>
       <c r="G499" t="n">
-        <v>-6642.043718628996</v>
+        <v>-6642.043718628997</v>
       </c>
     </row>
     <row r="500">
@@ -18125,13 +18125,13 @@
         <v>-363.26320365</v>
       </c>
       <c r="E502" t="n">
-        <v>-363.8728044837538</v>
+        <v>-363.8728044837539</v>
       </c>
       <c r="F502" t="n">
         <v>-6727.096363888889</v>
       </c>
       <c r="G502" t="n">
-        <v>-6738.385268217664</v>
+        <v>-6738.385268217665</v>
       </c>
     </row>
     <row r="503">
@@ -18175,13 +18175,13 @@
         <v>-363.37237427</v>
       </c>
       <c r="E504" t="n">
-        <v>-364.1647249207211</v>
+        <v>-364.1647249207212</v>
       </c>
       <c r="F504" t="n">
         <v>-6729.118042037037</v>
       </c>
       <c r="G504" t="n">
-        <v>-6743.791202235577</v>
+        <v>-6743.791202235578</v>
       </c>
     </row>
     <row r="505">
@@ -18300,13 +18300,13 @@
         <v>-363.60867981</v>
       </c>
       <c r="E509" t="n">
-        <v>-364.2785504299716</v>
+        <v>-364.2785504299717</v>
       </c>
       <c r="F509" t="n">
         <v>-6733.494070555555</v>
       </c>
       <c r="G509" t="n">
-        <v>-6745.899082036512</v>
+        <v>-6745.899082036514</v>
       </c>
     </row>
     <row r="510">
@@ -18356,7 +18356,7 @@
         <v>-6752.294239444444</v>
       </c>
       <c r="G511" t="n">
-        <v>-6668.374120315817</v>
+        <v>-6668.374120315819</v>
       </c>
     </row>
     <row r="512">
@@ -18400,13 +18400,13 @@
         <v>-364.23859016</v>
       </c>
       <c r="E513" t="n">
-        <v>-365.2824001069426</v>
+        <v>-365.2824001069428</v>
       </c>
       <c r="F513" t="n">
         <v>-6745.159077037038</v>
       </c>
       <c r="G513" t="n">
-        <v>-6764.488890869308</v>
+        <v>-6764.48889086931</v>
       </c>
     </row>
     <row r="514">
@@ -18431,7 +18431,7 @@
         <v>-6733.671805000001</v>
       </c>
       <c r="G514" t="n">
-        <v>-6654.903801742339</v>
+        <v>-6654.903801742341</v>
       </c>
     </row>
     <row r="515">
@@ -18456,7 +18456,7 @@
         <v>-6718.192337962962</v>
       </c>
       <c r="G515" t="n">
-        <v>-6741.336878855944</v>
+        <v>-6741.336878855945</v>
       </c>
     </row>
     <row r="516">
@@ -18481,7 +18481,7 @@
         <v>-6790.611953888888</v>
       </c>
       <c r="G516" t="n">
-        <v>-6805.821224529921</v>
+        <v>-6805.821224529923</v>
       </c>
     </row>
     <row r="517">
@@ -18500,13 +18500,13 @@
         <v>-365.81135092</v>
       </c>
       <c r="E517" t="n">
-        <v>-367.0429528068618</v>
+        <v>-367.0429528068619</v>
       </c>
       <c r="F517" t="n">
         <v>-6774.284276296296</v>
       </c>
       <c r="G517" t="n">
-        <v>-6797.09171864559</v>
+        <v>-6797.091718645591</v>
       </c>
     </row>
     <row r="518">
@@ -18525,13 +18525,13 @@
         <v>-121.56966149</v>
       </c>
       <c r="E518" t="n">
-        <v>-120.086157565517</v>
+        <v>-120.0861575655171</v>
       </c>
       <c r="F518" t="n">
         <v>-6753.870082777777</v>
       </c>
       <c r="G518" t="n">
-        <v>-6671.453198084279</v>
+        <v>-6671.453198084281</v>
       </c>
     </row>
     <row r="519">
@@ -18575,13 +18575,13 @@
         <v>-122.50780707</v>
       </c>
       <c r="E520" t="n">
-        <v>-120.9999995739425</v>
+        <v>-120.9999995739426</v>
       </c>
       <c r="F520" t="n">
         <v>-6805.989281666666</v>
       </c>
       <c r="G520" t="n">
-        <v>-6722.222198552362</v>
+        <v>-6722.222198552366</v>
       </c>
     </row>
     <row r="521">
@@ -18706,7 +18706,7 @@
         <v>-6798.027550740741</v>
       </c>
       <c r="G525" t="n">
-        <v>-6808.683305302823</v>
+        <v>-6808.683305302825</v>
       </c>
     </row>
     <row r="526">
@@ -18750,13 +18750,13 @@
         <v>-368.52269109</v>
       </c>
       <c r="E527" t="n">
-        <v>-369.0974262619834</v>
+        <v>-369.0974262619835</v>
       </c>
       <c r="F527" t="n">
         <v>-6824.494279444445</v>
       </c>
       <c r="G527" t="n">
-        <v>-6835.137523370063</v>
+        <v>-6835.137523370064</v>
       </c>
     </row>
     <row r="528">
@@ -18775,7 +18775,7 @@
         <v>-363.87208615</v>
       </c>
       <c r="E528" t="n">
-        <v>-364.786248475238</v>
+        <v>-364.7862484752381</v>
       </c>
       <c r="F528" t="n">
         <v>-6738.371965740741</v>
@@ -18825,13 +18825,13 @@
         <v>-121.38152211</v>
       </c>
       <c r="E530" t="n">
-        <v>-119.6077192563862</v>
+        <v>-119.6077192563863</v>
       </c>
       <c r="F530" t="n">
         <v>-6743.417895</v>
       </c>
       <c r="G530" t="n">
-        <v>-6644.873292021458</v>
+        <v>-6644.87329202146</v>
       </c>
     </row>
     <row r="531">
@@ -18881,7 +18881,7 @@
         <v>-6823.842659999999</v>
       </c>
       <c r="G532" t="n">
-        <v>-6733.394540000965</v>
+        <v>-6733.394540000966</v>
       </c>
     </row>
     <row r="533">
@@ -18981,7 +18981,7 @@
         <v>-6923.908387777778</v>
       </c>
       <c r="G536" t="n">
-        <v>-6839.229564072714</v>
+        <v>-6839.229564072716</v>
       </c>
     </row>
     <row r="537">
@@ -19000,13 +19000,13 @@
         <v>-123.43586562</v>
       </c>
       <c r="E537" t="n">
-        <v>-121.7612479540526</v>
+        <v>-121.7612479540527</v>
       </c>
       <c r="F537" t="n">
         <v>-6857.54809</v>
       </c>
       <c r="G537" t="n">
-        <v>-6764.513775225147</v>
+        <v>-6764.513775225148</v>
       </c>
     </row>
     <row r="538">
@@ -19050,13 +19050,13 @@
         <v>-362.79156266</v>
       </c>
       <c r="E539" t="n">
-        <v>-363.355047675687</v>
+        <v>-363.3550476756872</v>
       </c>
       <c r="F539" t="n">
         <v>-6718.362271481481</v>
       </c>
       <c r="G539" t="n">
-        <v>-6728.79717917939</v>
+        <v>-6728.797179179393</v>
       </c>
     </row>
     <row r="540">
@@ -19075,13 +19075,13 @@
         <v>-365.60738294</v>
       </c>
       <c r="E540" t="n">
-        <v>-366.583669915269</v>
+        <v>-366.5836699152691</v>
       </c>
       <c r="F540" t="n">
         <v>-6770.507091481481</v>
       </c>
       <c r="G540" t="n">
-        <v>-6788.586479912389</v>
+        <v>-6788.58647991239</v>
       </c>
     </row>
     <row r="541">
@@ -19106,7 +19106,7 @@
         <v>-6796.189723888889</v>
       </c>
       <c r="G541" t="n">
-        <v>-6724.754428952408</v>
+        <v>-6724.75442895241</v>
       </c>
     </row>
     <row r="542">
@@ -19131,7 +19131,7 @@
         <v>-6851.791218888889</v>
       </c>
       <c r="G542" t="n">
-        <v>-6776.654048999095</v>
+        <v>-6776.654048999097</v>
       </c>
     </row>
     <row r="543">
@@ -19150,13 +19150,13 @@
         <v>-364.25203448</v>
       </c>
       <c r="E543" t="n">
-        <v>-365.0867832788484</v>
+        <v>-365.0867832788485</v>
       </c>
       <c r="F543" t="n">
         <v>-6745.408045925927</v>
       </c>
       <c r="G543" t="n">
-        <v>-6760.866357015712</v>
+        <v>-6760.866357015714</v>
       </c>
     </row>
     <row r="544">
@@ -19181,7 +19181,7 @@
         <v>-6843.832901111111</v>
       </c>
       <c r="G544" t="n">
-        <v>-6773.115756906023</v>
+        <v>-6773.115756906025</v>
       </c>
     </row>
     <row r="545">
@@ -19225,13 +19225,13 @@
         <v>-362.73265687</v>
       </c>
       <c r="E546" t="n">
-        <v>-363.5804901487368</v>
+        <v>-363.5804901487369</v>
       </c>
       <c r="F546" t="n">
         <v>-6717.271423518519</v>
       </c>
       <c r="G546" t="n">
-        <v>-6732.972039791422</v>
+        <v>-6732.972039791423</v>
       </c>
     </row>
     <row r="547">
@@ -19300,13 +19300,13 @@
         <v>-363.24694169</v>
       </c>
       <c r="E549" t="n">
-        <v>-363.7561016049271</v>
+        <v>-363.7561016049272</v>
       </c>
       <c r="F549" t="n">
         <v>-6726.795216481481</v>
       </c>
       <c r="G549" t="n">
-        <v>-6736.224103794946</v>
+        <v>-6736.224103794947</v>
       </c>
     </row>
     <row r="550">
@@ -19325,13 +19325,13 @@
         <v>-366.62790669</v>
       </c>
       <c r="E550" t="n">
-        <v>-367.6967898109816</v>
+        <v>-367.6967898109817</v>
       </c>
       <c r="F550" t="n">
         <v>-6789.405679444444</v>
       </c>
       <c r="G550" t="n">
-        <v>-6809.199811314474</v>
+        <v>-6809.199811314475</v>
       </c>
     </row>
     <row r="551">
@@ -19375,13 +19375,13 @@
         <v>-365.54156507</v>
       </c>
       <c r="E552" t="n">
-        <v>-366.1966581687846</v>
+        <v>-366.1966581687847</v>
       </c>
       <c r="F552" t="n">
         <v>-6769.288242037037</v>
       </c>
       <c r="G552" t="n">
-        <v>-6781.419595718234</v>
+        <v>-6781.419595718235</v>
       </c>
     </row>
     <row r="553">
@@ -19425,13 +19425,13 @@
         <v>-364.88905358</v>
       </c>
       <c r="E554" t="n">
-        <v>-365.3316612737344</v>
+        <v>-365.3316612737345</v>
       </c>
       <c r="F554" t="n">
         <v>-6757.204695925926</v>
       </c>
       <c r="G554" t="n">
-        <v>-6765.401134698785</v>
+        <v>-6765.401134698786</v>
       </c>
     </row>
     <row r="555">
@@ -19450,13 +19450,13 @@
         <v>-363.30853792</v>
       </c>
       <c r="E555" t="n">
-        <v>-363.8907837506135</v>
+        <v>-363.8907837506134</v>
       </c>
       <c r="F555" t="n">
         <v>-6727.935887407407</v>
       </c>
       <c r="G555" t="n">
-        <v>-6738.718217603953</v>
+        <v>-6738.718217603951</v>
       </c>
     </row>
     <row r="556">
@@ -19506,7 +19506,7 @@
         <v>-6769.881743888889</v>
       </c>
       <c r="G557" t="n">
-        <v>-6687.283547920146</v>
+        <v>-6687.283547920148</v>
       </c>
     </row>
     <row r="558">
@@ -19525,13 +19525,13 @@
         <v>-369.8479563</v>
       </c>
       <c r="E558" t="n">
-        <v>-370.5922505110669</v>
+        <v>-370.592250511067</v>
       </c>
       <c r="F558" t="n">
         <v>-6849.036227777779</v>
       </c>
       <c r="G558" t="n">
-        <v>-6862.819453908646</v>
+        <v>-6862.819453908648</v>
       </c>
     </row>
     <row r="559">
@@ -19556,7 +19556,7 @@
         <v>-6754.827330740741</v>
       </c>
       <c r="G559" t="n">
-        <v>-6765.260329408063</v>
+        <v>-6765.260329408064</v>
       </c>
     </row>
     <row r="560">
@@ -19600,13 +19600,13 @@
         <v>-363.74306484</v>
       </c>
       <c r="E561" t="n">
-        <v>-364.0774737766226</v>
+        <v>-364.0774737766227</v>
       </c>
       <c r="F561" t="n">
         <v>-6735.982682222222</v>
       </c>
       <c r="G561" t="n">
-        <v>-6742.175440307827</v>
+        <v>-6742.175440307828</v>
       </c>
     </row>
     <row r="562">
@@ -19631,7 +19631,7 @@
         <v>-6719.568811666667</v>
       </c>
       <c r="G562" t="n">
-        <v>-6735.236221604625</v>
+        <v>-6735.236221604626</v>
       </c>
     </row>
     <row r="563">
@@ -19656,7 +19656,7 @@
         <v>-6729.027347777777</v>
       </c>
       <c r="G563" t="n">
-        <v>-6650.995155305684</v>
+        <v>-6650.995155305685</v>
       </c>
     </row>
     <row r="564">
@@ -19675,13 +19675,13 @@
         <v>-364.09723483</v>
       </c>
       <c r="E564" t="n">
-        <v>-364.7558869288509</v>
+        <v>-364.755886928851</v>
       </c>
       <c r="F564" t="n">
         <v>-6742.54138574074</v>
       </c>
       <c r="G564" t="n">
-        <v>-6754.738646830572</v>
+        <v>-6754.738646830574</v>
       </c>
     </row>
     <row r="565">
@@ -19706,7 +19706,7 @@
         <v>-6857.002322222222</v>
       </c>
       <c r="G565" t="n">
-        <v>-6777.198496349753</v>
+        <v>-6777.198496349754</v>
       </c>
     </row>
     <row r="566">
@@ -19725,13 +19725,13 @@
         <v>-368.42958085</v>
       </c>
       <c r="E566" t="n">
-        <v>-369.4772896753832</v>
+        <v>-369.4772896753834</v>
       </c>
       <c r="F566" t="n">
         <v>-6822.77001574074</v>
       </c>
       <c r="G566" t="n">
-        <v>-6842.172031025616</v>
+        <v>-6842.172031025618</v>
       </c>
     </row>
     <row r="567">
@@ -19825,13 +19825,13 @@
         <v>-362.59968794</v>
       </c>
       <c r="E570" t="n">
-        <v>-362.9813123109158</v>
+        <v>-362.9813123109159</v>
       </c>
       <c r="F570" t="n">
         <v>-6714.809035925927</v>
       </c>
       <c r="G570" t="n">
-        <v>-6721.876153905848</v>
+        <v>-6721.876153905851</v>
       </c>
     </row>
     <row r="571">
@@ -19856,7 +19856,7 @@
         <v>-6742.315502777778</v>
       </c>
       <c r="G571" t="n">
-        <v>-6760.010202214411</v>
+        <v>-6760.010202214412</v>
       </c>
     </row>
     <row r="572">
@@ -19875,13 +19875,13 @@
         <v>-363.23019453</v>
       </c>
       <c r="E572" t="n">
-        <v>-363.7586616274338</v>
+        <v>-363.7586616274339</v>
       </c>
       <c r="F572" t="n">
         <v>-6726.485083888889</v>
       </c>
       <c r="G572" t="n">
-        <v>-6736.271511619144</v>
+        <v>-6736.271511619146</v>
       </c>
     </row>
     <row r="573">
@@ -19900,13 +19900,13 @@
         <v>-365.5672135</v>
       </c>
       <c r="E573" t="n">
-        <v>-365.9679791296634</v>
+        <v>-365.9679791296635</v>
       </c>
       <c r="F573" t="n">
         <v>-6769.763212962962</v>
       </c>
       <c r="G573" t="n">
-        <v>-6777.184798697471</v>
+        <v>-6777.184798697472</v>
       </c>
     </row>
     <row r="574">
@@ -19931,7 +19931,7 @@
         <v>-6768.527379814815</v>
       </c>
       <c r="G574" t="n">
-        <v>-6788.773440886857</v>
+        <v>-6788.773440886858</v>
       </c>
     </row>
     <row r="575">
@@ -19981,7 +19981,7 @@
         <v>-6883.550936111112</v>
       </c>
       <c r="G576" t="n">
-        <v>-6796.004559228055</v>
+        <v>-6796.004559228057</v>
       </c>
     </row>
     <row r="577">
@@ -20025,7 +20025,7 @@
         <v>-366.67019623</v>
       </c>
       <c r="E578" t="n">
-        <v>-367.1153565028495</v>
+        <v>-367.1153565028496</v>
       </c>
       <c r="F578" t="n">
         <v>-6790.188819074074</v>
@@ -20056,7 +20056,7 @@
         <v>-6791.368505370371</v>
       </c>
       <c r="G579" t="n">
-        <v>-6801.239349917779</v>
+        <v>-6801.239349917781</v>
       </c>
     </row>
     <row r="580">
@@ -20106,7 +20106,7 @@
         <v>-6819.060850555556</v>
       </c>
       <c r="G581" t="n">
-        <v>-6731.688061565088</v>
+        <v>-6731.68806156509</v>
       </c>
     </row>
     <row r="582">
@@ -20125,13 +20125,13 @@
         <v>-366.67947125</v>
       </c>
       <c r="E582" t="n">
-        <v>-367.6228094969001</v>
+        <v>-367.6228094969</v>
       </c>
       <c r="F582" t="n">
         <v>-6790.360578703704</v>
       </c>
       <c r="G582" t="n">
-        <v>-6807.829805498151</v>
+        <v>-6807.829805498149</v>
       </c>
     </row>
     <row r="583">
@@ -20156,7 +20156,7 @@
         <v>-6732.992421111111</v>
       </c>
       <c r="G583" t="n">
-        <v>-6653.503686600705</v>
+        <v>-6653.503686600707</v>
       </c>
     </row>
     <row r="584">
@@ -20206,7 +20206,7 @@
         <v>-6762.846208518518</v>
       </c>
       <c r="G585" t="n">
-        <v>-6774.511713246199</v>
+        <v>-6774.5117132462</v>
       </c>
     </row>
     <row r="586">
@@ -20256,7 +20256,7 @@
         <v>-6717.016960370371</v>
       </c>
       <c r="G587" t="n">
-        <v>-6731.184396668546</v>
+        <v>-6731.184396668547</v>
       </c>
     </row>
     <row r="588">
@@ -20275,13 +20275,13 @@
         <v>-364.42533189</v>
       </c>
       <c r="E588" t="n">
-        <v>-365.0462901435943</v>
+        <v>-365.0462901435944</v>
       </c>
       <c r="F588" t="n">
         <v>-6748.617257222221</v>
       </c>
       <c r="G588" t="n">
-        <v>-6760.116484140635</v>
+        <v>-6760.116484140636</v>
       </c>
     </row>
     <row r="589">
@@ -20350,13 +20350,13 @@
         <v>-368.2403116</v>
       </c>
       <c r="E591" t="n">
-        <v>-369.1383767698768</v>
+        <v>-369.1383767698769</v>
       </c>
       <c r="F591" t="n">
         <v>-6819.265029629629</v>
       </c>
       <c r="G591" t="n">
-        <v>-6835.89586610883</v>
+        <v>-6835.895866108831</v>
       </c>
     </row>
     <row r="592">
@@ -20381,7 +20381,7 @@
         <v>-6718.991848333333</v>
       </c>
       <c r="G592" t="n">
-        <v>-6629.509498545287</v>
+        <v>-6629.509498545289</v>
       </c>
     </row>
     <row r="593">
@@ -20431,7 +20431,7 @@
         <v>-6748.662568518518</v>
       </c>
       <c r="G594" t="n">
-        <v>-6767.939177464425</v>
+        <v>-6767.939177464426</v>
       </c>
     </row>
     <row r="595">
@@ -20475,13 +20475,13 @@
         <v>-122.24062243</v>
       </c>
       <c r="E596" t="n">
-        <v>-120.786383150965</v>
+        <v>-120.7863831509651</v>
       </c>
       <c r="F596" t="n">
         <v>-6791.145690555556</v>
       </c>
       <c r="G596" t="n">
-        <v>-6710.354619498057</v>
+        <v>-6710.354619498059</v>
       </c>
     </row>
     <row r="597">
@@ -20556,7 +20556,7 @@
         <v>-6820.877762222222</v>
       </c>
       <c r="G599" t="n">
-        <v>-6735.364986066814</v>
+        <v>-6735.364986066816</v>
       </c>
     </row>
     <row r="600">
@@ -20575,13 +20575,13 @@
         <v>-122.65356535</v>
       </c>
       <c r="E600" t="n">
-        <v>-120.960377587859</v>
+        <v>-120.9603775878591</v>
       </c>
       <c r="F600" t="n">
         <v>-6814.086963888888</v>
       </c>
       <c r="G600" t="n">
-        <v>-6720.020977103279</v>
+        <v>-6720.020977103281</v>
       </c>
     </row>
     <row r="601">
@@ -20600,7 +20600,7 @@
         <v>-366.02658997</v>
       </c>
       <c r="E601" t="n">
-        <v>-366.8677283030568</v>
+        <v>-366.8677283030569</v>
       </c>
       <c r="F601" t="n">
         <v>-6778.27018462963</v>
@@ -20656,7 +20656,7 @@
         <v>-6827.405846111111</v>
       </c>
       <c r="G603" t="n">
-        <v>-6747.268121910533</v>
+        <v>-6747.268121910535</v>
       </c>
     </row>
     <row r="604">
@@ -20781,7 +20781,7 @@
         <v>-6894.844555</v>
       </c>
       <c r="G608" t="n">
-        <v>-6803.337259702448</v>
+        <v>-6803.33725970245</v>
       </c>
     </row>
     <row r="609">
@@ -20806,7 +20806,7 @@
         <v>-6787.312907962963</v>
       </c>
       <c r="G609" t="n">
-        <v>-6795.167895521659</v>
+        <v>-6795.167895521658</v>
       </c>
     </row>
     <row r="610">
@@ -20825,13 +20825,13 @@
         <v>-362.94431163</v>
       </c>
       <c r="E610" t="n">
-        <v>-363.5554330858649</v>
+        <v>-363.555433085865</v>
       </c>
       <c r="F610" t="n">
         <v>-6721.190956111112</v>
       </c>
       <c r="G610" t="n">
-        <v>-6732.50802010861</v>
+        <v>-6732.508020108611</v>
       </c>
     </row>
     <row r="611">
@@ -20850,7 +20850,7 @@
         <v>-366.69303484</v>
       </c>
       <c r="E611" t="n">
-        <v>-367.6461179447154</v>
+        <v>-367.6461179447155</v>
       </c>
       <c r="F611" t="n">
         <v>-6790.611756296296</v>
@@ -20900,13 +20900,13 @@
         <v>-363.49020779</v>
       </c>
       <c r="E613" t="n">
-        <v>-364.2646188841159</v>
+        <v>-364.264618884116</v>
       </c>
       <c r="F613" t="n">
         <v>-6731.300144259259</v>
       </c>
       <c r="G613" t="n">
-        <v>-6745.641090446592</v>
+        <v>-6745.641090446593</v>
       </c>
     </row>
     <row r="614">
@@ -20925,13 +20925,13 @@
         <v>-123.41634851</v>
       </c>
       <c r="E614" t="n">
-        <v>-121.8785187946152</v>
+        <v>-121.8785187946153</v>
       </c>
       <c r="F614" t="n">
         <v>-6856.463806111112</v>
       </c>
       <c r="G614" t="n">
-        <v>-6771.028821923069</v>
+        <v>-6771.028821923071</v>
       </c>
     </row>
     <row r="615">
@@ -20975,7 +20975,7 @@
         <v>-371.47163124</v>
       </c>
       <c r="E616" t="n">
-        <v>-372.1081793838979</v>
+        <v>-372.108179383898</v>
       </c>
       <c r="F616" t="n">
         <v>-6879.104282222223</v>
@@ -21000,13 +21000,13 @@
         <v>-363.09860747</v>
       </c>
       <c r="E617" t="n">
-        <v>-363.8363362960895</v>
+        <v>-363.8363362960894</v>
       </c>
       <c r="F617" t="n">
         <v>-6724.048286481481</v>
       </c>
       <c r="G617" t="n">
-        <v>-6737.709931409064</v>
+        <v>-6737.709931409062</v>
       </c>
     </row>
     <row r="618">
@@ -21106,7 +21106,7 @@
         <v>-6875.263714444444</v>
       </c>
       <c r="G621" t="n">
-        <v>-6789.598123744689</v>
+        <v>-6789.598123744691</v>
       </c>
     </row>
     <row r="622">
@@ -21125,13 +21125,13 @@
         <v>-364.62448686</v>
       </c>
       <c r="E622" t="n">
-        <v>-365.7598784639274</v>
+        <v>-365.7598784639275</v>
       </c>
       <c r="F622" t="n">
         <v>-6752.305312222223</v>
       </c>
       <c r="G622" t="n">
-        <v>-6773.331082665322</v>
+        <v>-6773.331082665325</v>
       </c>
     </row>
     <row r="623">
@@ -21200,13 +21200,13 @@
         <v>-363.60348382</v>
       </c>
       <c r="E625" t="n">
-        <v>-363.9869435193564</v>
+        <v>-363.9869435193565</v>
       </c>
       <c r="F625" t="n">
         <v>-6733.397848518519</v>
       </c>
       <c r="G625" t="n">
-        <v>-6740.498954062156</v>
+        <v>-6740.498954062157</v>
       </c>
     </row>
     <row r="626">
@@ -21231,7 +21231,7 @@
         <v>-6784.519828333334</v>
       </c>
       <c r="G626" t="n">
-        <v>-6698.653899434714</v>
+        <v>-6698.653899434716</v>
       </c>
     </row>
     <row r="627">
@@ -21256,7 +21256,7 @@
         <v>-6756.381464074074</v>
       </c>
       <c r="G627" t="n">
-        <v>-6768.035252031307</v>
+        <v>-6768.035252031309</v>
       </c>
     </row>
     <row r="628">
@@ -21281,7 +21281,7 @@
         <v>-6765.465725185186</v>
       </c>
       <c r="G628" t="n">
-        <v>-6781.998243182278</v>
+        <v>-6781.998243182279</v>
       </c>
     </row>
     <row r="629">
@@ -21325,13 +21325,13 @@
         <v>-370.46294146</v>
       </c>
       <c r="E630" t="n">
-        <v>-371.1013557160673</v>
+        <v>-371.1013557160672</v>
       </c>
       <c r="F630" t="n">
         <v>-6860.424841851852</v>
       </c>
       <c r="G630" t="n">
-        <v>-6872.24732807532</v>
+        <v>-6872.247328075319</v>
       </c>
     </row>
     <row r="631">
@@ -21350,13 +21350,13 @@
         <v>-363.26412556</v>
       </c>
       <c r="E631" t="n">
-        <v>-364.1028798820943</v>
+        <v>-364.1028798820944</v>
       </c>
       <c r="F631" t="n">
         <v>-6727.113436296297</v>
       </c>
       <c r="G631" t="n">
-        <v>-6742.645923742488</v>
+        <v>-6742.645923742489</v>
       </c>
     </row>
     <row r="632">
@@ -21375,13 +21375,13 @@
         <v>-365.87190291</v>
       </c>
       <c r="E632" t="n">
-        <v>-366.5995111992918</v>
+        <v>-366.5995111992919</v>
       </c>
       <c r="F632" t="n">
         <v>-6775.405609444445</v>
       </c>
       <c r="G632" t="n">
-        <v>-6788.879837023923</v>
+        <v>-6788.879837023925</v>
       </c>
     </row>
     <row r="633">
@@ -21400,13 +21400,13 @@
         <v>-363.98082642</v>
       </c>
       <c r="E633" t="n">
-        <v>-364.7702793798511</v>
+        <v>-364.770279379851</v>
       </c>
       <c r="F633" t="n">
         <v>-6740.385674444446</v>
       </c>
       <c r="G633" t="n">
-        <v>-6755.005173700947</v>
+        <v>-6755.005173700945</v>
       </c>
     </row>
     <row r="634">
@@ -21425,13 +21425,13 @@
         <v>-362.80903906</v>
       </c>
       <c r="E634" t="n">
-        <v>-363.7156986431654</v>
+        <v>-363.7156986431656</v>
       </c>
       <c r="F634" t="n">
         <v>-6718.685908518518</v>
       </c>
       <c r="G634" t="n">
-        <v>-6735.47590079936</v>
+        <v>-6735.475900799363</v>
       </c>
     </row>
     <row r="635">
@@ -21450,13 +21450,13 @@
         <v>-362.82289086</v>
       </c>
       <c r="E635" t="n">
-        <v>-363.2376295156345</v>
+        <v>-363.2376295156346</v>
       </c>
       <c r="F635" t="n">
         <v>-6718.942423333333</v>
       </c>
       <c r="G635" t="n">
-        <v>-6726.622768808046</v>
+        <v>-6726.622768808047</v>
       </c>
     </row>
     <row r="636">
@@ -21525,13 +21525,13 @@
         <v>-362.77391588</v>
       </c>
       <c r="E638" t="n">
-        <v>-363.7299157616624</v>
+        <v>-363.7299157616626</v>
       </c>
       <c r="F638" t="n">
         <v>-6718.035479259259</v>
       </c>
       <c r="G638" t="n">
-        <v>-6735.739180771526</v>
+        <v>-6735.739180771529</v>
       </c>
     </row>
     <row r="639">
@@ -21550,13 +21550,13 @@
         <v>-367.84326054</v>
       </c>
       <c r="E639" t="n">
-        <v>-368.5616464291237</v>
+        <v>-368.5616464291238</v>
       </c>
       <c r="F639" t="n">
         <v>-6811.912232222222</v>
       </c>
       <c r="G639" t="n">
-        <v>-6825.215674613402</v>
+        <v>-6825.215674613403</v>
       </c>
     </row>
     <row r="640">
@@ -21575,13 +21575,13 @@
         <v>-122.06385901</v>
       </c>
       <c r="E640" t="n">
-        <v>-120.7130493977413</v>
+        <v>-120.7130493977414</v>
       </c>
       <c r="F640" t="n">
         <v>-6781.325500555556</v>
       </c>
       <c r="G640" t="n">
-        <v>-6706.280522096741</v>
+        <v>-6706.280522096743</v>
       </c>
     </row>
     <row r="641">
@@ -21625,13 +21625,13 @@
         <v>-366.21469079</v>
       </c>
       <c r="E642" t="n">
-        <v>-367.0487968349926</v>
+        <v>-367.0487968349925</v>
       </c>
       <c r="F642" t="n">
         <v>-6781.753533148149</v>
       </c>
       <c r="G642" t="n">
-        <v>-6797.199941388752</v>
+        <v>-6797.199941388751</v>
       </c>
     </row>
     <row r="643">
@@ -21650,13 +21650,13 @@
         <v>-365.87074682</v>
       </c>
       <c r="E643" t="n">
-        <v>-366.5040889489139</v>
+        <v>-366.504088948914</v>
       </c>
       <c r="F643" t="n">
         <v>-6775.38420037037</v>
       </c>
       <c r="G643" t="n">
-        <v>-6787.112758313219</v>
+        <v>-6787.112758313222</v>
       </c>
     </row>
     <row r="644">
@@ -21681,7 +21681,7 @@
         <v>-6810.506632777778</v>
       </c>
       <c r="G644" t="n">
-        <v>-6724.855729803345</v>
+        <v>-6724.855729803347</v>
       </c>
     </row>
     <row r="645">
@@ -21775,13 +21775,13 @@
         <v>-362.54308031</v>
       </c>
       <c r="E648" t="n">
-        <v>-363.1672530181948</v>
+        <v>-363.1672530181949</v>
       </c>
       <c r="F648" t="n">
         <v>-6713.760746481481</v>
       </c>
       <c r="G648" t="n">
-        <v>-6725.319500336941</v>
+        <v>-6725.319500336942</v>
       </c>
     </row>
     <row r="649">
@@ -21856,7 +21856,7 @@
         <v>-6774.5547</v>
       </c>
       <c r="G651" t="n">
-        <v>-6693.891364132338</v>
+        <v>-6693.89136413234</v>
       </c>
     </row>
     <row r="652">
@@ -21881,7 +21881,7 @@
         <v>-6765.789619074075</v>
       </c>
       <c r="G652" t="n">
-        <v>-6781.132600142404</v>
+        <v>-6781.132600142405</v>
       </c>
     </row>
     <row r="653">
@@ -21906,7 +21906,7 @@
         <v>-6798.979037222222</v>
       </c>
       <c r="G653" t="n">
-        <v>-6728.116827346121</v>
+        <v>-6728.116827346123</v>
       </c>
     </row>
     <row r="654">
@@ -21931,7 +21931,7 @@
         <v>-6783.446242777777</v>
       </c>
       <c r="G654" t="n">
-        <v>-6793.434126972663</v>
+        <v>-6793.434126972664</v>
       </c>
     </row>
     <row r="655">
@@ -21956,7 +21956,7 @@
         <v>-6836.240636666666</v>
       </c>
       <c r="G655" t="n">
-        <v>-6738.30755519556</v>
+        <v>-6738.307555195561</v>
       </c>
     </row>
     <row r="656">
@@ -22006,7 +22006,7 @@
         <v>-6748.454712592593</v>
       </c>
       <c r="G657" t="n">
-        <v>-6761.865184374926</v>
+        <v>-6761.865184374927</v>
       </c>
     </row>
     <row r="658">
@@ -22025,13 +22025,13 @@
         <v>-362.92148138</v>
       </c>
       <c r="E658" t="n">
-        <v>-363.5319337683642</v>
+        <v>-363.5319337683643</v>
       </c>
       <c r="F658" t="n">
         <v>-6720.768173703704</v>
       </c>
       <c r="G658" t="n">
-        <v>-6732.072847562301</v>
+        <v>-6732.072847562302</v>
       </c>
     </row>
     <row r="659">
@@ -22075,13 +22075,13 @@
         <v>-122.75608817</v>
       </c>
       <c r="E660" t="n">
-        <v>-121.1957788267109</v>
+        <v>-121.195778826711</v>
       </c>
       <c r="F660" t="n">
         <v>-6819.782676111111</v>
       </c>
       <c r="G660" t="n">
-        <v>-6733.098823706164</v>
+        <v>-6733.098823706165</v>
       </c>
     </row>
     <row r="661">
@@ -22131,7 +22131,7 @@
         <v>-6714.143529444445</v>
       </c>
       <c r="G662" t="n">
-        <v>-6633.634218804918</v>
+        <v>-6633.634218804919</v>
       </c>
     </row>
     <row r="663">
@@ -22150,13 +22150,13 @@
         <v>-363.13345652</v>
       </c>
       <c r="E663" t="n">
-        <v>-363.1517313734262</v>
+        <v>-363.1517313734263</v>
       </c>
       <c r="F663" t="n">
         <v>-6724.69363925926</v>
       </c>
       <c r="G663" t="n">
-        <v>-6725.032062470856</v>
+        <v>-6725.032062470857</v>
       </c>
     </row>
     <row r="664">
@@ -22200,13 +22200,13 @@
         <v>-363.58577539</v>
       </c>
       <c r="E665" t="n">
-        <v>-364.6512094977253</v>
+        <v>-364.6512094977252</v>
       </c>
       <c r="F665" t="n">
         <v>-6733.069914629629</v>
       </c>
       <c r="G665" t="n">
-        <v>-6752.800175883802</v>
+        <v>-6752.800175883801</v>
       </c>
     </row>
     <row r="666">
@@ -22225,13 +22225,13 @@
         <v>-362.80632798</v>
       </c>
       <c r="E666" t="n">
-        <v>-363.4521500305173</v>
+        <v>-363.4521500305174</v>
       </c>
       <c r="F666" t="n">
         <v>-6718.635703333333</v>
       </c>
       <c r="G666" t="n">
-        <v>-6730.595370935504</v>
+        <v>-6730.595370935507</v>
       </c>
     </row>
     <row r="667">
@@ -22256,7 +22256,7 @@
         <v>-6749.141444814815</v>
       </c>
       <c r="G667" t="n">
-        <v>-6761.33214062955</v>
+        <v>-6761.332140629551</v>
       </c>
     </row>
     <row r="668">
@@ -22300,13 +22300,13 @@
         <v>-123.82006912</v>
       </c>
       <c r="E669" t="n">
-        <v>-122.3796246999856</v>
+        <v>-122.3796246999855</v>
       </c>
       <c r="F669" t="n">
         <v>-6878.892728888889</v>
       </c>
       <c r="G669" t="n">
-        <v>-6798.868038888086</v>
+        <v>-6798.868038888085</v>
       </c>
     </row>
     <row r="670">
@@ -22356,7 +22356,7 @@
         <v>-6819.004283888888</v>
       </c>
       <c r="G671" t="n">
-        <v>-6734.252185226781</v>
+        <v>-6734.252185226783</v>
       </c>
     </row>
     <row r="672">
@@ -22400,13 +22400,13 @@
         <v>-364.62451789</v>
       </c>
       <c r="E673" t="n">
-        <v>-365.7444088996389</v>
+        <v>-365.744408899639</v>
       </c>
       <c r="F673" t="n">
         <v>-6752.305886851852</v>
       </c>
       <c r="G673" t="n">
-        <v>-6773.044609252572</v>
+        <v>-6773.044609252574</v>
       </c>
     </row>
     <row r="674">
@@ -22456,7 +22456,7 @@
         <v>-6804.002129444445</v>
       </c>
       <c r="G675" t="n">
-        <v>-6723.734651870487</v>
+        <v>-6723.734651870489</v>
       </c>
     </row>
     <row r="676">
@@ -22525,13 +22525,13 @@
         <v>-123.44244111</v>
       </c>
       <c r="E678" t="n">
-        <v>-121.9366770255769</v>
+        <v>-121.936677025577</v>
       </c>
       <c r="F678" t="n">
         <v>-6857.913395</v>
       </c>
       <c r="G678" t="n">
-        <v>-6774.259834754273</v>
+        <v>-6774.259834754275</v>
       </c>
     </row>
     <row r="679">
@@ -22581,7 +22581,7 @@
         <v>-6836.987929444444</v>
       </c>
       <c r="G680" t="n">
-        <v>-6749.424068880245</v>
+        <v>-6749.424068880247</v>
       </c>
     </row>
     <row r="681">
@@ -22600,13 +22600,13 @@
         <v>-363.73530937</v>
       </c>
       <c r="E681" t="n">
-        <v>-364.7410353895452</v>
+        <v>-364.7410353895453</v>
       </c>
       <c r="F681" t="n">
         <v>-6735.839062407407</v>
       </c>
       <c r="G681" t="n">
-        <v>-6754.463618324912</v>
+        <v>-6754.463618324913</v>
       </c>
     </row>
     <row r="682">
@@ -22625,13 +22625,13 @@
         <v>-365.12523974</v>
       </c>
       <c r="E682" t="n">
-        <v>-365.7046610566497</v>
+        <v>-365.7046610566498</v>
       </c>
       <c r="F682" t="n">
         <v>-6761.578513703704</v>
       </c>
       <c r="G682" t="n">
-        <v>-6772.308538086107</v>
+        <v>-6772.308538086108</v>
       </c>
     </row>
     <row r="683">
@@ -22681,7 +22681,7 @@
         <v>-6713.070027407408</v>
       </c>
       <c r="G684" t="n">
-        <v>-6718.326108069509</v>
+        <v>-6718.32610806951</v>
       </c>
     </row>
     <row r="685">
@@ -22706,7 +22706,7 @@
         <v>-6750.701358333334</v>
       </c>
       <c r="G685" t="n">
-        <v>-6767.501859547766</v>
+        <v>-6767.501859547767</v>
       </c>
     </row>
     <row r="686">
@@ -22725,13 +22725,13 @@
         <v>-364.77537255</v>
       </c>
       <c r="E686" t="n">
-        <v>-365.7576453915764</v>
+        <v>-365.7576453915765</v>
       </c>
       <c r="F686" t="n">
         <v>-6755.099491666666</v>
       </c>
       <c r="G686" t="n">
-        <v>-6773.289729473637</v>
+        <v>-6773.289729473639</v>
       </c>
     </row>
     <row r="687">
@@ -22750,13 +22750,13 @@
         <v>-362.98153355</v>
       </c>
       <c r="E687" t="n">
-        <v>-364.233452595597</v>
+        <v>-364.2334525955972</v>
       </c>
       <c r="F687" t="n">
         <v>-6721.880250925926</v>
       </c>
       <c r="G687" t="n">
-        <v>-6745.0639369555</v>
+        <v>-6745.063936955503</v>
       </c>
     </row>
     <row r="688">
@@ -22775,13 +22775,13 @@
         <v>-121.8946505</v>
       </c>
       <c r="E688" t="n">
-        <v>-120.2732352102184</v>
+        <v>-120.2732352102185</v>
       </c>
       <c r="F688" t="n">
         <v>-6771.925027777778</v>
       </c>
       <c r="G688" t="n">
-        <v>-6681.846400567691</v>
+        <v>-6681.846400567692</v>
       </c>
     </row>
     <row r="689">
@@ -22800,13 +22800,13 @@
         <v>-363.26435833</v>
       </c>
       <c r="E689" t="n">
-        <v>-363.8705367002717</v>
+        <v>-363.8705367002718</v>
       </c>
       <c r="F689" t="n">
         <v>-6727.117746851852</v>
       </c>
       <c r="G689" t="n">
-        <v>-6738.343272227254</v>
+        <v>-6738.343272227255</v>
       </c>
     </row>
     <row r="690">
@@ -22831,7 +22831,7 @@
         <v>-6835.931640555556</v>
       </c>
       <c r="G690" t="n">
-        <v>-6759.617059312572</v>
+        <v>-6759.617059312575</v>
       </c>
     </row>
     <row r="691">
@@ -22856,7 +22856,7 @@
         <v>-6782.398228703703</v>
       </c>
       <c r="G691" t="n">
-        <v>-6797.426546177334</v>
+        <v>-6797.426546177336</v>
       </c>
     </row>
     <row r="692">
@@ -22906,7 +22906,7 @@
         <v>-6761.330139444445</v>
       </c>
       <c r="G693" t="n">
-        <v>-6670.918785742878</v>
+        <v>-6670.91878574288</v>
       </c>
     </row>
     <row r="694">
@@ -22925,13 +22925,13 @@
         <v>-122.96259863</v>
       </c>
       <c r="E694" t="n">
-        <v>-121.3741137345065</v>
+        <v>-121.3741137345066</v>
       </c>
       <c r="F694" t="n">
         <v>-6831.255479444445</v>
       </c>
       <c r="G694" t="n">
-        <v>-6743.006318583695</v>
+        <v>-6743.006318583697</v>
       </c>
     </row>
     <row r="695">
@@ -22950,13 +22950,13 @@
         <v>-364.62106916</v>
       </c>
       <c r="E695" t="n">
-        <v>-365.4568722103459</v>
+        <v>-365.456872210346</v>
       </c>
       <c r="F695" t="n">
         <v>-6752.242021481482</v>
       </c>
       <c r="G695" t="n">
-        <v>-6767.719855747147</v>
+        <v>-6767.719855747148</v>
       </c>
     </row>
     <row r="696">
@@ -23006,7 +23006,7 @@
         <v>-6809.033360925927</v>
       </c>
       <c r="G697" t="n">
-        <v>-6824.450916719555</v>
+        <v>-6824.450916719557</v>
       </c>
     </row>
     <row r="698">
@@ -23031,7 +23031,7 @@
         <v>-6752.976789999999</v>
       </c>
       <c r="G698" t="n">
-        <v>-6765.912381614723</v>
+        <v>-6765.912381614725</v>
       </c>
     </row>
     <row r="699">
@@ -23056,7 +23056,7 @@
         <v>-6739.444536481482</v>
       </c>
       <c r="G699" t="n">
-        <v>-6760.761656016639</v>
+        <v>-6760.761656016637</v>
       </c>
     </row>
     <row r="700">
@@ -23081,7 +23081,7 @@
         <v>-6743.860521481482</v>
       </c>
       <c r="G700" t="n">
-        <v>-6761.112207053777</v>
+        <v>-6761.112207053776</v>
       </c>
     </row>
     <row r="701">
@@ -23100,13 +23100,13 @@
         <v>-121.28020916</v>
       </c>
       <c r="E701" t="n">
-        <v>-119.8701193239762</v>
+        <v>-119.8701193239763</v>
       </c>
       <c r="F701" t="n">
         <v>-6737.789397777778</v>
       </c>
       <c r="G701" t="n">
-        <v>-6659.451073554235</v>
+        <v>-6659.451073554237</v>
       </c>
     </row>
     <row r="702">
@@ -23125,13 +23125,13 @@
         <v>-362.80930721</v>
       </c>
       <c r="E702" t="n">
-        <v>-363.4631752865864</v>
+        <v>-363.4631752865865</v>
       </c>
       <c r="F702" t="n">
         <v>-6718.69087425926</v>
       </c>
       <c r="G702" t="n">
-        <v>-6730.799542344193</v>
+        <v>-6730.799542344194</v>
       </c>
     </row>
     <row r="703">
@@ -23156,7 +23156,7 @@
         <v>-6820.851470555555</v>
       </c>
       <c r="G703" t="n">
-        <v>-6739.979735930156</v>
+        <v>-6739.979735930158</v>
       </c>
     </row>
     <row r="704">
@@ -23225,13 +23225,13 @@
         <v>-366.08444324</v>
       </c>
       <c r="E706" t="n">
-        <v>-366.3269721382246</v>
+        <v>-366.3269721382247</v>
       </c>
       <c r="F706" t="n">
         <v>-6779.341541481482</v>
       </c>
       <c r="G706" t="n">
-        <v>-6783.83281737453</v>
+        <v>-6783.832817374531</v>
       </c>
     </row>
     <row r="707">
@@ -23306,7 +23306,7 @@
         <v>-6715.929516666667</v>
       </c>
       <c r="G709" t="n">
-        <v>-6633.953014554416</v>
+        <v>-6633.953014554417</v>
       </c>
     </row>
     <row r="710">
@@ -23325,7 +23325,7 @@
         <v>-362.56202832</v>
       </c>
       <c r="E710" t="n">
-        <v>-363.7208948263212</v>
+        <v>-363.7208948263211</v>
       </c>
       <c r="F710" t="n">
         <v>-6714.111635555556</v>
@@ -23425,13 +23425,13 @@
         <v>-362.83156344</v>
       </c>
       <c r="E714" t="n">
-        <v>-363.6764669926778</v>
+        <v>-363.6764669926779</v>
       </c>
       <c r="F714" t="n">
         <v>-6719.103026666667</v>
       </c>
       <c r="G714" t="n">
-        <v>-6734.749388753292</v>
+        <v>-6734.749388753295</v>
       </c>
     </row>
     <row r="715">
@@ -23500,13 +23500,13 @@
         <v>-367.9826885</v>
       </c>
       <c r="E717" t="n">
-        <v>-369.0194590313951</v>
+        <v>-369.0194590313952</v>
       </c>
       <c r="F717" t="n">
         <v>-6814.494231481482</v>
       </c>
       <c r="G717" t="n">
-        <v>-6833.693685766575</v>
+        <v>-6833.693685766577</v>
       </c>
     </row>
     <row r="718">
@@ -23525,13 +23525,13 @@
         <v>-364.02607498</v>
       </c>
       <c r="E718" t="n">
-        <v>-364.78709335261</v>
+        <v>-364.7870933526099</v>
       </c>
       <c r="F718" t="n">
         <v>-6741.223610740741</v>
       </c>
       <c r="G718" t="n">
-        <v>-6755.316543566852</v>
+        <v>-6755.316543566851</v>
       </c>
     </row>
     <row r="719">
@@ -23581,7 +23581,7 @@
         <v>-6742.593829629629</v>
       </c>
       <c r="G720" t="n">
-        <v>-6758.340939367235</v>
+        <v>-6758.340939367236</v>
       </c>
     </row>
     <row r="721">
@@ -23606,7 +23606,7 @@
         <v>-6762.309055</v>
       </c>
       <c r="G721" t="n">
-        <v>-6670.370088552506</v>
+        <v>-6670.370088552507</v>
       </c>
     </row>
     <row r="722">
@@ -23631,7 +23631,7 @@
         <v>-7201.673554375</v>
       </c>
       <c r="G722" t="n">
-        <v>-7191.813193166692</v>
+        <v>-7191.813193166691</v>
       </c>
     </row>
     <row r="723">
@@ -23656,7 +23656,7 @@
         <v>-7316.8728475</v>
       </c>
       <c r="G723" t="n">
-        <v>-7306.127001265395</v>
+        <v>-7306.127001265394</v>
       </c>
     </row>
     <row r="724">
@@ -23681,7 +23681,7 @@
         <v>-7457.0092975</v>
       </c>
       <c r="G724" t="n">
-        <v>-7450.689449099918</v>
+        <v>-7450.689449099919</v>
       </c>
     </row>
     <row r="725">
@@ -23775,13 +23775,13 @@
         <v>-118.47934419</v>
       </c>
       <c r="E728" t="n">
-        <v>-118.3580627326091</v>
+        <v>-118.3580627326092</v>
       </c>
       <c r="F728" t="n">
         <v>-7404.959011875</v>
       </c>
       <c r="G728" t="n">
-        <v>-7397.378920788071</v>
+        <v>-7397.378920788072</v>
       </c>
     </row>
     <row r="729">
@@ -23806,7 +23806,7 @@
         <v>-7324.696973124999</v>
       </c>
       <c r="G729" t="n">
-        <v>-7313.927145710203</v>
+        <v>-7313.927145710204</v>
       </c>
     </row>
     <row r="730">
@@ -23825,13 +23825,13 @@
         <v>-387.00418175</v>
       </c>
       <c r="E730" t="n">
-        <v>-387.1953525278586</v>
+        <v>-387.1953525278587</v>
       </c>
       <c r="F730" t="n">
         <v>-7166.744106481481</v>
       </c>
       <c r="G730" t="n">
-        <v>-7170.284306071456</v>
+        <v>-7170.284306071458</v>
       </c>
     </row>
     <row r="731">
@@ -23931,7 +23931,7 @@
         <v>-7336.593401874999</v>
       </c>
       <c r="G734" t="n">
-        <v>-7331.960728571582</v>
+        <v>-7331.960728571583</v>
       </c>
     </row>
     <row r="735">
@@ -24006,7 +24006,7 @@
         <v>-7231.777866875001</v>
       </c>
       <c r="G737" t="n">
-        <v>-7221.529259543028</v>
+        <v>-7221.529259543029</v>
       </c>
     </row>
     <row r="738">
@@ -24031,7 +24031,7 @@
         <v>-7337.577519375001</v>
       </c>
       <c r="G738" t="n">
-        <v>-7326.702504634387</v>
+        <v>-7326.702504634388</v>
       </c>
     </row>
     <row r="739">
@@ -24056,7 +24056,7 @@
         <v>-7459.596290625</v>
       </c>
       <c r="G739" t="n">
-        <v>-7453.781084606254</v>
+        <v>-7453.781084606255</v>
       </c>
     </row>
     <row r="740">
@@ -24106,7 +24106,7 @@
         <v>-7197.641903125</v>
       </c>
       <c r="G741" t="n">
-        <v>-7187.890253158375</v>
+        <v>-7187.890253158377</v>
       </c>
     </row>
     <row r="742">
@@ -24125,13 +24125,13 @@
         <v>-120.56628118</v>
       </c>
       <c r="E742" t="n">
-        <v>-120.4368284386649</v>
+        <v>-120.436828438665</v>
       </c>
       <c r="F742" t="n">
         <v>-7535.39257375</v>
       </c>
       <c r="G742" t="n">
-        <v>-7527.301777416559</v>
+        <v>-7527.301777416561</v>
       </c>
     </row>
     <row r="743">
@@ -24181,7 +24181,7 @@
         <v>-7438.656793749999</v>
       </c>
       <c r="G744" t="n">
-        <v>-7425.753899640255</v>
+        <v>-7425.753899640256</v>
       </c>
     </row>
     <row r="745">
@@ -24231,7 +24231,7 @@
         <v>-7999.592494375001</v>
       </c>
       <c r="G746" t="n">
-        <v>-8020.54799199735</v>
+        <v>-8020.547991997352</v>
       </c>
     </row>
     <row r="747">
@@ -24331,7 +24331,7 @@
         <v>-7999.141105625</v>
       </c>
       <c r="G750" t="n">
-        <v>-8020.071964508622</v>
+        <v>-8020.071964508624</v>
       </c>
     </row>
     <row r="751">
@@ -24375,13 +24375,13 @@
         <v>-131.05688898</v>
       </c>
       <c r="E752" t="n">
-        <v>-131.3898006362978</v>
+        <v>-131.3898006362979</v>
       </c>
       <c r="F752" t="n">
         <v>-8191.05556125</v>
       </c>
       <c r="G752" t="n">
-        <v>-8211.862539768616</v>
+        <v>-8211.862539768617</v>
       </c>
     </row>
     <row r="753">
@@ -24456,7 +24456,7 @@
         <v>-7999.2785525</v>
       </c>
       <c r="G755" t="n">
-        <v>-8020.327305126175</v>
+        <v>-8020.327305126177</v>
       </c>
     </row>
     <row r="756">
@@ -24531,7 +24531,7 @@
         <v>-7997.004129375</v>
       </c>
       <c r="G758" t="n">
-        <v>-8020.994207045432</v>
+        <v>-8020.99420704543</v>
       </c>
     </row>
     <row r="759">
@@ -24600,13 +24600,13 @@
         <v>-130.57107152</v>
       </c>
       <c r="E761" t="n">
-        <v>-130.8453064881554</v>
+        <v>-130.8453064881555</v>
       </c>
       <c r="F761" t="n">
         <v>-8160.69197</v>
       </c>
       <c r="G761" t="n">
-        <v>-8177.831655509714</v>
+        <v>-8177.831655509717</v>
       </c>
     </row>
     <row r="762">
@@ -24650,13 +24650,13 @@
         <v>-131.79708208</v>
       </c>
       <c r="E763" t="n">
-        <v>-132.2090136937998</v>
+        <v>-132.2090136937999</v>
       </c>
       <c r="F763" t="n">
         <v>-8237.31763</v>
       </c>
       <c r="G763" t="n">
-        <v>-8263.06335586249</v>
+        <v>-8263.063355862492</v>
       </c>
     </row>
     <row r="764">
@@ -24706,7 +24706,7 @@
         <v>-8052.277868124999</v>
       </c>
       <c r="G765" t="n">
-        <v>-8076.168314243788</v>
+        <v>-8076.16831424379</v>
       </c>
     </row>
     <row r="766">
@@ -24781,7 +24781,7 @@
         <v>-7984.5798975</v>
       </c>
       <c r="G768" t="n">
-        <v>-8007.916368427344</v>
+        <v>-8007.916368427342</v>
       </c>
     </row>
     <row r="769">
@@ -24875,13 +24875,13 @@
         <v>-130.58160211</v>
       </c>
       <c r="E772" t="n">
-        <v>-130.9161358845947</v>
+        <v>-130.9161358845948</v>
       </c>
       <c r="F772" t="n">
         <v>-8161.350131875</v>
       </c>
       <c r="G772" t="n">
-        <v>-8182.25849278717</v>
+        <v>-8182.258492787172</v>
       </c>
     </row>
     <row r="773">
@@ -25081,7 +25081,7 @@
         <v>-7997.97589875</v>
       </c>
       <c r="G780" t="n">
-        <v>-8018.871138454342</v>
+        <v>-8018.871138454344</v>
       </c>
     </row>
     <row r="781">
@@ -25131,7 +25131,7 @@
         <v>-8122.566376875</v>
       </c>
       <c r="G782" t="n">
-        <v>-8142.99333947697</v>
+        <v>-8142.993339476971</v>
       </c>
     </row>
     <row r="783">
@@ -25156,7 +25156,7 @@
         <v>-7693.977561875</v>
       </c>
       <c r="G783" t="n">
-        <v>-7682.946422406427</v>
+        <v>-7682.946422406428</v>
       </c>
     </row>
     <row r="784">
@@ -25181,7 +25181,7 @@
         <v>-7836.358743125001</v>
       </c>
       <c r="G784" t="n">
-        <v>-7824.429879679279</v>
+        <v>-7824.42987967928</v>
       </c>
     </row>
     <row r="785">
@@ -25206,7 +25206,7 @@
         <v>-7598.33797375</v>
       </c>
       <c r="G785" t="n">
-        <v>-7589.548952654991</v>
+        <v>-7589.548952654992</v>
       </c>
     </row>
     <row r="786">
@@ -25231,7 +25231,7 @@
         <v>-7603.610691875</v>
       </c>
       <c r="G786" t="n">
-        <v>-7589.976584088881</v>
+        <v>-7589.976584088882</v>
       </c>
     </row>
     <row r="787">
@@ -25281,7 +25281,7 @@
         <v>-7559.104235000001</v>
       </c>
       <c r="G788" t="n">
-        <v>-7552.202156522035</v>
+        <v>-7552.202156522036</v>
       </c>
     </row>
     <row r="789">
@@ -25306,7 +25306,7 @@
         <v>-7750.87309</v>
       </c>
       <c r="G789" t="n">
-        <v>-7739.314124513718</v>
+        <v>-7739.314124513719</v>
       </c>
     </row>
     <row r="790">
@@ -25325,13 +25325,13 @@
         <v>-124.02220671</v>
       </c>
       <c r="E790" t="n">
-        <v>-123.8556230621205</v>
+        <v>-123.8556230621206</v>
       </c>
       <c r="F790" t="n">
         <v>-7751.387919375001</v>
       </c>
       <c r="G790" t="n">
-        <v>-7740.976441382534</v>
+        <v>-7740.976441382535</v>
       </c>
     </row>
     <row r="791">
@@ -25356,7 +25356,7 @@
         <v>-7866.5352375</v>
       </c>
       <c r="G791" t="n">
-        <v>-7870.836087105176</v>
+        <v>-7870.836087105177</v>
       </c>
     </row>
     <row r="792">
@@ -25381,7 +25381,7 @@
         <v>-7863.436946875</v>
       </c>
       <c r="G792" t="n">
-        <v>-7850.457297681622</v>
+        <v>-7850.457297681623</v>
       </c>
     </row>
     <row r="793">
@@ -25431,7 +25431,7 @@
         <v>-7782.27468625</v>
       </c>
       <c r="G794" t="n">
-        <v>-7771.875368350667</v>
+        <v>-7771.875368350669</v>
       </c>
     </row>
     <row r="795">
@@ -25481,7 +25481,7 @@
         <v>-7804.841740625</v>
       </c>
       <c r="G796" t="n">
-        <v>-7793.352448149461</v>
+        <v>-7793.352448149463</v>
       </c>
     </row>
     <row r="797">
@@ -25556,7 +25556,7 @@
         <v>-7670.129229375</v>
       </c>
       <c r="G799" t="n">
-        <v>-7658.50910547257</v>
+        <v>-7658.509105472571</v>
       </c>
     </row>
     <row r="800">
@@ -25581,7 +25581,7 @@
         <v>-7678.911864375001</v>
       </c>
       <c r="G800" t="n">
-        <v>-7667.036399565453</v>
+        <v>-7667.036399565454</v>
       </c>
     </row>
     <row r="801">
@@ -25600,13 +25600,13 @@
         <v>-121.8889044</v>
       </c>
       <c r="E801" t="n">
-        <v>-121.7318195621883</v>
+        <v>-121.7318195621884</v>
       </c>
       <c r="F801" t="n">
         <v>-7618.056525</v>
       </c>
       <c r="G801" t="n">
-        <v>-7608.238722636771</v>
+        <v>-7608.238722636773</v>
       </c>
     </row>
     <row r="802">
@@ -25631,7 +25631,7 @@
         <v>-6294.801362222222</v>
       </c>
       <c r="G802" t="n">
-        <v>-6213.565281601844</v>
+        <v>-6213.565281601845</v>
       </c>
     </row>
   </sheetData>
@@ -25680,13 +25680,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41.98268622749266</v>
+        <v>41.98268622749241</v>
       </c>
       <c r="D2" t="n">
-        <v>29.65271549685644</v>
+        <v>29.6527154968565</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9877985536754598</v>
+        <v>0.98779855367546</v>
       </c>
     </row>
     <row r="3">
@@ -25699,13 +25699,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.27250259232452</v>
+        <v>36.27250259232429</v>
       </c>
       <c r="D3" t="n">
-        <v>24.82274733456041</v>
+        <v>24.82274733456064</v>
       </c>
       <c r="E3" t="n">
-        <v>0.990245830911735</v>
+        <v>0.9902458309117351</v>
       </c>
     </row>
     <row r="4">
@@ -25805,10 +25805,10 @@
         <v>48</v>
       </c>
       <c r="E2" t="n">
-        <v>82.56731174589125</v>
+        <v>82.56731174589055</v>
       </c>
       <c r="F2" t="n">
-        <v>82.23658855164037</v>
+        <v>82.23658855163966</v>
       </c>
     </row>
     <row r="3">
@@ -25829,10 +25829,10 @@
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>9.567826908704136</v>
+        <v>9.567826908703402</v>
       </c>
       <c r="F3" t="n">
-        <v>9.288901338848595</v>
+        <v>9.288901338847912</v>
       </c>
     </row>
     <row r="4">
@@ -25853,10 +25853,10 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>23.30231791431833</v>
+        <v>23.30231791431846</v>
       </c>
       <c r="F4" t="n">
-        <v>23.14869963095771</v>
+        <v>23.14869963095787</v>
       </c>
     </row>
     <row r="5">
@@ -25877,10 +25877,10 @@
         <v>133</v>
       </c>
       <c r="E5" t="n">
-        <v>13.77983376549253</v>
+        <v>13.77983376549292</v>
       </c>
       <c r="F5" t="n">
-        <v>13.05033984115232</v>
+        <v>13.05033984115271</v>
       </c>
     </row>
     <row r="6">
@@ -25901,10 +25901,10 @@
         <v>132</v>
       </c>
       <c r="E6" t="n">
-        <v>83.3671715173524</v>
+        <v>83.36717151735144</v>
       </c>
       <c r="F6" t="n">
-        <v>83.0848265362507</v>
+        <v>83.08482653624971</v>
       </c>
     </row>
     <row r="7">
@@ -25925,10 +25925,10 @@
         <v>39</v>
       </c>
       <c r="E7" t="n">
-        <v>9.745290242235997</v>
+        <v>9.745290242235352</v>
       </c>
       <c r="F7" t="n">
-        <v>9.396849869686939</v>
+        <v>9.396849869686308</v>
       </c>
     </row>
     <row r="8">
@@ -25949,10 +25949,10 @@
         <v>40</v>
       </c>
       <c r="E8" t="n">
-        <v>22.17536832431313</v>
+        <v>22.17536832431351</v>
       </c>
       <c r="F8" t="n">
-        <v>21.46486241884588</v>
+        <v>21.46486241884632</v>
       </c>
     </row>
     <row r="9">
@@ -25973,10 +25973,10 @@
         <v>590</v>
       </c>
       <c r="E9" t="n">
-        <v>13.84455207221187</v>
+        <v>13.84455207221237</v>
       </c>
       <c r="F9" t="n">
-        <v>13.03517266190877</v>
+        <v>13.0351726619093</v>
       </c>
     </row>
   </sheetData>
